--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T310"/>
+  <dimension ref="A1:T316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15050,7 +15050,7 @@
         <v>3.1645</v>
       </c>
       <c r="Q203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R203" t="n">
         <v>22.37</v>
@@ -15122,7 +15122,7 @@
         <v>3.1645</v>
       </c>
       <c r="Q204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R204" t="n">
         <v>20.1</v>
@@ -15266,7 +15266,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="Q206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
@@ -15410,7 +15410,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="Q208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -17210,7 +17210,7 @@
         <v>9.692</v>
       </c>
       <c r="Q233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>9.692</v>
       </c>
       <c r="Q234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -22764,6 +22764,438 @@
       </c>
       <c r="T310" t="n">
         <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>103</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>2</v>
+      </c>
+      <c r="G311" t="n">
+        <v>230</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>34</v>
+      </c>
+      <c r="J311" t="n">
+        <v>30</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L311" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="M311" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N311" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O311" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="P311" t="n">
+        <v>8.747999999999999</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>3</v>
+      </c>
+      <c r="R311" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S311" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="T311" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>103</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>2</v>
+      </c>
+      <c r="G312" t="n">
+        <v>230</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>34</v>
+      </c>
+      <c r="J312" t="n">
+        <v>30</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M312" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="N312" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O312" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="P312" t="n">
+        <v>9.097</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>2</v>
+      </c>
+      <c r="R312" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="S312" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="T312" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>103</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>2</v>
+      </c>
+      <c r="G313" t="n">
+        <v>230</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>34</v>
+      </c>
+      <c r="J313" t="n">
+        <v>30</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="M313" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="N313" t="n">
+        <v>10</v>
+      </c>
+      <c r="O313" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P313" t="n">
+        <v>9.154</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>1</v>
+      </c>
+      <c r="R313" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="S313" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="T313" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>104</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>York, PA</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>3</v>
+      </c>
+      <c r="G314" t="n">
+        <v>240</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>86</v>
+      </c>
+      <c r="J314" t="n">
+        <v>18</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="M314" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="N314" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O314" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="P314" t="n">
+        <v>8.647</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>3</v>
+      </c>
+      <c r="R314" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="S314" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="T314" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>104</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>York, PA</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>3</v>
+      </c>
+      <c r="G315" t="n">
+        <v>240</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>86</v>
+      </c>
+      <c r="J315" t="n">
+        <v>18</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M315" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="N315" t="n">
+        <v>10</v>
+      </c>
+      <c r="O315" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="P315" t="n">
+        <v>8.994999999999999</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>1</v>
+      </c>
+      <c r="R315" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S315" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T315" t="n">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>104</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>York, PA</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>3</v>
+      </c>
+      <c r="G316" t="n">
+        <v>240</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="I316" t="n">
+        <v>86</v>
+      </c>
+      <c r="J316" t="n">
+        <v>18</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="M316" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="N316" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O316" t="n">
+        <v>10</v>
+      </c>
+      <c r="P316" t="n">
+        <v>8.720500000000001</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>2</v>
+      </c>
+      <c r="R316" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S316" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T316" t="n">
+        <v>4.39</v>
       </c>
     </row>
   </sheetData>

--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -554,8 +554,10 @@
       <c r="I2" t="n">
         <v>92</v>
       </c>
-      <c r="J2" t="n">
-        <v>27</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -626,8 +628,10 @@
       <c r="I3" t="n">
         <v>92</v>
       </c>
-      <c r="J3" t="n">
-        <v>27</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -698,8 +702,10 @@
       <c r="I4" t="n">
         <v>92</v>
       </c>
-      <c r="J4" t="n">
-        <v>27</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -770,8 +776,10 @@
       <c r="I5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="n">
-        <v>27</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -842,8 +850,10 @@
       <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
-        <v>27</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -914,8 +924,10 @@
       <c r="I7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
-        <v>27</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -986,8 +998,10 @@
       <c r="I8" t="n">
         <v>90</v>
       </c>
-      <c r="J8" t="n">
-        <v>37</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1058,8 +1072,10 @@
       <c r="I9" t="n">
         <v>90</v>
       </c>
-      <c r="J9" t="n">
-        <v>37</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1130,8 +1146,10 @@
       <c r="I10" t="n">
         <v>90</v>
       </c>
-      <c r="J10" t="n">
-        <v>37</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1202,8 +1220,10 @@
       <c r="I11" t="n">
         <v>22</v>
       </c>
-      <c r="J11" t="n">
-        <v>37</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1274,8 +1294,10 @@
       <c r="I12" t="n">
         <v>22</v>
       </c>
-      <c r="J12" t="n">
-        <v>37</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1346,8 +1368,10 @@
       <c r="I13" t="n">
         <v>22</v>
       </c>
-      <c r="J13" t="n">
-        <v>37</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1418,8 +1442,10 @@
       <c r="I14" t="n">
         <v>86</v>
       </c>
-      <c r="J14" t="n">
-        <v>42</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1490,8 +1516,10 @@
       <c r="I15" t="n">
         <v>86</v>
       </c>
-      <c r="J15" t="n">
-        <v>42</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1562,8 +1590,10 @@
       <c r="I16" t="n">
         <v>86</v>
       </c>
-      <c r="J16" t="n">
-        <v>42</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1634,8 +1664,10 @@
       <c r="I17" t="n">
         <v>93</v>
       </c>
-      <c r="J17" t="n">
-        <v>47</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1706,8 +1738,10 @@
       <c r="I18" t="n">
         <v>93</v>
       </c>
-      <c r="J18" t="n">
-        <v>47</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1778,8 +1812,10 @@
       <c r="I19" t="n">
         <v>93</v>
       </c>
-      <c r="J19" t="n">
-        <v>47</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1850,8 +1886,10 @@
       <c r="I20" t="n">
         <v>24</v>
       </c>
-      <c r="J20" t="n">
-        <v>47</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1922,8 +1960,10 @@
       <c r="I21" t="n">
         <v>24</v>
       </c>
-      <c r="J21" t="n">
-        <v>47</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1994,8 +2034,10 @@
       <c r="I22" t="n">
         <v>24</v>
       </c>
-      <c r="J22" t="n">
-        <v>47</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2066,8 +2108,10 @@
       <c r="I23" t="n">
         <v>89</v>
       </c>
-      <c r="J23" t="n">
-        <v>23</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2138,8 +2182,10 @@
       <c r="I24" t="n">
         <v>89</v>
       </c>
-      <c r="J24" t="n">
-        <v>23</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2210,8 +2256,10 @@
       <c r="I25" t="n">
         <v>89</v>
       </c>
-      <c r="J25" t="n">
-        <v>23</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2282,8 +2330,10 @@
       <c r="I26" t="n">
         <v>26</v>
       </c>
-      <c r="J26" t="n">
-        <v>23</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2354,8 +2404,10 @@
       <c r="I27" t="n">
         <v>26</v>
       </c>
-      <c r="J27" t="n">
-        <v>23</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2426,8 +2478,10 @@
       <c r="I28" t="n">
         <v>26</v>
       </c>
-      <c r="J28" t="n">
-        <v>23</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2498,8 +2552,10 @@
       <c r="I29" t="n">
         <v>19</v>
       </c>
-      <c r="J29" t="n">
-        <v>17</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2570,8 +2626,10 @@
       <c r="I30" t="n">
         <v>19</v>
       </c>
-      <c r="J30" t="n">
-        <v>17</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2642,8 +2700,10 @@
       <c r="I31" t="n">
         <v>19</v>
       </c>
-      <c r="J31" t="n">
-        <v>17</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2714,8 +2774,10 @@
       <c r="I32" t="n">
         <v>90</v>
       </c>
-      <c r="J32" t="n">
-        <v>5</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2786,8 +2848,10 @@
       <c r="I33" t="n">
         <v>90</v>
       </c>
-      <c r="J33" t="n">
-        <v>5</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2858,8 +2922,10 @@
       <c r="I34" t="n">
         <v>90</v>
       </c>
-      <c r="J34" t="n">
-        <v>5</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2930,8 +2996,10 @@
       <c r="I35" t="n">
         <v>21</v>
       </c>
-      <c r="J35" t="n">
-        <v>5</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3002,8 +3070,10 @@
       <c r="I36" t="n">
         <v>21</v>
       </c>
-      <c r="J36" t="n">
-        <v>5</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3074,8 +3144,10 @@
       <c r="I37" t="n">
         <v>21</v>
       </c>
-      <c r="J37" t="n">
-        <v>5</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3146,8 +3218,10 @@
       <c r="I38" t="n">
         <v>94</v>
       </c>
-      <c r="J38" t="n">
-        <v>1</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3218,8 +3292,10 @@
       <c r="I39" t="n">
         <v>94</v>
       </c>
-      <c r="J39" t="n">
-        <v>1</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3290,8 +3366,10 @@
       <c r="I40" t="n">
         <v>94</v>
       </c>
-      <c r="J40" t="n">
-        <v>1</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3362,8 +3440,10 @@
       <c r="I41" t="n">
         <v>88</v>
       </c>
-      <c r="J41" t="n">
-        <v>1</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3434,8 +3514,10 @@
       <c r="I42" t="n">
         <v>88</v>
       </c>
-      <c r="J42" t="n">
-        <v>1</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3506,8 +3588,10 @@
       <c r="I43" t="n">
         <v>88</v>
       </c>
-      <c r="J43" t="n">
-        <v>1</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3578,8 +3662,10 @@
       <c r="I44" t="n">
         <v>92</v>
       </c>
-      <c r="J44" t="n">
-        <v>4</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3650,8 +3736,10 @@
       <c r="I45" t="n">
         <v>92</v>
       </c>
-      <c r="J45" t="n">
-        <v>4</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3722,8 +3810,10 @@
       <c r="I46" t="n">
         <v>92</v>
       </c>
-      <c r="J46" t="n">
-        <v>4</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3794,8 +3884,10 @@
       <c r="I47" t="n">
         <v>20</v>
       </c>
-      <c r="J47" t="n">
-        <v>4</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3866,8 +3958,10 @@
       <c r="I48" t="n">
         <v>20</v>
       </c>
-      <c r="J48" t="n">
-        <v>4</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3938,8 +4032,10 @@
       <c r="I49" t="n">
         <v>20</v>
       </c>
-      <c r="J49" t="n">
-        <v>4</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4010,8 +4106,10 @@
       <c r="I50" t="n">
         <v>84</v>
       </c>
-      <c r="J50" t="n">
-        <v>7</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4082,8 +4180,10 @@
       <c r="I51" t="n">
         <v>84</v>
       </c>
-      <c r="J51" t="n">
-        <v>7</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4154,8 +4254,10 @@
       <c r="I52" t="n">
         <v>84</v>
       </c>
-      <c r="J52" t="n">
-        <v>7</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4226,8 +4328,10 @@
       <c r="I53" t="n">
         <v>91</v>
       </c>
-      <c r="J53" t="n">
-        <v>9</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4298,8 +4402,10 @@
       <c r="I54" t="n">
         <v>91</v>
       </c>
-      <c r="J54" t="n">
-        <v>9</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4370,8 +4476,10 @@
       <c r="I55" t="n">
         <v>91</v>
       </c>
-      <c r="J55" t="n">
-        <v>9</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4442,8 +4550,10 @@
       <c r="I56" t="n">
         <v>90</v>
       </c>
-      <c r="J56" t="n">
-        <v>10</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4514,8 +4624,10 @@
       <c r="I57" t="n">
         <v>90</v>
       </c>
-      <c r="J57" t="n">
-        <v>10</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4586,8 +4698,10 @@
       <c r="I58" t="n">
         <v>90</v>
       </c>
-      <c r="J58" t="n">
-        <v>10</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4658,8 +4772,10 @@
       <c r="I59" t="n">
         <v>93</v>
       </c>
-      <c r="J59" t="n">
-        <v>12</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4730,8 +4846,10 @@
       <c r="I60" t="n">
         <v>93</v>
       </c>
-      <c r="J60" t="n">
-        <v>12</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4802,8 +4920,10 @@
       <c r="I61" t="n">
         <v>93</v>
       </c>
-      <c r="J61" t="n">
-        <v>12</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4874,8 +4994,10 @@
       <c r="I62" t="n">
         <v>18</v>
       </c>
-      <c r="J62" t="n">
-        <v>12</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4946,8 +5068,10 @@
       <c r="I63" t="n">
         <v>18</v>
       </c>
-      <c r="J63" t="n">
-        <v>12</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5018,8 +5142,10 @@
       <c r="I64" t="n">
         <v>18</v>
       </c>
-      <c r="J64" t="n">
-        <v>12</v>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5090,8 +5216,10 @@
       <c r="I65" t="n">
         <v>22</v>
       </c>
-      <c r="J65" t="n">
-        <v>15</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5162,8 +5290,10 @@
       <c r="I66" t="n">
         <v>22</v>
       </c>
-      <c r="J66" t="n">
-        <v>15</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5234,8 +5364,10 @@
       <c r="I67" t="n">
         <v>22</v>
       </c>
-      <c r="J67" t="n">
-        <v>15</v>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5306,8 +5438,10 @@
       <c r="I68" t="n">
         <v>87</v>
       </c>
-      <c r="J68" t="n">
-        <v>19</v>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5378,8 +5512,10 @@
       <c r="I69" t="n">
         <v>87</v>
       </c>
-      <c r="J69" t="n">
-        <v>19</v>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5450,8 +5586,10 @@
       <c r="I70" t="n">
         <v>87</v>
       </c>
-      <c r="J70" t="n">
-        <v>19</v>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5522,8 +5660,10 @@
       <c r="I71" t="n">
         <v>19</v>
       </c>
-      <c r="J71" t="n">
-        <v>19</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5594,8 +5734,10 @@
       <c r="I72" t="n">
         <v>19</v>
       </c>
-      <c r="J72" t="n">
-        <v>19</v>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5666,8 +5808,10 @@
       <c r="I73" t="n">
         <v>19</v>
       </c>
-      <c r="J73" t="n">
-        <v>19</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5738,8 +5882,10 @@
       <c r="I74" t="n">
         <v>90</v>
       </c>
-      <c r="J74" t="n">
-        <v>21</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5810,8 +5956,10 @@
       <c r="I75" t="n">
         <v>90</v>
       </c>
-      <c r="J75" t="n">
-        <v>21</v>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5882,8 +6030,10 @@
       <c r="I76" t="n">
         <v>90</v>
       </c>
-      <c r="J76" t="n">
-        <v>21</v>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5954,8 +6104,10 @@
       <c r="I77" t="n">
         <v>23</v>
       </c>
-      <c r="J77" t="n">
-        <v>21</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6026,8 +6178,10 @@
       <c r="I78" t="n">
         <v>23</v>
       </c>
-      <c r="J78" t="n">
-        <v>21</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6098,8 +6252,10 @@
       <c r="I79" t="n">
         <v>23</v>
       </c>
-      <c r="J79" t="n">
-        <v>21</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6170,8 +6326,10 @@
       <c r="I80" t="n">
         <v>91</v>
       </c>
-      <c r="J80" t="n">
-        <v>25</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6242,8 +6400,10 @@
       <c r="I81" t="n">
         <v>91</v>
       </c>
-      <c r="J81" t="n">
-        <v>25</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6314,8 +6474,10 @@
       <c r="I82" t="n">
         <v>91</v>
       </c>
-      <c r="J82" t="n">
-        <v>25</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6386,8 +6548,10 @@
       <c r="I83" t="n">
         <v>21</v>
       </c>
-      <c r="J83" t="n">
-        <v>25</v>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6458,8 +6622,10 @@
       <c r="I84" t="n">
         <v>21</v>
       </c>
-      <c r="J84" t="n">
-        <v>25</v>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6530,8 +6696,10 @@
       <c r="I85" t="n">
         <v>21</v>
       </c>
-      <c r="J85" t="n">
-        <v>25</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6602,8 +6770,10 @@
       <c r="I86" t="n">
         <v>88</v>
       </c>
-      <c r="J86" t="n">
-        <v>26</v>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6674,8 +6844,10 @@
       <c r="I87" t="n">
         <v>88</v>
       </c>
-      <c r="J87" t="n">
-        <v>26</v>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6746,8 +6918,10 @@
       <c r="I88" t="n">
         <v>88</v>
       </c>
-      <c r="J88" t="n">
-        <v>26</v>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6818,8 +6992,10 @@
       <c r="I89" t="n">
         <v>17</v>
       </c>
-      <c r="J89" t="n">
-        <v>29</v>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6890,8 +7066,10 @@
       <c r="I90" t="n">
         <v>17</v>
       </c>
-      <c r="J90" t="n">
-        <v>29</v>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6962,8 +7140,10 @@
       <c r="I91" t="n">
         <v>17</v>
       </c>
-      <c r="J91" t="n">
-        <v>29</v>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7034,8 +7214,10 @@
       <c r="I92" t="n">
         <v>21</v>
       </c>
-      <c r="J92" t="n">
-        <v>102</v>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7106,8 +7288,10 @@
       <c r="I93" t="n">
         <v>21</v>
       </c>
-      <c r="J93" t="n">
-        <v>102</v>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7178,8 +7362,10 @@
       <c r="I94" t="n">
         <v>21</v>
       </c>
-      <c r="J94" t="n">
-        <v>102</v>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7250,8 +7436,10 @@
       <c r="I95" t="n">
         <v>98</v>
       </c>
-      <c r="J95" t="n">
-        <v>40</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7322,8 +7510,10 @@
       <c r="I96" t="n">
         <v>98</v>
       </c>
-      <c r="J96" t="n">
-        <v>40</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7394,8 +7584,10 @@
       <c r="I97" t="n">
         <v>98</v>
       </c>
-      <c r="J97" t="n">
-        <v>40</v>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7466,8 +7658,10 @@
       <c r="I98" t="n">
         <v>92</v>
       </c>
-      <c r="J98" t="n">
-        <v>25</v>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7538,8 +7732,10 @@
       <c r="I99" t="n">
         <v>92</v>
       </c>
-      <c r="J99" t="n">
-        <v>25</v>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7610,8 +7806,10 @@
       <c r="I100" t="n">
         <v>92</v>
       </c>
-      <c r="J100" t="n">
-        <v>25</v>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7682,8 +7880,10 @@
       <c r="I101" t="n">
         <v>97</v>
       </c>
-      <c r="J101" t="n">
-        <v>35</v>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7754,8 +7954,10 @@
       <c r="I102" t="n">
         <v>97</v>
       </c>
-      <c r="J102" t="n">
-        <v>35</v>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7826,8 +8028,10 @@
       <c r="I103" t="n">
         <v>97</v>
       </c>
-      <c r="J103" t="n">
-        <v>35</v>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7898,8 +8102,10 @@
       <c r="I104" t="n">
         <v>91</v>
       </c>
-      <c r="J104" t="n">
-        <v>20</v>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7970,8 +8176,10 @@
       <c r="I105" t="n">
         <v>91</v>
       </c>
-      <c r="J105" t="n">
-        <v>20</v>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8042,8 +8250,10 @@
       <c r="I106" t="n">
         <v>91</v>
       </c>
-      <c r="J106" t="n">
-        <v>20</v>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8114,8 +8324,10 @@
       <c r="I107" t="n">
         <v>18</v>
       </c>
-      <c r="J107" t="n">
-        <v>60</v>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8186,8 +8398,10 @@
       <c r="I108" t="n">
         <v>18</v>
       </c>
-      <c r="J108" t="n">
-        <v>60</v>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8258,8 +8472,10 @@
       <c r="I109" t="n">
         <v>18</v>
       </c>
-      <c r="J109" t="n">
-        <v>60</v>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8330,8 +8546,10 @@
       <c r="I110" t="n">
         <v>89</v>
       </c>
-      <c r="J110" t="n">
-        <v>18</v>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8402,8 +8620,10 @@
       <c r="I111" t="n">
         <v>89</v>
       </c>
-      <c r="J111" t="n">
-        <v>18</v>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8474,8 +8694,10 @@
       <c r="I112" t="n">
         <v>89</v>
       </c>
-      <c r="J112" t="n">
-        <v>18</v>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8546,8 +8768,10 @@
       <c r="I113" t="n">
         <v>91</v>
       </c>
-      <c r="J113" t="n">
-        <v>10</v>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8618,8 +8842,10 @@
       <c r="I114" t="n">
         <v>91</v>
       </c>
-      <c r="J114" t="n">
-        <v>10</v>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8690,8 +8916,10 @@
       <c r="I115" t="n">
         <v>91</v>
       </c>
-      <c r="J115" t="n">
-        <v>10</v>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8762,8 +8990,10 @@
       <c r="I116" t="n">
         <v>20</v>
       </c>
-      <c r="J116" t="n">
-        <v>18</v>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8834,8 +9064,10 @@
       <c r="I117" t="n">
         <v>20</v>
       </c>
-      <c r="J117" t="n">
-        <v>18</v>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8906,8 +9138,10 @@
       <c r="I118" t="n">
         <v>20</v>
       </c>
-      <c r="J118" t="n">
-        <v>18</v>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8978,8 +9212,10 @@
       <c r="I119" t="n">
         <v>102</v>
       </c>
-      <c r="J119" t="n">
-        <v>28</v>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -9050,8 +9286,10 @@
       <c r="I120" t="n">
         <v>102</v>
       </c>
-      <c r="J120" t="n">
-        <v>28</v>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9122,8 +9360,10 @@
       <c r="I121" t="n">
         <v>102</v>
       </c>
-      <c r="J121" t="n">
-        <v>28</v>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9194,8 +9434,10 @@
       <c r="I122" t="n">
         <v>22</v>
       </c>
-      <c r="J122" t="n">
-        <v>11</v>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9266,8 +9508,10 @@
       <c r="I123" t="n">
         <v>22</v>
       </c>
-      <c r="J123" t="n">
-        <v>11</v>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9338,8 +9582,10 @@
       <c r="I124" t="n">
         <v>22</v>
       </c>
-      <c r="J124" t="n">
-        <v>11</v>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9410,8 +9656,10 @@
       <c r="I125" t="n">
         <v>94</v>
       </c>
-      <c r="J125" t="n">
-        <v>30</v>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9482,8 +9730,10 @@
       <c r="I126" t="n">
         <v>94</v>
       </c>
-      <c r="J126" t="n">
-        <v>30</v>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9554,8 +9804,10 @@
       <c r="I127" t="n">
         <v>94</v>
       </c>
-      <c r="J127" t="n">
-        <v>30</v>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9626,8 +9878,10 @@
       <c r="I128" t="n">
         <v>17</v>
       </c>
-      <c r="J128" t="n">
-        <v>9</v>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9698,8 +9952,10 @@
       <c r="I129" t="n">
         <v>17</v>
       </c>
-      <c r="J129" t="n">
-        <v>9</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9770,8 +10026,10 @@
       <c r="I130" t="n">
         <v>17</v>
       </c>
-      <c r="J130" t="n">
-        <v>9</v>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9842,8 +10100,10 @@
       <c r="I131" t="n">
         <v>89</v>
       </c>
-      <c r="J131" t="n">
-        <v>32</v>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9914,8 +10174,10 @@
       <c r="I132" t="n">
         <v>89</v>
       </c>
-      <c r="J132" t="n">
-        <v>32</v>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9986,8 +10248,10 @@
       <c r="I133" t="n">
         <v>89</v>
       </c>
-      <c r="J133" t="n">
-        <v>32</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10058,8 +10322,10 @@
       <c r="I134" t="n">
         <v>15</v>
       </c>
-      <c r="J134" t="n">
-        <v>28</v>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10130,8 +10396,10 @@
       <c r="I135" t="n">
         <v>15</v>
       </c>
-      <c r="J135" t="n">
-        <v>28</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10202,8 +10470,10 @@
       <c r="I136" t="n">
         <v>15</v>
       </c>
-      <c r="J136" t="n">
-        <v>28</v>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10274,8 +10544,10 @@
       <c r="I137" t="n">
         <v>78</v>
       </c>
-      <c r="J137" t="n">
-        <v>15</v>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10346,8 +10618,10 @@
       <c r="I138" t="n">
         <v>78</v>
       </c>
-      <c r="J138" t="n">
-        <v>15</v>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10418,8 +10692,10 @@
       <c r="I139" t="n">
         <v>78</v>
       </c>
-      <c r="J139" t="n">
-        <v>15</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10490,8 +10766,10 @@
       <c r="I140" t="n">
         <v>82</v>
       </c>
-      <c r="J140" t="n">
-        <v>10</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10562,8 +10840,10 @@
       <c r="I141" t="n">
         <v>82</v>
       </c>
-      <c r="J141" t="n">
-        <v>10</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10634,8 +10914,10 @@
       <c r="I142" t="n">
         <v>82</v>
       </c>
-      <c r="J142" t="n">
-        <v>10</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,8 +10988,10 @@
       <c r="I143" t="n">
         <v>79</v>
       </c>
-      <c r="J143" t="n">
-        <v>8</v>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10778,8 +11062,10 @@
       <c r="I144" t="n">
         <v>79</v>
       </c>
-      <c r="J144" t="n">
-        <v>8</v>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10850,8 +11136,10 @@
       <c r="I145" t="n">
         <v>79</v>
       </c>
-      <c r="J145" t="n">
-        <v>8</v>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10922,8 +11210,10 @@
       <c r="I146" t="n">
         <v>48</v>
       </c>
-      <c r="J146" t="n">
-        <v>20</v>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10994,8 +11284,10 @@
       <c r="I147" t="n">
         <v>48</v>
       </c>
-      <c r="J147" t="n">
-        <v>20</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11066,8 +11358,10 @@
       <c r="I148" t="n">
         <v>48</v>
       </c>
-      <c r="J148" t="n">
-        <v>20</v>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11138,8 +11432,10 @@
       <c r="I149" t="n">
         <v>42</v>
       </c>
-      <c r="J149" t="n">
-        <v>30</v>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11210,8 +11506,10 @@
       <c r="I150" t="n">
         <v>42</v>
       </c>
-      <c r="J150" t="n">
-        <v>30</v>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11282,8 +11580,10 @@
       <c r="I151" t="n">
         <v>42</v>
       </c>
-      <c r="J151" t="n">
-        <v>30</v>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11354,8 +11654,10 @@
       <c r="I152" t="n">
         <v>40</v>
       </c>
-      <c r="J152" t="n">
-        <v>22</v>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11426,8 +11728,10 @@
       <c r="I153" t="n">
         <v>40</v>
       </c>
-      <c r="J153" t="n">
-        <v>22</v>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11498,8 +11802,10 @@
       <c r="I154" t="n">
         <v>40</v>
       </c>
-      <c r="J154" t="n">
-        <v>22</v>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11570,8 +11876,10 @@
       <c r="I155" t="n">
         <v>95</v>
       </c>
-      <c r="J155" t="n">
-        <v>20</v>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11642,8 +11950,10 @@
       <c r="I156" t="n">
         <v>95</v>
       </c>
-      <c r="J156" t="n">
-        <v>20</v>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11714,8 +12024,10 @@
       <c r="I157" t="n">
         <v>95</v>
       </c>
-      <c r="J157" t="n">
-        <v>20</v>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11786,8 +12098,10 @@
       <c r="I158" t="n">
         <v>90</v>
       </c>
-      <c r="J158" t="n">
-        <v>28</v>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11858,8 +12172,10 @@
       <c r="I159" t="n">
         <v>90</v>
       </c>
-      <c r="J159" t="n">
-        <v>28</v>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11930,8 +12246,10 @@
       <c r="I160" t="n">
         <v>90</v>
       </c>
-      <c r="J160" t="n">
-        <v>28</v>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12002,8 +12320,10 @@
       <c r="I161" t="n">
         <v>92</v>
       </c>
-      <c r="J161" t="n">
-        <v>14</v>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12074,8 +12394,10 @@
       <c r="I162" t="n">
         <v>92</v>
       </c>
-      <c r="J162" t="n">
-        <v>14</v>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12146,8 +12468,10 @@
       <c r="I163" t="n">
         <v>92</v>
       </c>
-      <c r="J163" t="n">
-        <v>14</v>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12218,8 +12542,10 @@
       <c r="I164" t="n">
         <v>18</v>
       </c>
-      <c r="J164" t="n">
-        <v>25</v>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12290,8 +12616,10 @@
       <c r="I165" t="n">
         <v>18</v>
       </c>
-      <c r="J165" t="n">
-        <v>25</v>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12362,8 +12690,10 @@
       <c r="I166" t="n">
         <v>18</v>
       </c>
-      <c r="J166" t="n">
-        <v>25</v>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12434,8 +12764,10 @@
       <c r="I167" t="n">
         <v>22</v>
       </c>
-      <c r="J167" t="n">
-        <v>40</v>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12506,8 +12838,10 @@
       <c r="I168" t="n">
         <v>22</v>
       </c>
-      <c r="J168" t="n">
-        <v>40</v>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12578,8 +12912,10 @@
       <c r="I169" t="n">
         <v>22</v>
       </c>
-      <c r="J169" t="n">
-        <v>40</v>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12650,8 +12986,10 @@
       <c r="I170" t="n">
         <v>92</v>
       </c>
-      <c r="J170" t="n">
-        <v>22</v>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12722,8 +13060,10 @@
       <c r="I171" t="n">
         <v>92</v>
       </c>
-      <c r="J171" t="n">
-        <v>22</v>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12794,8 +13134,10 @@
       <c r="I172" t="n">
         <v>92</v>
       </c>
-      <c r="J172" t="n">
-        <v>22</v>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12866,8 +13208,10 @@
       <c r="I173" t="n">
         <v>88</v>
       </c>
-      <c r="J173" t="n">
-        <v>12</v>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -12938,8 +13282,10 @@
       <c r="I174" t="n">
         <v>88</v>
       </c>
-      <c r="J174" t="n">
-        <v>12</v>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13010,8 +13356,10 @@
       <c r="I175" t="n">
         <v>88</v>
       </c>
-      <c r="J175" t="n">
-        <v>12</v>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13082,8 +13430,10 @@
       <c r="I176" t="n">
         <v>84</v>
       </c>
-      <c r="J176" t="n">
-        <v>8</v>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13154,8 +13504,10 @@
       <c r="I177" t="n">
         <v>84</v>
       </c>
-      <c r="J177" t="n">
-        <v>8</v>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13226,8 +13578,10 @@
       <c r="I178" t="n">
         <v>84</v>
       </c>
-      <c r="J178" t="n">
-        <v>8</v>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13298,8 +13652,10 @@
       <c r="I179" t="n">
         <v>12</v>
       </c>
-      <c r="J179" t="n">
-        <v>20</v>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13370,8 +13726,10 @@
       <c r="I180" t="n">
         <v>12</v>
       </c>
-      <c r="J180" t="n">
-        <v>20</v>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13442,8 +13800,10 @@
       <c r="I181" t="n">
         <v>12</v>
       </c>
-      <c r="J181" t="n">
-        <v>20</v>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13514,8 +13874,10 @@
       <c r="I182" t="n">
         <v>20</v>
       </c>
-      <c r="J182" t="n">
-        <v>24</v>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13586,8 +13948,10 @@
       <c r="I183" t="n">
         <v>20</v>
       </c>
-      <c r="J183" t="n">
-        <v>24</v>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13658,8 +14022,10 @@
       <c r="I184" t="n">
         <v>20</v>
       </c>
-      <c r="J184" t="n">
-        <v>24</v>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13730,8 +14096,10 @@
       <c r="I185" t="n">
         <v>22</v>
       </c>
-      <c r="J185" t="n">
-        <v>1</v>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13802,8 +14170,10 @@
       <c r="I186" t="n">
         <v>22</v>
       </c>
-      <c r="J186" t="n">
-        <v>1</v>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -13874,8 +14244,10 @@
       <c r="I187" t="n">
         <v>22</v>
       </c>
-      <c r="J187" t="n">
-        <v>1</v>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -13946,8 +14318,10 @@
       <c r="I188" t="n">
         <v>28</v>
       </c>
-      <c r="J188" t="n">
-        <v>3</v>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -14018,8 +14392,10 @@
       <c r="I189" t="n">
         <v>28</v>
       </c>
-      <c r="J189" t="n">
-        <v>3</v>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14090,8 +14466,10 @@
       <c r="I190" t="n">
         <v>28</v>
       </c>
-      <c r="J190" t="n">
-        <v>3</v>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14162,8 +14540,10 @@
       <c r="I191" t="n">
         <v>77</v>
       </c>
-      <c r="J191" t="n">
-        <v>22</v>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14234,8 +14614,10 @@
       <c r="I192" t="n">
         <v>77</v>
       </c>
-      <c r="J192" t="n">
-        <v>22</v>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14306,8 +14688,10 @@
       <c r="I193" t="n">
         <v>77</v>
       </c>
-      <c r="J193" t="n">
-        <v>22</v>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14378,8 +14762,10 @@
       <c r="I194" t="n">
         <v>44</v>
       </c>
-      <c r="J194" t="n">
-        <v>32</v>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14450,8 +14836,10 @@
       <c r="I195" t="n">
         <v>44</v>
       </c>
-      <c r="J195" t="n">
-        <v>32</v>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14522,8 +14910,10 @@
       <c r="I196" t="n">
         <v>44</v>
       </c>
-      <c r="J196" t="n">
-        <v>32</v>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14594,8 +14984,10 @@
       <c r="I197" t="n">
         <v>94</v>
       </c>
-      <c r="J197" t="n">
-        <v>24</v>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14666,8 +15058,10 @@
       <c r="I198" t="n">
         <v>94</v>
       </c>
-      <c r="J198" t="n">
-        <v>24</v>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14738,8 +15132,10 @@
       <c r="I199" t="n">
         <v>94</v>
       </c>
-      <c r="J199" t="n">
-        <v>24</v>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14810,8 +15206,10 @@
       <c r="I200" t="n">
         <v>10</v>
       </c>
-      <c r="J200" t="n">
-        <v>33</v>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -14882,8 +15280,10 @@
       <c r="I201" t="n">
         <v>10</v>
       </c>
-      <c r="J201" t="n">
-        <v>33</v>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -14954,8 +15354,10 @@
       <c r="I202" t="n">
         <v>10</v>
       </c>
-      <c r="J202" t="n">
-        <v>33</v>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15026,8 +15428,10 @@
       <c r="I203" t="n">
         <v>91</v>
       </c>
-      <c r="J203" t="n">
-        <v>48</v>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15098,8 +15502,10 @@
       <c r="I204" t="n">
         <v>91</v>
       </c>
-      <c r="J204" t="n">
-        <v>48</v>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15170,8 +15576,10 @@
       <c r="I205" t="n">
         <v>91</v>
       </c>
-      <c r="J205" t="n">
-        <v>48</v>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15242,8 +15650,10 @@
       <c r="I206" t="n">
         <v>68</v>
       </c>
-      <c r="J206" t="n">
-        <v>15</v>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15314,8 +15724,10 @@
       <c r="I207" t="n">
         <v>68</v>
       </c>
-      <c r="J207" t="n">
-        <v>15</v>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15386,8 +15798,10 @@
       <c r="I208" t="n">
         <v>68</v>
       </c>
-      <c r="J208" t="n">
-        <v>15</v>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15458,8 +15872,10 @@
       <c r="I209" t="n">
         <v>8</v>
       </c>
-      <c r="J209" t="n">
-        <v>18</v>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15530,8 +15946,10 @@
       <c r="I210" t="n">
         <v>8</v>
       </c>
-      <c r="J210" t="n">
-        <v>18</v>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15602,8 +16020,10 @@
       <c r="I211" t="n">
         <v>8</v>
       </c>
-      <c r="J211" t="n">
-        <v>18</v>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15674,8 +16094,10 @@
       <c r="I212" t="n">
         <v>5</v>
       </c>
-      <c r="J212" t="n">
-        <v>11</v>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -15746,8 +16168,10 @@
       <c r="I213" t="n">
         <v>5</v>
       </c>
-      <c r="J213" t="n">
-        <v>11</v>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -15818,8 +16242,10 @@
       <c r="I214" t="n">
         <v>5</v>
       </c>
-      <c r="J214" t="n">
-        <v>11</v>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -15890,8 +16316,10 @@
       <c r="I215" t="n">
         <v>42</v>
       </c>
-      <c r="J215" t="n">
-        <v>29</v>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -15962,8 +16390,10 @@
       <c r="I216" t="n">
         <v>42</v>
       </c>
-      <c r="J216" t="n">
-        <v>29</v>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16034,8 +16464,10 @@
       <c r="I217" t="n">
         <v>42</v>
       </c>
-      <c r="J217" t="n">
-        <v>29</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16106,8 +16538,10 @@
       <c r="I218" t="n">
         <v>50</v>
       </c>
-      <c r="J218" t="n">
-        <v>9</v>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16178,8 +16612,10 @@
       <c r="I219" t="n">
         <v>50</v>
       </c>
-      <c r="J219" t="n">
-        <v>9</v>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16250,8 +16686,10 @@
       <c r="I220" t="n">
         <v>50</v>
       </c>
-      <c r="J220" t="n">
-        <v>9</v>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16322,8 +16760,10 @@
       <c r="I221" t="n">
         <v>54</v>
       </c>
-      <c r="J221" t="n">
-        <v>52</v>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16394,8 +16834,10 @@
       <c r="I222" t="n">
         <v>54</v>
       </c>
-      <c r="J222" t="n">
-        <v>52</v>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16466,8 +16908,10 @@
       <c r="I223" t="n">
         <v>54</v>
       </c>
-      <c r="J223" t="n">
-        <v>52</v>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16538,8 +16982,10 @@
       <c r="I224" t="n">
         <v>62</v>
       </c>
-      <c r="J224" t="n">
-        <v>24</v>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16610,8 +17056,10 @@
       <c r="I225" t="n">
         <v>62</v>
       </c>
-      <c r="J225" t="n">
-        <v>24</v>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16682,8 +17130,10 @@
       <c r="I226" t="n">
         <v>62</v>
       </c>
-      <c r="J226" t="n">
-        <v>24</v>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -16754,8 +17204,10 @@
       <c r="I227" t="n">
         <v>68</v>
       </c>
-      <c r="J227" t="n">
-        <v>14</v>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -16826,8 +17278,10 @@
       <c r="I228" t="n">
         <v>68</v>
       </c>
-      <c r="J228" t="n">
-        <v>14</v>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -16898,8 +17352,10 @@
       <c r="I229" t="n">
         <v>68</v>
       </c>
-      <c r="J229" t="n">
-        <v>14</v>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -16970,8 +17426,10 @@
       <c r="I230" t="n">
         <v>59</v>
       </c>
-      <c r="J230" t="n">
-        <v>35</v>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -17042,8 +17500,10 @@
       <c r="I231" t="n">
         <v>59</v>
       </c>
-      <c r="J231" t="n">
-        <v>35</v>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -17114,8 +17574,10 @@
       <c r="I232" t="n">
         <v>59</v>
       </c>
-      <c r="J232" t="n">
-        <v>35</v>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -17186,8 +17648,10 @@
       <c r="I233" t="n">
         <v>72</v>
       </c>
-      <c r="J233" t="n">
-        <v>74</v>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17258,8 +17722,10 @@
       <c r="I234" t="n">
         <v>72</v>
       </c>
-      <c r="J234" t="n">
-        <v>74</v>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17330,8 +17796,10 @@
       <c r="I235" t="n">
         <v>72</v>
       </c>
-      <c r="J235" t="n">
-        <v>74</v>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17402,8 +17870,10 @@
       <c r="I236" t="n">
         <v>78</v>
       </c>
-      <c r="J236" t="n">
-        <v>16</v>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17474,8 +17944,10 @@
       <c r="I237" t="n">
         <v>78</v>
       </c>
-      <c r="J237" t="n">
-        <v>16</v>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17546,8 +18018,10 @@
       <c r="I238" t="n">
         <v>78</v>
       </c>
-      <c r="J238" t="n">
-        <v>16</v>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -17618,8 +18092,10 @@
       <c r="I239" t="n">
         <v>82</v>
       </c>
-      <c r="J239" t="n">
-        <v>31</v>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17690,8 +18166,10 @@
       <c r="I240" t="n">
         <v>82</v>
       </c>
-      <c r="J240" t="n">
-        <v>31</v>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -17762,8 +18240,10 @@
       <c r="I241" t="n">
         <v>82</v>
       </c>
-      <c r="J241" t="n">
-        <v>31</v>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -17834,8 +18314,10 @@
       <c r="I242" t="n">
         <v>80</v>
       </c>
-      <c r="J242" t="n">
-        <v>44</v>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -17906,8 +18388,10 @@
       <c r="I243" t="n">
         <v>80</v>
       </c>
-      <c r="J243" t="n">
-        <v>44</v>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -17978,8 +18462,10 @@
       <c r="I244" t="n">
         <v>80</v>
       </c>
-      <c r="J244" t="n">
-        <v>44</v>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18050,8 +18536,10 @@
       <c r="I245" t="n">
         <v>83</v>
       </c>
-      <c r="J245" t="n">
-        <v>22</v>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -18122,8 +18610,10 @@
       <c r="I246" t="n">
         <v>83</v>
       </c>
-      <c r="J246" t="n">
-        <v>22</v>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18194,8 +18684,10 @@
       <c r="I247" t="n">
         <v>83</v>
       </c>
-      <c r="J247" t="n">
-        <v>22</v>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18266,8 +18758,10 @@
       <c r="I248" t="n">
         <v>96</v>
       </c>
-      <c r="J248" t="n">
-        <v>7</v>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -18338,8 +18832,10 @@
       <c r="I249" t="n">
         <v>96</v>
       </c>
-      <c r="J249" t="n">
-        <v>7</v>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -18410,8 +18906,10 @@
       <c r="I250" t="n">
         <v>96</v>
       </c>
-      <c r="J250" t="n">
-        <v>7</v>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -18482,8 +18980,10 @@
       <c r="I251" t="n">
         <v>98</v>
       </c>
-      <c r="J251" t="n">
-        <v>26</v>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -18554,8 +19054,10 @@
       <c r="I252" t="n">
         <v>98</v>
       </c>
-      <c r="J252" t="n">
-        <v>26</v>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -18626,8 +19128,10 @@
       <c r="I253" t="n">
         <v>98</v>
       </c>
-      <c r="J253" t="n">
-        <v>26</v>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -18698,8 +19202,10 @@
       <c r="I254" t="n">
         <v>90</v>
       </c>
-      <c r="J254" t="n">
-        <v>86</v>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -18770,8 +19276,10 @@
       <c r="I255" t="n">
         <v>90</v>
       </c>
-      <c r="J255" t="n">
-        <v>86</v>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -18842,8 +19350,10 @@
       <c r="I256" t="n">
         <v>90</v>
       </c>
-      <c r="J256" t="n">
-        <v>86</v>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -18914,8 +19424,10 @@
       <c r="I257" t="n">
         <v>29</v>
       </c>
-      <c r="J257" t="n">
-        <v>41</v>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -18986,8 +19498,10 @@
       <c r="I258" t="n">
         <v>29</v>
       </c>
-      <c r="J258" t="n">
-        <v>41</v>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -19058,8 +19572,10 @@
       <c r="I259" t="n">
         <v>29</v>
       </c>
-      <c r="J259" t="n">
-        <v>41</v>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -19130,8 +19646,10 @@
       <c r="I260" t="n">
         <v>24</v>
       </c>
-      <c r="J260" t="n">
-        <v>12</v>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -19202,8 +19720,10 @@
       <c r="I261" t="n">
         <v>24</v>
       </c>
-      <c r="J261" t="n">
-        <v>12</v>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -19274,8 +19794,10 @@
       <c r="I262" t="n">
         <v>24</v>
       </c>
-      <c r="J262" t="n">
-        <v>12</v>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -19346,8 +19868,10 @@
       <c r="I263" t="n">
         <v>18</v>
       </c>
-      <c r="J263" t="n">
-        <v>25</v>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -19418,8 +19942,10 @@
       <c r="I264" t="n">
         <v>18</v>
       </c>
-      <c r="J264" t="n">
-        <v>25</v>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -19490,8 +20016,10 @@
       <c r="I265" t="n">
         <v>18</v>
       </c>
-      <c r="J265" t="n">
-        <v>25</v>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -19562,8 +20090,10 @@
       <c r="I266" t="n">
         <v>87</v>
       </c>
-      <c r="J266" t="n">
-        <v>15</v>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -19634,8 +20164,10 @@
       <c r="I267" t="n">
         <v>87</v>
       </c>
-      <c r="J267" t="n">
-        <v>15</v>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -19706,8 +20238,10 @@
       <c r="I268" t="n">
         <v>87</v>
       </c>
-      <c r="J268" t="n">
-        <v>15</v>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -19778,8 +20312,10 @@
       <c r="I269" t="n">
         <v>22</v>
       </c>
-      <c r="J269" t="n">
-        <v>30</v>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -19850,8 +20386,10 @@
       <c r="I270" t="n">
         <v>22</v>
       </c>
-      <c r="J270" t="n">
-        <v>30</v>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -19922,8 +20460,10 @@
       <c r="I271" t="n">
         <v>22</v>
       </c>
-      <c r="J271" t="n">
-        <v>30</v>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -19994,8 +20534,10 @@
       <c r="I272" t="n">
         <v>92</v>
       </c>
-      <c r="J272" t="n">
-        <v>28</v>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -20066,8 +20608,10 @@
       <c r="I273" t="n">
         <v>92</v>
       </c>
-      <c r="J273" t="n">
-        <v>28</v>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -20138,8 +20682,10 @@
       <c r="I274" t="n">
         <v>92</v>
       </c>
-      <c r="J274" t="n">
-        <v>28</v>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -20210,8 +20756,10 @@
       <c r="I275" t="n">
         <v>25</v>
       </c>
-      <c r="J275" t="n">
-        <v>22</v>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -20282,8 +20830,10 @@
       <c r="I276" t="n">
         <v>25</v>
       </c>
-      <c r="J276" t="n">
-        <v>22</v>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -20354,8 +20904,10 @@
       <c r="I277" t="n">
         <v>25</v>
       </c>
-      <c r="J277" t="n">
-        <v>22</v>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20426,8 +20978,10 @@
       <c r="I278" t="n">
         <v>18</v>
       </c>
-      <c r="J278" t="n">
-        <v>28</v>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20498,8 +21052,10 @@
       <c r="I279" t="n">
         <v>18</v>
       </c>
-      <c r="J279" t="n">
-        <v>28</v>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -20570,8 +21126,10 @@
       <c r="I280" t="n">
         <v>18</v>
       </c>
-      <c r="J280" t="n">
-        <v>28</v>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -20642,8 +21200,10 @@
       <c r="I281" t="n">
         <v>14</v>
       </c>
-      <c r="J281" t="n">
-        <v>35</v>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -20714,8 +21274,10 @@
       <c r="I282" t="n">
         <v>14</v>
       </c>
-      <c r="J282" t="n">
-        <v>35</v>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -20786,8 +21348,10 @@
       <c r="I283" t="n">
         <v>14</v>
       </c>
-      <c r="J283" t="n">
-        <v>35</v>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -20858,8 +21422,10 @@
       <c r="I284" t="n">
         <v>28</v>
       </c>
-      <c r="J284" t="n">
-        <v>20</v>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -20930,8 +21496,10 @@
       <c r="I285" t="n">
         <v>28</v>
       </c>
-      <c r="J285" t="n">
-        <v>20</v>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21002,8 +21570,10 @@
       <c r="I286" t="n">
         <v>28</v>
       </c>
-      <c r="J286" t="n">
-        <v>20</v>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21074,8 +21644,10 @@
       <c r="I287" t="n">
         <v>10</v>
       </c>
-      <c r="J287" t="n">
-        <v>18</v>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -21146,8 +21718,10 @@
       <c r="I288" t="n">
         <v>10</v>
       </c>
-      <c r="J288" t="n">
-        <v>18</v>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -21218,8 +21792,10 @@
       <c r="I289" t="n">
         <v>10</v>
       </c>
-      <c r="J289" t="n">
-        <v>18</v>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -21290,8 +21866,10 @@
       <c r="I290" t="n">
         <v>5</v>
       </c>
-      <c r="J290" t="n">
-        <v>40</v>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -21362,8 +21940,10 @@
       <c r="I291" t="n">
         <v>5</v>
       </c>
-      <c r="J291" t="n">
-        <v>40</v>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21434,8 +22014,10 @@
       <c r="I292" t="n">
         <v>5</v>
       </c>
-      <c r="J292" t="n">
-        <v>40</v>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -21506,8 +22088,10 @@
       <c r="I293" t="n">
         <v>22</v>
       </c>
-      <c r="J293" t="n">
-        <v>30</v>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -21578,8 +22162,10 @@
       <c r="I294" t="n">
         <v>22</v>
       </c>
-      <c r="J294" t="n">
-        <v>30</v>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -21650,8 +22236,10 @@
       <c r="I295" t="n">
         <v>22</v>
       </c>
-      <c r="J295" t="n">
-        <v>30</v>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -21722,8 +22310,10 @@
       <c r="I296" t="n">
         <v>12</v>
       </c>
-      <c r="J296" t="n">
-        <v>25</v>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -21794,8 +22384,10 @@
       <c r="I297" t="n">
         <v>12</v>
       </c>
-      <c r="J297" t="n">
-        <v>25</v>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
@@ -21866,8 +22458,10 @@
       <c r="I298" t="n">
         <v>12</v>
       </c>
-      <c r="J298" t="n">
-        <v>25</v>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -21938,8 +22532,10 @@
       <c r="I299" t="n">
         <v>89</v>
       </c>
-      <c r="J299" t="n">
-        <v>15</v>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -22010,8 +22606,10 @@
       <c r="I300" t="n">
         <v>89</v>
       </c>
-      <c r="J300" t="n">
-        <v>15</v>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -22082,8 +22680,10 @@
       <c r="I301" t="n">
         <v>89</v>
       </c>
-      <c r="J301" t="n">
-        <v>15</v>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -22154,8 +22754,10 @@
       <c r="I302" t="n">
         <v>91</v>
       </c>
-      <c r="J302" t="n">
-        <v>22</v>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -22226,8 +22828,10 @@
       <c r="I303" t="n">
         <v>91</v>
       </c>
-      <c r="J303" t="n">
-        <v>22</v>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -22298,8 +22902,10 @@
       <c r="I304" t="n">
         <v>91</v>
       </c>
-      <c r="J304" t="n">
-        <v>22</v>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -22370,8 +22976,10 @@
       <c r="I305" t="n">
         <v>12</v>
       </c>
-      <c r="J305" t="n">
-        <v>68</v>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -22442,8 +23050,10 @@
       <c r="I306" t="n">
         <v>12</v>
       </c>
-      <c r="J306" t="n">
-        <v>68</v>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -22514,8 +23124,10 @@
       <c r="I307" t="n">
         <v>12</v>
       </c>
-      <c r="J307" t="n">
-        <v>68</v>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -22586,8 +23198,10 @@
       <c r="I308" t="n">
         <v>87</v>
       </c>
-      <c r="J308" t="n">
-        <v>33</v>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -22658,8 +23272,10 @@
       <c r="I309" t="n">
         <v>87</v>
       </c>
-      <c r="J309" t="n">
-        <v>33</v>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -22730,8 +23346,10 @@
       <c r="I310" t="n">
         <v>87</v>
       </c>
-      <c r="J310" t="n">
-        <v>33</v>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -22802,8 +23420,10 @@
       <c r="I311" t="n">
         <v>34</v>
       </c>
-      <c r="J311" t="n">
-        <v>30</v>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -22874,8 +23494,10 @@
       <c r="I312" t="n">
         <v>34</v>
       </c>
-      <c r="J312" t="n">
-        <v>30</v>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -22946,8 +23568,10 @@
       <c r="I313" t="n">
         <v>34</v>
       </c>
-      <c r="J313" t="n">
-        <v>30</v>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23018,8 +23642,10 @@
       <c r="I314" t="n">
         <v>86</v>
       </c>
-      <c r="J314" t="n">
-        <v>18</v>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -23090,8 +23716,10 @@
       <c r="I315" t="n">
         <v>86</v>
       </c>
-      <c r="J315" t="n">
-        <v>18</v>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -23162,8 +23790,10 @@
       <c r="I316" t="n">
         <v>86</v>
       </c>
-      <c r="J316" t="n">
-        <v>18</v>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>

--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I'm working from home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm working from home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I'm home all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 2 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what AC temperature should I set?</t>
+          <t>I'm gone most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 1 person — what AC temperature should I set?</t>
+          <t>I'm planning to stay in all day with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I'm around all day with 1 person — what heat temperature should I set?</t>
+          <t>I'm around all day with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what AC temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 2 people — what heat temperature should I set?</t>
+          <t>I'm spending the day at home with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 2 people — what heat temperature should I set?</t>
+          <t>I'm not planning to leave today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>I'm away most of today — what heat temperature should I set?</t>
+          <t>I'm away most of today, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I'm staying home today with 1 person — what AC temperature should I set?</t>
+          <t>I'm staying home today with 1 person, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the rowhouse?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the rowhouse?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the rowhouse?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>I'm not home today — what AC temperature should I set?</t>
+          <t>I'm not home today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 5 people — what AC temperature should I set?</t>
+          <t>I'm home and not going out with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I'm out for a couple hours — what heat temperature should I set for the townhouse?</t>
+          <t>I'm out for a couple hours, what heat temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>I'm staying put today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying put today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I'm working from home today with 4 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>I'm home all day with 5 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I'm running out for a short while — what AC temperature should I set for the townhouse?</t>
+          <t>I'm running out for a short while, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>I'm gone for a few hours — what AC temperature should I set for the townhouse?</t>
+          <t>I'm gone for a few hours, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>I'm out of the house all day — what AC temperature should I set?</t>
+          <t>I'm out of the house all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit — what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>I'm away for the day — what heat temperature should I set?</t>
+          <t>I'm away for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>I'm planning to stay in all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm planning to stay in all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>I'm around all day with 3 people — what AC temperature should I set?</t>
+          <t>I'm around all day with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>I'm home for the day with 2 people — what heat temperature should I set?</t>
+          <t>I'm home for the day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>I'm going to be out all day — what AC temperature should I set?</t>
+          <t>I'm going to be out all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>I'm leaving the house for most of the day — what AC temperature should I set?</t>
+          <t>I'm leaving the house for most of the day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>We're about to turn in — what heat temperature should I set overnight?</t>
+          <t>We're about to turn in, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>We're heading to bed soon — what heat temperature should I set overnight?</t>
+          <t>We're heading to bed soon, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>I'm not planning to leave today with 4 people — what AC temperature should I set?</t>
+          <t>I'm not planning to leave today with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>I'm staying home today with 2 people — what heat temperature should I set?</t>
+          <t>I'm staying home today with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>I'm home and not going out with 4 people — what heat temperature should I set?</t>
+          <t>I'm home and not going out with 4 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>I'm out of the house for a while — what AC temperature should I set?</t>
+          <t>I'm out of the house for a while, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>I'm home all day with 4 people — what AC temperature should I set?</t>
+          <t>I'm home all day with 4 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 5 people — what AC temperature should I set?</t>
+          <t>I'm not going anywhere with 5 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 1 person — what heat temperature should I set?</t>
+          <t>I'm sticking around the house with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -19838,7 +19838,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -20282,7 +20282,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>I'm staying in today with 3 people — what heat temperature should I set?</t>
+          <t>I'm staying in today with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>I'm around all day with 2 people — what heat temperature should I set?</t>
+          <t>I'm around all day with 2 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>We're calling it a night — what heat temperature should I set overnight?</t>
+          <t>We're calling it a night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -21836,7 +21836,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -21910,7 +21910,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>I'm not going anywhere with 3 people — what heat temperature should I set?</t>
+          <t>I'm not going anywhere with 3 people, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>I'm working from home today with 2 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -22798,7 +22798,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">

--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.01</v>
+        <v>7.75</v>
       </c>
       <c r="M2" t="n">
-        <v>8.01</v>
+        <v>7.77</v>
       </c>
       <c r="N2" t="n">
         <v>7</v>
@@ -577,7 +577,7 @@
         <v>7.43</v>
       </c>
       <c r="P2" t="n">
-        <v>7.721</v>
+        <v>7.558999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8.23</v>
+        <v>7.96</v>
       </c>
       <c r="M3" t="n">
-        <v>8.220000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="N3" t="n">
         <v>10</v>
@@ -651,7 +651,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>8.564</v>
+        <v>8.3955</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8.44</v>
+        <v>8.17</v>
       </c>
       <c r="M4" t="n">
-        <v>8.42</v>
+        <v>8.17</v>
       </c>
       <c r="N4" t="n">
         <v>7</v>
@@ -725,7 +725,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.097</v>
+        <v>7.9285</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="N5" t="n">
         <v>8.6</v>
@@ -799,7 +799,7 @@
         <v>6.31</v>
       </c>
       <c r="P5" t="n">
-        <v>9.166500000000001</v>
+        <v>9.1165</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="N6" t="n">
         <v>9.32</v>
@@ -873,7 +873,7 @@
         <v>6.31</v>
       </c>
       <c r="P6" t="n">
-        <v>9.310500000000001</v>
+        <v>9.153500000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.92</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="N7" t="n">
         <v>7</v>
@@ -947,7 +947,7 @@
         <v>6.31</v>
       </c>
       <c r="P7" t="n">
-        <v>8.7735</v>
+        <v>8.5825</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.56</v>
+        <v>5.36</v>
       </c>
       <c r="M8" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
       <c r="N8" t="n">
         <v>9.32</v>
@@ -1021,7 +1021,7 @@
         <v>7.71</v>
       </c>
       <c r="P8" t="n">
-        <v>6.658999999999999</v>
+        <v>6.532500000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.97</v>
+        <v>5.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6.03</v>
+        <v>5.83</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
@@ -1095,7 +1095,7 @@
         <v>7.71</v>
       </c>
       <c r="P9" t="n">
-        <v>6.458</v>
+        <v>6.321999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.38</v>
+        <v>6.15</v>
       </c>
       <c r="M10" t="n">
-        <v>6.42</v>
+        <v>6.22</v>
       </c>
       <c r="N10" t="n">
         <v>4.06</v>
@@ -1169,7 +1169,7 @@
         <v>7.04</v>
       </c>
       <c r="P10" t="n">
-        <v>6.029</v>
+        <v>5.89</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.79</v>
+        <v>7.53</v>
       </c>
       <c r="M11" t="n">
-        <v>7.79</v>
+        <v>7.56</v>
       </c>
       <c r="N11" t="n">
         <v>6.11</v>
@@ -1243,7 +1243,7 @@
         <v>5.96</v>
       </c>
       <c r="P11" t="n">
-        <v>7.1795</v>
+        <v>7.021</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.4</v>
+        <v>7.15</v>
       </c>
       <c r="M12" t="n">
-        <v>7.42</v>
+        <v>7.19</v>
       </c>
       <c r="N12" t="n">
         <v>8.6</v>
@@ -1317,7 +1317,7 @@
         <v>5.96</v>
       </c>
       <c r="P12" t="n">
-        <v>7.431</v>
+        <v>7.2755</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.01</v>
+        <v>6.77</v>
       </c>
       <c r="M13" t="n">
-        <v>7.04</v>
+        <v>6.82</v>
       </c>
       <c r="N13" t="n">
         <v>9.32</v>
@@ -1391,7 +1391,7 @@
         <v>5.96</v>
       </c>
       <c r="P13" t="n">
-        <v>7.325</v>
+        <v>7.175999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>7.63</v>
+        <v>7.38</v>
       </c>
       <c r="M14" t="n">
-        <v>7.56</v>
+        <v>7.33</v>
       </c>
       <c r="N14" t="n">
         <v>8.6</v>
@@ -1465,7 +1465,7 @@
         <v>7.5</v>
       </c>
       <c r="P14" t="n">
-        <v>7.779999999999999</v>
+        <v>7.624499999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7.84</v>
+        <v>7.58</v>
       </c>
       <c r="M15" t="n">
-        <v>7.76</v>
+        <v>7.52</v>
       </c>
       <c r="N15" t="n">
         <v>9.32</v>
@@ -1539,7 +1539,7 @@
         <v>7.82</v>
       </c>
       <c r="P15" t="n">
-        <v>8.105</v>
+        <v>7.943</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.039999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="M16" t="n">
-        <v>7.96</v>
+        <v>7.72</v>
       </c>
       <c r="N16" t="n">
         <v>7</v>
@@ -1613,7 +1613,7 @@
         <v>7.82</v>
       </c>
       <c r="P16" t="n">
-        <v>7.771</v>
+        <v>7.609</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.16</v>
+        <v>6.92</v>
       </c>
       <c r="M17" t="n">
-        <v>7.19</v>
+        <v>6.96</v>
       </c>
       <c r="N17" t="n">
         <v>8.6</v>
@@ -1687,7 +1687,7 @@
         <v>7.29</v>
       </c>
       <c r="P17" t="n">
-        <v>7.478</v>
+        <v>7.3255</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.45</v>
+        <v>7.21</v>
       </c>
       <c r="M18" t="n">
-        <v>7.47</v>
+        <v>7.24</v>
       </c>
       <c r="N18" t="n">
         <v>6.11</v>
@@ -1761,7 +1761,7 @@
         <v>7.29</v>
       </c>
       <c r="P18" t="n">
-        <v>7.164999999999999</v>
+        <v>7.012499999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.75</v>
+        <v>7.49</v>
       </c>
       <c r="M19" t="n">
-        <v>7.75</v>
+        <v>7.51</v>
       </c>
       <c r="N19" t="n">
         <v>2.86</v>
@@ -1835,7 +1835,7 @@
         <v>5.61</v>
       </c>
       <c r="P19" t="n">
-        <v>6.451</v>
+        <v>6.289</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.42</v>
+        <v>8.15</v>
       </c>
       <c r="M20" t="n">
-        <v>8.4</v>
+        <v>8.15</v>
       </c>
       <c r="N20" t="n">
         <v>5.13</v>
@@ -1909,7 +1909,7 @@
         <v>5.61</v>
       </c>
       <c r="P20" t="n">
-        <v>7.333499999999999</v>
+        <v>7.164999999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8.08</v>
+        <v>7.81</v>
       </c>
       <c r="M21" t="n">
-        <v>8.07</v>
+        <v>7.83</v>
       </c>
       <c r="N21" t="n">
         <v>7.83</v>
@@ -1983,7 +1983,7 @@
         <v>5.61</v>
       </c>
       <c r="P21" t="n">
-        <v>7.656</v>
+        <v>7.491</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.73</v>
+        <v>7.48</v>
       </c>
       <c r="M22" t="n">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
       <c r="N22" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
         <v>5.61</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8695</v>
+        <v>7.7105</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.15</v>
+        <v>6.91</v>
       </c>
       <c r="M23" t="n">
-        <v>7.17</v>
+        <v>6.95</v>
       </c>
       <c r="N23" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8545</v>
+        <v>7.7055</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7.39</v>
+        <v>7.15</v>
       </c>
       <c r="M24" t="n">
-        <v>7.41</v>
+        <v>7.18</v>
       </c>
       <c r="N24" t="n">
         <v>7.83</v>
@@ -2205,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>7.576499999999999</v>
+        <v>7.423999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7.64</v>
+        <v>7.38</v>
       </c>
       <c r="M25" t="n">
-        <v>7.64</v>
+        <v>7.41</v>
       </c>
       <c r="N25" t="n">
         <v>5.13</v>
@@ -2279,7 +2279,7 @@
         <v>8.33</v>
       </c>
       <c r="P25" t="n">
-        <v>7.241499999999999</v>
+        <v>7.082999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9.83</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>9.77</v>
+        <v>9.49</v>
       </c>
       <c r="N26" t="n">
         <v>7.83</v>
@@ -2353,7 +2353,7 @@
         <v>6.2</v>
       </c>
       <c r="P26" t="n">
-        <v>8.8645</v>
+        <v>8.676499999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9.59</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>9.539999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="N27" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>6.2</v>
       </c>
       <c r="P27" t="n">
-        <v>9.145999999999999</v>
+        <v>8.961499999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9.359999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="M28" t="n">
-        <v>9.31</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>7.83</v>
@@ -2501,7 +2501,7 @@
         <v>6.2</v>
       </c>
       <c r="P28" t="n">
-        <v>8.5625</v>
+        <v>8.378</v>
       </c>
       <c r="Q28" t="n">
         <v>3</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8.73</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>8.640000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
         <v>9.08</v>
       </c>
       <c r="P32" t="n">
-        <v>9.005000000000001</v>
+        <v>8.833499999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8.890000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>8.81</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>7.83</v>
@@ -2871,7 +2871,7 @@
         <v>9.08</v>
       </c>
       <c r="P33" t="n">
-        <v>8.6785</v>
+        <v>8.503499999999999</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>9.06</v>
+        <v>8.77</v>
       </c>
       <c r="M34" t="n">
-        <v>8.970000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>5.13</v>
@@ -2945,7 +2945,7 @@
         <v>9.44</v>
       </c>
       <c r="P34" t="n">
-        <v>8.2995</v>
+        <v>8.121499999999999</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>9.81</v>
       </c>
       <c r="M35" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="N35" t="n">
         <v>7</v>
@@ -3019,7 +3019,7 @@
         <v>7.13</v>
       </c>
       <c r="P35" t="n">
-        <v>8.9695</v>
+        <v>8.8215</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.949999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>9.85</v>
+        <v>9.57</v>
       </c>
       <c r="N36" t="n">
         <v>9.32</v>
@@ -3093,7 +3093,7 @@
         <v>7.13</v>
       </c>
       <c r="P36" t="n">
-        <v>9.366</v>
+        <v>9.175000000000001</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.779999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="M37" t="n">
-        <v>9.68</v>
+        <v>9.4</v>
       </c>
       <c r="N37" t="n">
         <v>8.6</v>
@@ -3167,7 +3167,7 @@
         <v>7.13</v>
       </c>
       <c r="P37" t="n">
-        <v>9.111499999999999</v>
+        <v>8.923500000000001</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>8.720000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="M38" t="n">
-        <v>8.630000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
         <v>9.52</v>
       </c>
       <c r="P38" t="n">
-        <v>9.064499999999999</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8.859999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="M39" t="n">
-        <v>8.779999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="N39" t="n">
         <v>7.34</v>
@@ -3315,7 +3315,7 @@
         <v>9.52</v>
       </c>
       <c r="P39" t="n">
-        <v>8.626999999999999</v>
+        <v>8.451999999999998</v>
       </c>
       <c r="Q39" t="n">
         <v>2</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>9.01</v>
+        <v>8.73</v>
       </c>
       <c r="M40" t="n">
-        <v>8.92</v>
+        <v>8.66</v>
       </c>
       <c r="N40" t="n">
         <v>3.83</v>
@@ -3389,7 +3389,7 @@
         <v>9.52</v>
       </c>
       <c r="P40" t="n">
-        <v>8.018999999999998</v>
+        <v>7.844</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>8.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>8.460000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>7.83</v>
@@ -3463,7 +3463,7 @@
         <v>9.42</v>
       </c>
       <c r="P41" t="n">
-        <v>8.484</v>
+        <v>8.312499999999998</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8.630000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="M42" t="n">
-        <v>8.6</v>
+        <v>8.35</v>
       </c>
       <c r="N42" t="n">
         <v>10</v>
@@ -3537,7 +3537,7 @@
         <v>9.42</v>
       </c>
       <c r="P42" t="n">
-        <v>9.012</v>
+        <v>8.8405</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="M43" t="n">
-        <v>8.75</v>
+        <v>8.49</v>
       </c>
       <c r="N43" t="n">
         <v>7.83</v>
@@ -3611,7 +3611,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="P43" t="n">
-        <v>8.7295</v>
+        <v>8.554499999999999</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>7.48</v>
+        <v>7.23</v>
       </c>
       <c r="M44" t="n">
-        <v>7.41</v>
+        <v>7.18</v>
       </c>
       <c r="N44" t="n">
         <v>8.6</v>
@@ -3685,7 +3685,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>7.9375</v>
+        <v>7.782</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>7.77</v>
+        <v>7.52</v>
       </c>
       <c r="M45" t="n">
-        <v>7.7</v>
+        <v>7.46</v>
       </c>
       <c r="N45" t="n">
         <v>6.11</v>
@@ -3759,7 +3759,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="P45" t="n">
-        <v>7.628</v>
+        <v>7.468999999999999</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>8.06</v>
+        <v>7.8</v>
       </c>
       <c r="M46" t="n">
-        <v>7.99</v>
+        <v>7.74</v>
       </c>
       <c r="N46" t="n">
         <v>2.86</v>
@@ -3833,7 +3833,7 @@
         <v>7.23</v>
       </c>
       <c r="P46" t="n">
-        <v>6.871</v>
+        <v>6.7055</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>7.35</v>
+        <v>7.11</v>
       </c>
       <c r="M47" t="n">
-        <v>7.28</v>
+        <v>7.06</v>
       </c>
       <c r="N47" t="n">
         <v>6.11</v>
@@ -3907,7 +3907,7 @@
         <v>7.23</v>
       </c>
       <c r="P47" t="n">
-        <v>7.059500000000001</v>
+        <v>6.9105</v>
       </c>
       <c r="Q47" t="n">
         <v>3</v>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.99</v>
+        <v>6.75</v>
       </c>
       <c r="M48" t="n">
-        <v>6.92</v>
+        <v>6.7</v>
       </c>
       <c r="N48" t="n">
         <v>8.6</v>
@@ -3981,7 +3981,7 @@
         <v>7.23</v>
       </c>
       <c r="P48" t="n">
-        <v>7.3235</v>
+        <v>7.174499999999999</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6.62</v>
+        <v>6.39</v>
       </c>
       <c r="M49" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="N49" t="n">
         <v>9.32</v>
@@ -4055,7 +4055,7 @@
         <v>7.23</v>
       </c>
       <c r="P49" t="n">
-        <v>7.227</v>
+        <v>7.084499999999999</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>8.02</v>
+        <v>7.76</v>
       </c>
       <c r="M50" t="n">
-        <v>7.94</v>
+        <v>7.7</v>
       </c>
       <c r="N50" t="n">
         <v>9.32</v>
@@ -4129,7 +4129,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P50" t="n">
-        <v>8.4305</v>
+        <v>8.2685</v>
       </c>
       <c r="Q50" t="n">
         <v>2</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>8.279999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="M51" t="n">
-        <v>8.199999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="N51" t="n">
         <v>8.6</v>
@@ -4203,7 +4203,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P51" t="n">
-        <v>8.455499999999999</v>
+        <v>8.286999999999999</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>8.539999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="M52" t="n">
-        <v>8.449999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N52" t="n">
         <v>6.11</v>
@@ -4277,7 +4277,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>8.122999999999999</v>
+        <v>7.951499999999999</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>7.74</v>
       </c>
       <c r="M53" t="n">
-        <v>7.92</v>
+        <v>7.68</v>
       </c>
       <c r="N53" t="n">
         <v>8.300000000000001</v>
@@ -4351,7 +4351,7 @@
         <v>8.630000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>8.1265</v>
+        <v>7.9645</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>8.210000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="M54" t="n">
-        <v>8.119999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="N54" t="n">
         <v>5.13</v>
@@ -4425,7 +4425,7 @@
         <v>8.630000000000001</v>
       </c>
       <c r="P54" t="n">
-        <v>7.6255</v>
+        <v>7.460500000000001</v>
       </c>
       <c r="Q54" t="n">
         <v>2</v>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>8.41</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>8.33</v>
+        <v>8.08</v>
       </c>
       <c r="N55" t="n">
         <v>0.64</v>
@@ -4499,7 +4499,7 @@
         <v>6.74</v>
       </c>
       <c r="P55" t="n">
-        <v>6.5775</v>
+        <v>6.409</v>
       </c>
       <c r="Q55" t="n">
         <v>3</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="M56" t="n">
-        <v>5.92</v>
+        <v>5.73</v>
       </c>
       <c r="N56" t="n">
         <v>5.13</v>
@@ -4573,7 +4573,7 @@
         <v>8.48</v>
       </c>
       <c r="P56" t="n">
-        <v>6.128</v>
+        <v>5.9985</v>
       </c>
       <c r="Q56" t="n">
         <v>3</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>6.2</v>
+        <v>5.98</v>
       </c>
       <c r="M57" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="N57" t="n">
         <v>9.18</v>
@@ -4647,7 +4647,7 @@
         <v>8.48</v>
       </c>
       <c r="P57" t="n">
-        <v>7.1555</v>
+        <v>7.0195</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>6.54</v>
+        <v>6.31</v>
       </c>
       <c r="M58" t="n">
-        <v>6.58</v>
+        <v>6.37</v>
       </c>
       <c r="N58" t="n">
         <v>7.34</v>
@@ -4721,7 +4721,7 @@
         <v>8.48</v>
       </c>
       <c r="P58" t="n">
-        <v>7.005</v>
+        <v>6.8625</v>
       </c>
       <c r="Q58" t="n">
         <v>2</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="M59" t="n">
-        <v>4.79</v>
+        <v>4.62</v>
       </c>
       <c r="N59" t="n">
         <v>9.18</v>
@@ -4795,7 +4795,7 @@
         <v>8.44</v>
       </c>
       <c r="P59" t="n">
-        <v>6.2305</v>
+        <v>6.114</v>
       </c>
       <c r="Q59" t="n">
         <v>2</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5.2</v>
+        <v>5.01</v>
       </c>
       <c r="M60" t="n">
-        <v>5.15</v>
+        <v>4.98</v>
       </c>
       <c r="N60" t="n">
         <v>8.300000000000001</v>
@@ -4869,7 +4869,7 @@
         <v>8.44</v>
       </c>
       <c r="P60" t="n">
-        <v>6.2885</v>
+        <v>6.172000000000001</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5.57</v>
+        <v>5.37</v>
       </c>
       <c r="M61" t="n">
-        <v>5.51</v>
+        <v>5.33</v>
       </c>
       <c r="N61" t="n">
         <v>5.13</v>
@@ -4943,7 +4943,7 @@
         <v>8.44</v>
       </c>
       <c r="P61" t="n">
-        <v>5.8915</v>
+        <v>5.7685</v>
       </c>
       <c r="Q61" t="n">
         <v>3</v>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7.31</v>
+        <v>7.07</v>
       </c>
       <c r="M62" t="n">
-        <v>7.24</v>
+        <v>7.02</v>
       </c>
       <c r="N62" t="n">
         <v>6.29</v>
@@ -5017,7 +5017,7 @@
         <v>6.58</v>
       </c>
       <c r="P62" t="n">
-        <v>6.972</v>
+        <v>6.823</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.92</v>
+        <v>6.68</v>
       </c>
       <c r="M63" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="N63" t="n">
         <v>9.18</v>
@@ -5091,7 +5091,7 @@
         <v>6.58</v>
       </c>
       <c r="P63" t="n">
-        <v>7.2965</v>
+        <v>7.151</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>6.52</v>
+        <v>6.3</v>
       </c>
       <c r="M64" t="n">
-        <v>6.46</v>
+        <v>6.25</v>
       </c>
       <c r="N64" t="n">
         <v>8.300000000000001</v>
@@ -5165,7 +5165,7 @@
         <v>6.58</v>
       </c>
       <c r="P64" t="n">
-        <v>6.864</v>
+        <v>6.7245</v>
       </c>
       <c r="Q64" t="n">
         <v>3</v>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>6.84</v>
+        <v>6.6</v>
       </c>
       <c r="M65" t="n">
-        <v>6.87</v>
+        <v>6.65</v>
       </c>
       <c r="N65" t="n">
         <v>6.11</v>
@@ -5239,7 +5239,7 @@
         <v>6.44</v>
       </c>
       <c r="P65" t="n">
-        <v>6.644500000000001</v>
+        <v>6.495500000000001</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="M66" t="n">
-        <v>6.44</v>
+        <v>6.24</v>
       </c>
       <c r="N66" t="n">
         <v>8.6</v>
@@ -5313,7 +5313,7 @@
         <v>6.44</v>
       </c>
       <c r="P66" t="n">
-        <v>6.859999999999999</v>
+        <v>6.723999999999999</v>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.96</v>
+        <v>5.75</v>
       </c>
       <c r="M67" t="n">
-        <v>6.02</v>
+        <v>5.82</v>
       </c>
       <c r="N67" t="n">
         <v>9.32</v>
@@ -5387,7 +5387,7 @@
         <v>6.44</v>
       </c>
       <c r="P67" t="n">
-        <v>6.725</v>
+        <v>6.592</v>
       </c>
       <c r="Q67" t="n">
         <v>2</v>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.16</v>
+        <v>4.97</v>
       </c>
       <c r="M68" t="n">
-        <v>5.25</v>
+        <v>5.07</v>
       </c>
       <c r="N68" t="n">
         <v>9.18</v>
@@ -5461,7 +5461,7 @@
         <v>8.16</v>
       </c>
       <c r="P68" t="n">
-        <v>6.4455</v>
+        <v>6.3255</v>
       </c>
       <c r="Q68" t="n">
         <v>2</v>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.58</v>
+        <v>5.38</v>
       </c>
       <c r="M69" t="n">
-        <v>5.65</v>
+        <v>5.46</v>
       </c>
       <c r="N69" t="n">
         <v>8.300000000000001</v>
@@ -5535,7 +5535,7 @@
         <v>8.49</v>
       </c>
       <c r="P69" t="n">
-        <v>6.585000000000001</v>
+        <v>6.4585</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="M70" t="n">
-        <v>6.06</v>
+        <v>5.86</v>
       </c>
       <c r="N70" t="n">
         <v>5.13</v>
@@ -5609,7 +5609,7 @@
         <v>8.49</v>
       </c>
       <c r="P70" t="n">
-        <v>6.220499999999999</v>
+        <v>6.0845</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="M71" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="N71" t="n">
         <v>5.92</v>
@@ -5683,7 +5683,7 @@
         <v>6.34</v>
       </c>
       <c r="P71" t="n">
-        <v>7.1595</v>
+        <v>7.000999999999999</v>
       </c>
       <c r="Q71" t="n">
         <v>2</v>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>7.32</v>
+        <v>7.08</v>
       </c>
       <c r="M72" t="n">
-        <v>7.34</v>
+        <v>7.12</v>
       </c>
       <c r="N72" t="n">
         <v>9.109999999999999</v>
@@ -5757,7 +5757,7 @@
         <v>6.34</v>
       </c>
       <c r="P72" t="n">
-        <v>7.538</v>
+        <v>7.388999999999999</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6.92</v>
+        <v>6.69</v>
       </c>
       <c r="M73" t="n">
-        <v>6.95</v>
+        <v>6.74</v>
       </c>
       <c r="N73" t="n">
         <v>8.15</v>
@@ -5831,7 +5831,7 @@
         <v>6.34</v>
       </c>
       <c r="P73" t="n">
-        <v>7.089499999999999</v>
+        <v>6.946999999999999</v>
       </c>
       <c r="Q73" t="n">
         <v>3</v>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>5.62</v>
+        <v>5.42</v>
       </c>
       <c r="M74" t="n">
-        <v>5.69</v>
+        <v>5.51</v>
       </c>
       <c r="N74" t="n">
         <v>8.6</v>
@@ -5905,7 +5905,7 @@
         <v>7.92</v>
       </c>
       <c r="P74" t="n">
-        <v>6.5855</v>
+        <v>6.462499999999999</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>6.09</v>
+        <v>5.88</v>
       </c>
       <c r="M75" t="n">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="N75" t="n">
         <v>6.11</v>
@@ -5979,7 +5979,7 @@
         <v>8.25</v>
       </c>
       <c r="P75" t="n">
-        <v>6.439</v>
+        <v>6.306</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>6.56</v>
+        <v>6.34</v>
       </c>
       <c r="M76" t="n">
-        <v>6.6</v>
+        <v>6.39</v>
       </c>
       <c r="N76" t="n">
         <v>2.86</v>
@@ -6053,7 +6053,7 @@
         <v>6.14</v>
       </c>
       <c r="P76" t="n">
-        <v>5.771</v>
+        <v>5.6315</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>5.68</v>
+        <v>5.47</v>
       </c>
       <c r="M77" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="N77" t="n">
         <v>6.11</v>
@@ -6127,7 +6127,7 @@
         <v>6.14</v>
       </c>
       <c r="P77" t="n">
-        <v>5.859500000000001</v>
+        <v>5.73</v>
       </c>
       <c r="Q77" t="n">
         <v>2</v>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="M78" t="n">
-        <v>5.22</v>
+        <v>5.04</v>
       </c>
       <c r="N78" t="n">
         <v>8.6</v>
@@ -6201,7 +6201,7 @@
         <v>6.14</v>
       </c>
       <c r="P78" t="n">
-        <v>6.007</v>
+        <v>5.887</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="M79" t="n">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="N79" t="n">
         <v>9.32</v>
@@ -6275,7 +6275,7 @@
         <v>6.14</v>
       </c>
       <c r="P79" t="n">
-        <v>5.803500000000001</v>
+        <v>5.69</v>
       </c>
       <c r="Q79" t="n">
         <v>3</v>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="M80" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="N80" t="n">
         <v>10</v>
@@ -6349,7 +6349,7 @@
         <v>7.88</v>
       </c>
       <c r="P80" t="n">
-        <v>5.236499999999999</v>
+        <v>5.1455</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="M81" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="N81" t="n">
         <v>7.83</v>
@@ -6423,7 +6423,7 @@
         <v>7.88</v>
       </c>
       <c r="P81" t="n">
-        <v>5.1595</v>
+        <v>5.058999999999999</v>
       </c>
       <c r="Q81" t="n">
         <v>2</v>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="M82" t="n">
-        <v>4.31</v>
+        <v>4.15</v>
       </c>
       <c r="N82" t="n">
         <v>5.13</v>
@@ -6497,7 +6497,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P82" t="n">
-        <v>5.024499999999999</v>
+        <v>4.9175</v>
       </c>
       <c r="Q82" t="n">
         <v>3</v>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.65</v>
+        <v>4.47</v>
       </c>
       <c r="M83" t="n">
-        <v>4.75</v>
+        <v>4.58</v>
       </c>
       <c r="N83" t="n">
         <v>7</v>
@@ -6571,7 +6571,7 @@
         <v>6.1</v>
       </c>
       <c r="P83" t="n">
-        <v>5.3725</v>
+        <v>5.259</v>
       </c>
       <c r="Q83" t="n">
         <v>2</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.04</v>
+        <v>3.87</v>
       </c>
       <c r="M84" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="N84" t="n">
         <v>9.32</v>
@@ -6645,7 +6645,7 @@
         <v>6.1</v>
       </c>
       <c r="P84" t="n">
-        <v>5.447</v>
+        <v>5.34</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="L85" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="M85" t="n">
         <v>3.42</v>
-      </c>
-      <c r="M85" t="n">
-        <v>3.56</v>
       </c>
       <c r="N85" t="n">
         <v>8.6</v>
@@ -6719,7 +6719,7 @@
         <v>6.1</v>
       </c>
       <c r="P85" t="n">
-        <v>4.907</v>
+        <v>4.813</v>
       </c>
       <c r="Q85" t="n">
         <v>3</v>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="M86" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="N86" t="n">
         <v>8.300000000000001</v>
@@ -6793,7 +6793,7 @@
         <v>7.79</v>
       </c>
       <c r="P86" t="n">
-        <v>5.795</v>
+        <v>5.685</v>
       </c>
       <c r="Q86" t="n">
         <v>3</v>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="M87" t="n">
-        <v>4.98</v>
+        <v>4.8</v>
       </c>
       <c r="N87" t="n">
         <v>9.18</v>
@@ -6867,7 +6867,7 @@
         <v>7.79</v>
       </c>
       <c r="P87" t="n">
-        <v>6.2115</v>
+        <v>6.0945</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
       <c r="M88" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="N88" t="n">
         <v>6.29</v>
@@ -6941,7 +6941,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P88" t="n">
-        <v>5.92</v>
+        <v>5.7965</v>
       </c>
       <c r="Q88" t="n">
         <v>2</v>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.36</v>
+        <v>6.14</v>
       </c>
       <c r="M89" t="n">
-        <v>6.41</v>
+        <v>6.2</v>
       </c>
       <c r="N89" t="n">
         <v>7</v>
@@ -7015,7 +7015,7 @@
         <v>5.96</v>
       </c>
       <c r="P89" t="n">
-        <v>6.445500000000001</v>
+        <v>6.306</v>
       </c>
       <c r="Q89" t="n">
         <v>2</v>
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>5.93</v>
+        <v>5.72</v>
       </c>
       <c r="M90" t="n">
-        <v>5.99</v>
+        <v>5.8</v>
       </c>
       <c r="N90" t="n">
         <v>9.32</v>
@@ -7089,7 +7089,7 @@
         <v>5.96</v>
       </c>
       <c r="P90" t="n">
-        <v>6.6335</v>
+        <v>6.504</v>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="M91" t="n">
-        <v>5.58</v>
+        <v>5.39</v>
       </c>
       <c r="N91" t="n">
         <v>8.6</v>
@@ -7163,7 +7163,7 @@
         <v>5.96</v>
       </c>
       <c r="P91" t="n">
-        <v>6.217</v>
+        <v>6.0905</v>
       </c>
       <c r="Q91" t="n">
         <v>3</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>5.49</v>
+        <v>5.29</v>
       </c>
       <c r="M92" t="n">
-        <v>5.82</v>
+        <v>5.62</v>
       </c>
       <c r="N92" t="n">
         <v>7</v>
@@ -7237,7 +7237,7 @@
         <v>5.61</v>
       </c>
       <c r="P92" t="n">
-        <v>5.9255</v>
+        <v>5.7955</v>
       </c>
       <c r="Q92" t="n">
         <v>2</v>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="M93" t="n">
-        <v>5.3</v>
+        <v>5.12</v>
       </c>
       <c r="N93" t="n">
         <v>9.32</v>
@@ -7311,7 +7311,7 @@
         <v>5.61</v>
       </c>
       <c r="P93" t="n">
-        <v>6.039499999999999</v>
+        <v>5.922499999999999</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
       <c r="M94" t="n">
-        <v>4.79</v>
+        <v>4.62</v>
       </c>
       <c r="N94" t="n">
         <v>8.6</v>
@@ -7385,7 +7385,7 @@
         <v>5.61</v>
       </c>
       <c r="P94" t="n">
-        <v>5.552</v>
+        <v>5.4415</v>
       </c>
       <c r="Q94" t="n">
         <v>3</v>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>4.55</v>
+        <v>4.37</v>
       </c>
       <c r="M98" t="n">
-        <v>4.66</v>
+        <v>4.49</v>
       </c>
       <c r="N98" t="n">
         <v>10</v>
@@ -7681,7 +7681,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P98" t="n">
-        <v>6.214</v>
+        <v>6.1005</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.81</v>
+        <v>4.62</v>
       </c>
       <c r="M99" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="N99" t="n">
         <v>8.6</v>
@@ -7755,7 +7755,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P99" t="n">
-        <v>6.096</v>
+        <v>5.9795</v>
       </c>
       <c r="Q99" t="n">
         <v>2</v>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>5.06</v>
+        <v>4.87</v>
       </c>
       <c r="M100" t="n">
-        <v>5.15</v>
+        <v>4.97</v>
       </c>
       <c r="N100" t="n">
         <v>7</v>
@@ -7829,7 +7829,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P100" t="n">
-        <v>5.9385</v>
+        <v>5.8185</v>
       </c>
       <c r="Q100" t="n">
         <v>3</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
         <v>2.35</v>
@@ -8051,7 +8051,7 @@
         <v>6.74</v>
       </c>
       <c r="P103" t="n">
-        <v>1.4845</v>
+        <v>1.481</v>
       </c>
       <c r="Q103" t="n">
         <v>3</v>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>5.95</v>
+        <v>5.74</v>
       </c>
       <c r="M104" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="N104" t="n">
         <v>9.32</v>
@@ -8125,7 +8125,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P104" t="n">
-        <v>6.943999999999999</v>
+        <v>6.810999999999999</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>6.18</v>
+        <v>5.96</v>
       </c>
       <c r="M105" t="n">
-        <v>6.12</v>
+        <v>5.92</v>
       </c>
       <c r="N105" t="n">
         <v>7.83</v>
@@ -8199,7 +8199,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P105" t="n">
-        <v>6.791999999999999</v>
+        <v>6.656</v>
       </c>
       <c r="Q105" t="n">
         <v>2</v>
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="M106" t="n">
-        <v>6.34</v>
+        <v>6.14</v>
       </c>
       <c r="N106" t="n">
         <v>6.11</v>
@@ -8273,7 +8273,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P106" t="n">
-        <v>6.590999999999999</v>
+        <v>6.454999999999999</v>
       </c>
       <c r="Q106" t="n">
         <v>3</v>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>7.04</v>
+        <v>6.8</v>
       </c>
       <c r="M107" t="n">
-        <v>7.06</v>
+        <v>6.84</v>
       </c>
       <c r="N107" t="n">
         <v>6.11</v>
@@ -8347,7 +8347,7 @@
         <v>5.68</v>
       </c>
       <c r="P107" t="n">
-        <v>6.657000000000001</v>
+        <v>6.508</v>
       </c>
       <c r="Q107" t="n">
         <v>3</v>
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>6.59</v>
+        <v>6.36</v>
       </c>
       <c r="M108" t="n">
-        <v>6.63</v>
+        <v>6.42</v>
       </c>
       <c r="N108" t="n">
         <v>8.6</v>
@@ -8421,7 +8421,7 @@
         <v>5.68</v>
       </c>
       <c r="P108" t="n">
-        <v>6.869499999999999</v>
+        <v>6.726999999999999</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -8483,10 +8483,10 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>6.13</v>
+        <v>5.92</v>
       </c>
       <c r="M109" t="n">
-        <v>6.19</v>
+        <v>5.99</v>
       </c>
       <c r="N109" t="n">
         <v>9.32</v>
@@ -8495,7 +8495,7 @@
         <v>5.68</v>
       </c>
       <c r="P109" t="n">
-        <v>6.7215</v>
+        <v>6.5885</v>
       </c>
       <c r="Q109" t="n">
         <v>2</v>
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.46</v>
+        <v>5.26</v>
       </c>
       <c r="M110" t="n">
-        <v>5.53</v>
+        <v>5.35</v>
       </c>
       <c r="N110" t="n">
         <v>10</v>
@@ -8569,7 +8569,7 @@
         <v>8.32</v>
       </c>
       <c r="P110" t="n">
-        <v>6.8215</v>
+        <v>6.6985</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="M111" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="N111" t="n">
         <v>9.32</v>
@@ -8643,7 +8643,7 @@
         <v>8.32</v>
       </c>
       <c r="P111" t="n">
-        <v>6.77</v>
+        <v>6.647</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>5.73</v>
+        <v>5.52</v>
       </c>
       <c r="M112" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="N112" t="n">
         <v>8.6</v>
@@ -8717,7 +8717,7 @@
         <v>8.32</v>
       </c>
       <c r="P112" t="n">
-        <v>6.7135</v>
+        <v>6.584</v>
       </c>
       <c r="Q112" t="n">
         <v>3</v>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>6.68</v>
+        <v>6.45</v>
       </c>
       <c r="M113" t="n">
-        <v>6.61</v>
+        <v>6.4</v>
       </c>
       <c r="N113" t="n">
         <v>4.5</v>
@@ -8791,7 +8791,7 @@
         <v>9.09</v>
       </c>
       <c r="P113" t="n">
-        <v>6.581</v>
+        <v>6.4385</v>
       </c>
       <c r="Q113" t="n">
         <v>2</v>
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>6.12</v>
+        <v>5.9</v>
       </c>
       <c r="M114" t="n">
-        <v>6.06</v>
+        <v>5.86</v>
       </c>
       <c r="N114" t="n">
         <v>10</v>
@@ -8865,7 +8865,7 @@
         <v>8.75</v>
       </c>
       <c r="P114" t="n">
-        <v>7.269499999999999</v>
+        <v>7.1335</v>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -8927,10 +8927,10 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.56</v>
+        <v>5.36</v>
       </c>
       <c r="M115" t="n">
-        <v>5.51</v>
+        <v>5.32</v>
       </c>
       <c r="N115" t="n">
         <v>4.5</v>
@@ -8939,7 +8939,7 @@
         <v>7.36</v>
       </c>
       <c r="P115" t="n">
-        <v>5.6005</v>
+        <v>5.474</v>
       </c>
       <c r="Q115" t="n">
         <v>3</v>
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>6.82</v>
+        <v>6.59</v>
       </c>
       <c r="M116" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="N116" t="n">
         <v>6.11</v>
@@ -9013,7 +9013,7 @@
         <v>6.44</v>
       </c>
       <c r="P116" t="n">
-        <v>6.6315</v>
+        <v>6.489000000000001</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>5.77</v>
+        <v>5.56</v>
       </c>
       <c r="M117" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="N117" t="n">
         <v>8.6</v>
@@ -9087,7 +9087,7 @@
         <v>6.44</v>
       </c>
       <c r="P117" t="n">
-        <v>6.461</v>
+        <v>6.327999999999999</v>
       </c>
       <c r="Q117" t="n">
         <v>2</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="M118" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="N118" t="n">
         <v>1.53</v>
@@ -9161,7 +9161,7 @@
         <v>5.04</v>
       </c>
       <c r="P118" t="n">
-        <v>4.165</v>
+        <v>4.0515</v>
       </c>
       <c r="Q118" t="n">
         <v>3</v>
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="N119" t="n">
         <v>8.6</v>
@@ -9235,7 +9235,7 @@
         <v>7.23</v>
       </c>
       <c r="P119" t="n">
-        <v>2.9085</v>
+        <v>2.878</v>
       </c>
       <c r="Q119" t="n">
         <v>1</v>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="M120" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="N120" t="n">
         <v>7</v>
@@ -9309,7 +9309,7 @@
         <v>7.23</v>
       </c>
       <c r="P120" t="n">
-        <v>2.8715</v>
+        <v>2.8255</v>
       </c>
       <c r="Q120" t="n">
         <v>2</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="M121" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="N121" t="n">
         <v>5.13</v>
@@ -9383,7 +9383,7 @@
         <v>7.23</v>
       </c>
       <c r="P121" t="n">
-        <v>2.8105</v>
+        <v>2.758</v>
       </c>
       <c r="Q121" t="n">
         <v>3</v>
@@ -9445,10 +9445,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>9.32</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M122" t="n">
-        <v>9.369999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="N122" t="n">
         <v>10</v>
@@ -9457,7 +9457,7 @@
         <v>6.74</v>
       </c>
       <c r="P122" t="n">
-        <v>9.086499999999999</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>9.699999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M123" t="n">
-        <v>9.720000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="N123" t="n">
         <v>6.11</v>
@@ -9531,7 +9531,7 @@
         <v>6.74</v>
       </c>
       <c r="P123" t="n">
-        <v>8.545</v>
+        <v>8.354000000000001</v>
       </c>
       <c r="Q123" t="n">
         <v>2</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="M124" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -9605,7 +9605,7 @@
         <v>3.22</v>
       </c>
       <c r="P124" t="n">
-        <v>6.983</v>
+        <v>6.833999999999999</v>
       </c>
       <c r="Q124" t="n">
         <v>3</v>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="M125" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="N125" t="n">
         <v>7.59</v>
@@ -9679,7 +9679,7 @@
         <v>7.79</v>
       </c>
       <c r="P125" t="n">
-        <v>5.327999999999999</v>
+        <v>5.223999999999999</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="M126" t="n">
-        <v>4.42</v>
+        <v>4.26</v>
       </c>
       <c r="N126" t="n">
         <v>5.63</v>
@@ -9753,7 +9753,7 @@
         <v>7.79</v>
       </c>
       <c r="P126" t="n">
-        <v>5.1825</v>
+        <v>5.0725</v>
       </c>
       <c r="Q126" t="n">
         <v>2</v>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>4.85</v>
+        <v>4.66</v>
       </c>
       <c r="M127" t="n">
-        <v>4.8</v>
+        <v>4.63</v>
       </c>
       <c r="N127" t="n">
         <v>3.23</v>
@@ -9827,7 +9827,7 @@
         <v>6.82</v>
       </c>
       <c r="P127" t="n">
-        <v>4.803999999999999</v>
+        <v>4.687499999999999</v>
       </c>
       <c r="Q127" t="n">
         <v>3</v>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>9.289999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="M128" t="n">
-        <v>9.34</v>
+        <v>9.07</v>
       </c>
       <c r="N128" t="n">
         <v>6.11</v>
@@ -9901,7 +9901,7 @@
         <v>6.94</v>
       </c>
       <c r="P128" t="n">
-        <v>8.318999999999999</v>
+        <v>8.134500000000001</v>
       </c>
       <c r="Q128" t="n">
         <v>3</v>
@@ -9963,10 +9963,10 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>9.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M129" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N129" t="n">
         <v>8.6</v>
@@ -9975,7 +9975,7 @@
         <v>6.94</v>
       </c>
       <c r="P129" t="n">
-        <v>8.680999999999999</v>
+        <v>8.499499999999999</v>
       </c>
       <c r="Q129" t="n">
         <v>2</v>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>8.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M130" t="n">
-        <v>9.01</v>
+        <v>8.74</v>
       </c>
       <c r="N130" t="n">
         <v>10</v>
@@ -10049,7 +10049,7 @@
         <v>6.94</v>
       </c>
       <c r="P130" t="n">
-        <v>8.8705</v>
+        <v>8.692</v>
       </c>
       <c r="Q130" t="n">
         <v>1</v>
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M131" t="n">
-        <v>5.35</v>
+        <v>5.17</v>
       </c>
       <c r="N131" t="n">
         <v>8.6</v>
@@ -10123,7 +10123,7 @@
         <v>7.79</v>
       </c>
       <c r="P131" t="n">
-        <v>6.380999999999999</v>
+        <v>6.258</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>5.68</v>
+        <v>5.48</v>
       </c>
       <c r="M132" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
       <c r="N132" t="n">
         <v>7</v>
@@ -10197,7 +10197,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P132" t="n">
-        <v>6.2925</v>
+        <v>6.166</v>
       </c>
       <c r="Q132" t="n">
         <v>2</v>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>5.97</v>
+        <v>5.76</v>
       </c>
       <c r="M133" t="n">
-        <v>5.91</v>
+        <v>5.72</v>
       </c>
       <c r="N133" t="n">
         <v>5.13</v>
@@ -10271,7 +10271,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P133" t="n">
-        <v>6.103499999999999</v>
+        <v>5.973999999999999</v>
       </c>
       <c r="Q133" t="n">
         <v>3</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="M134" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>2.85</v>
       </c>
       <c r="P134" t="n">
-        <v>1.0155</v>
+        <v>0.9604999999999999</v>
       </c>
       <c r="Q134" t="n">
         <v>3</v>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
         <v>2.35</v>
@@ -10419,7 +10419,7 @@
         <v>6.14</v>
       </c>
       <c r="P135" t="n">
-        <v>1.417</v>
+        <v>1.391</v>
       </c>
       <c r="Q135" t="n">
         <v>2</v>
@@ -10555,10 +10555,10 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>6.58</v>
+        <v>6.35</v>
       </c>
       <c r="M137" t="n">
-        <v>6.62</v>
+        <v>6.41</v>
       </c>
       <c r="N137" t="n">
         <v>7.83</v>
@@ -10567,7 +10567,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="P137" t="n">
-        <v>7.173999999999999</v>
+        <v>7.0315</v>
       </c>
       <c r="Q137" t="n">
         <v>3</v>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>7</v>
+        <v>6.77</v>
       </c>
       <c r="M138" t="n">
-        <v>7.03</v>
+        <v>6.81</v>
       </c>
       <c r="N138" t="n">
         <v>10</v>
@@ -10641,7 +10641,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="P138" t="n">
-        <v>7.8775</v>
+        <v>7.7315</v>
       </c>
       <c r="Q138" t="n">
         <v>2</v>
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="M140" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="N140" t="n">
         <v>8.300000000000001</v>
@@ -10789,7 +10789,7 @@
         <v>9.09</v>
       </c>
       <c r="P140" t="n">
-        <v>6.1265</v>
+        <v>6.013</v>
       </c>
       <c r="Q140" t="n">
         <v>3</v>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M141" t="n">
-        <v>5.48</v>
+        <v>5.3</v>
       </c>
       <c r="N141" t="n">
         <v>8.300000000000001</v>
@@ -10863,7 +10863,7 @@
         <v>9.09</v>
       </c>
       <c r="P141" t="n">
-        <v>6.561500000000001</v>
+        <v>6.4385</v>
       </c>
       <c r="Q141" t="n">
         <v>1</v>
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>5.74</v>
+        <v>5.54</v>
       </c>
       <c r="M142" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="N142" t="n">
         <v>6.29</v>
@@ -10937,7 +10937,7 @@
         <v>9.09</v>
       </c>
       <c r="P142" t="n">
-        <v>6.377</v>
+        <v>6.2505</v>
       </c>
       <c r="Q142" t="n">
         <v>2</v>
@@ -10999,10 +10999,10 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>8.279999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="M143" t="n">
-        <v>8.27</v>
+        <v>8.02</v>
       </c>
       <c r="N143" t="n">
         <v>7.83</v>
@@ -11011,7 +11011,7 @@
         <v>9.44</v>
       </c>
       <c r="P143" t="n">
-        <v>8.360499999999998</v>
+        <v>8.194999999999999</v>
       </c>
       <c r="Q143" t="n">
         <v>3</v>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="M144" t="n">
-        <v>8.51</v>
+        <v>8.25</v>
       </c>
       <c r="N144" t="n">
         <v>9.32</v>
@@ -11085,7 +11085,7 @@
         <v>9.44</v>
       </c>
       <c r="P144" t="n">
-        <v>8.814499999999999</v>
+        <v>8.6425</v>
       </c>
       <c r="Q144" t="n">
         <v>2</v>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="M149" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N149" t="n">
         <v>6.11</v>
@@ -11455,7 +11455,7 @@
         <v>7.23</v>
       </c>
       <c r="P149" t="n">
-        <v>8.8065</v>
+        <v>8.6365</v>
       </c>
       <c r="Q149" t="n">
         <v>2</v>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>9.640000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="M150" t="n">
-        <v>9.59</v>
+        <v>9.31</v>
       </c>
       <c r="N150" t="n">
         <v>8.6</v>
@@ -11529,7 +11529,7 @@
         <v>7.23</v>
       </c>
       <c r="P150" t="n">
-        <v>9.052999999999999</v>
+        <v>8.865</v>
       </c>
       <c r="Q150" t="n">
         <v>1</v>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>9.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M151" t="n">
-        <v>9.029999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="N151" t="n">
         <v>8.6</v>
@@ -11603,7 +11603,7 @@
         <v>7.23</v>
       </c>
       <c r="P151" t="n">
-        <v>8.685999999999998</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="Q151" t="n">
         <v>3</v>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>10</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M153" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="N153" t="n">
         <v>10</v>
@@ -11751,7 +11751,7 @@
         <v>7.5</v>
       </c>
       <c r="P153" t="n">
-        <v>9.625</v>
+        <v>9.471</v>
       </c>
       <c r="Q153" t="n">
         <v>1</v>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>9.630000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="M154" t="n">
-        <v>9.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N154" t="n">
         <v>6.65</v>
@@ -11825,7 +11825,7 @@
         <v>7.5</v>
       </c>
       <c r="P154" t="n">
-        <v>8.696999999999999</v>
+        <v>8.509</v>
       </c>
       <c r="Q154" t="n">
         <v>3</v>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="M155" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="N155" t="n">
         <v>6.11</v>
@@ -11899,7 +11899,7 @@
         <v>7.5</v>
       </c>
       <c r="P155" t="n">
-        <v>4.4175</v>
+        <v>4.327</v>
       </c>
       <c r="Q155" t="n">
         <v>3</v>
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.89</v>
+        <v>3.73</v>
       </c>
       <c r="M156" t="n">
-        <v>4.01</v>
+        <v>3.86</v>
       </c>
       <c r="N156" t="n">
         <v>10</v>
@@ -11973,7 +11973,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P156" t="n">
-        <v>5.8005</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="Q156" t="n">
         <v>1</v>
@@ -12035,10 +12035,10 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.83</v>
+        <v>4.64</v>
       </c>
       <c r="M157" t="n">
-        <v>4.92</v>
+        <v>4.75</v>
       </c>
       <c r="N157" t="n">
         <v>5.13</v>
@@ -12047,7 +12047,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P157" t="n">
-        <v>5.427</v>
+        <v>5.310499999999999</v>
       </c>
       <c r="Q157" t="n">
         <v>2</v>
@@ -12183,10 +12183,10 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="M159" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="N159" t="n">
         <v>10</v>
@@ -12195,7 +12195,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="P159" t="n">
-        <v>4.250999999999999</v>
+        <v>4.1795</v>
       </c>
       <c r="Q159" t="n">
         <v>2</v>
@@ -12257,10 +12257,10 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="M160" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="N160" t="n">
         <v>7.59</v>
@@ -12269,7 +12269,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="P160" t="n">
-        <v>4.324</v>
+        <v>4.246</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -12331,10 +12331,10 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>7.24</v>
+        <v>7</v>
       </c>
       <c r="M161" t="n">
-        <v>7.17</v>
+        <v>6.95</v>
       </c>
       <c r="N161" t="n">
         <v>7.83</v>
@@ -12343,7 +12343,7 @@
         <v>8.51</v>
       </c>
       <c r="P161" t="n">
-        <v>7.523999999999999</v>
+        <v>7.375</v>
       </c>
       <c r="Q161" t="n">
         <v>2</v>
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>7.53</v>
+        <v>7.28</v>
       </c>
       <c r="M162" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="N162" t="n">
         <v>9.32</v>
@@ -12417,7 +12417,7 @@
         <v>8.51</v>
       </c>
       <c r="P162" t="n">
-        <v>8.007</v>
+        <v>7.8515</v>
       </c>
       <c r="Q162" t="n">
         <v>1</v>
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>7.88</v>
+        <v>7.62</v>
       </c>
       <c r="M163" t="n">
-        <v>7.8</v>
+        <v>7.57</v>
       </c>
       <c r="N163" t="n">
         <v>5.13</v>
@@ -12491,7 +12491,7 @@
         <v>8.51</v>
       </c>
       <c r="P163" t="n">
-        <v>7.3965</v>
+        <v>7.238</v>
       </c>
       <c r="Q163" t="n">
         <v>3</v>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>6.37</v>
+        <v>6.15</v>
       </c>
       <c r="M164" t="n">
-        <v>6.42</v>
+        <v>6.21</v>
       </c>
       <c r="N164" t="n">
         <v>5.13</v>
@@ -12565,7 +12565,7 @@
         <v>6.31</v>
       </c>
       <c r="P164" t="n">
-        <v>6.1305</v>
+        <v>5.991</v>
       </c>
       <c r="Q164" t="n">
         <v>2</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>5.74</v>
+        <v>5.54</v>
       </c>
       <c r="M165" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="N165" t="n">
         <v>8.6</v>
@@ -12639,7 +12639,7 @@
         <v>6.31</v>
       </c>
       <c r="P165" t="n">
-        <v>6.421999999999999</v>
+        <v>6.295499999999999</v>
       </c>
       <c r="Q165" t="n">
         <v>1</v>
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="M166" t="n">
-        <v>4.89</v>
+        <v>4.72</v>
       </c>
       <c r="N166" t="n">
         <v>7</v>
@@ -12713,7 +12713,7 @@
         <v>6.31</v>
       </c>
       <c r="P166" t="n">
-        <v>5.497999999999999</v>
+        <v>5.381500000000001</v>
       </c>
       <c r="Q166" t="n">
         <v>3</v>
@@ -12775,10 +12775,10 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>6.16</v>
+        <v>5.95</v>
       </c>
       <c r="M167" t="n">
-        <v>6.22</v>
+        <v>6.01</v>
       </c>
       <c r="N167" t="n">
         <v>6.11</v>
@@ -12787,7 +12787,7 @@
         <v>5.89</v>
       </c>
       <c r="P167" t="n">
-        <v>6.1305</v>
+        <v>5.994</v>
       </c>
       <c r="Q167" t="n">
         <v>2</v>
@@ -12849,10 +12849,10 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>5.31</v>
+        <v>5.11</v>
       </c>
       <c r="M168" t="n">
-        <v>5.39</v>
+        <v>5.2</v>
       </c>
       <c r="N168" t="n">
         <v>10</v>
@@ -12861,7 +12861,7 @@
         <v>5.89</v>
       </c>
       <c r="P168" t="n">
-        <v>6.363</v>
+        <v>6.236499999999999</v>
       </c>
       <c r="Q168" t="n">
         <v>1</v>
@@ -12923,10 +12923,10 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>4.07</v>
+        <v>3.91</v>
       </c>
       <c r="M169" t="n">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="N169" t="n">
         <v>5.13</v>
@@ -12935,7 +12935,7 @@
         <v>5.89</v>
       </c>
       <c r="P169" t="n">
-        <v>4.667</v>
+        <v>4.563</v>
       </c>
       <c r="Q169" t="n">
         <v>3</v>
@@ -12997,10 +12997,10 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>5.92</v>
+        <v>5.7</v>
       </c>
       <c r="M170" t="n">
-        <v>5.86</v>
+        <v>5.67</v>
       </c>
       <c r="N170" t="n">
         <v>8.6</v>
@@ -13009,10 +13009,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P170" t="n">
-        <v>6.776999999999999</v>
+        <v>6.644499999999999</v>
       </c>
       <c r="Q170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R170" t="n">
         <v>8.58</v>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>6.79</v>
+        <v>6.56</v>
       </c>
       <c r="M171" t="n">
-        <v>6.72</v>
+        <v>6.51</v>
       </c>
       <c r="N171" t="n">
         <v>1.53</v>
@@ -13083,7 +13083,7 @@
         <v>5.14</v>
       </c>
       <c r="P171" t="n">
-        <v>5.465999999999999</v>
+        <v>5.323499999999999</v>
       </c>
       <c r="Q171" t="n">
         <v>3</v>
@@ -13160,7 +13160,7 @@
         <v>6.7265</v>
       </c>
       <c r="Q172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -13219,10 +13219,10 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>6.94</v>
+        <v>6.7</v>
       </c>
       <c r="M173" t="n">
-        <v>6.87</v>
+        <v>6.65</v>
       </c>
       <c r="N173" t="n">
         <v>8.6</v>
@@ -13231,7 +13231,7 @@
         <v>8.51</v>
       </c>
       <c r="P173" t="n">
-        <v>7.482999999999999</v>
+        <v>7.334</v>
       </c>
       <c r="Q173" t="n">
         <v>1</v>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>7.6</v>
+        <v>7.35</v>
       </c>
       <c r="M174" t="n">
-        <v>7.53</v>
+        <v>7.29</v>
       </c>
       <c r="N174" t="n">
         <v>1.53</v>
@@ -13305,7 +13305,7 @@
         <v>5.37</v>
       </c>
       <c r="P174" t="n">
-        <v>6.027</v>
+        <v>5.867999999999999</v>
       </c>
       <c r="Q174" t="n">
         <v>3</v>
@@ -13441,10 +13441,10 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>6.41</v>
+        <v>6.18</v>
       </c>
       <c r="M176" t="n">
-        <v>6.67</v>
+        <v>6.46</v>
       </c>
       <c r="N176" t="n">
         <v>7.59</v>
@@ -13453,7 +13453,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="P176" t="n">
-        <v>7.121</v>
+        <v>6.978499999999999</v>
       </c>
       <c r="Q176" t="n">
         <v>3</v>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>6.82</v>
+        <v>6.59</v>
       </c>
       <c r="M177" t="n">
-        <v>7.05</v>
+        <v>6.83</v>
       </c>
       <c r="N177" t="n">
         <v>9.25</v>
@@ -13527,7 +13527,7 @@
         <v>9.33</v>
       </c>
       <c r="P177" t="n">
-        <v>7.763</v>
+        <v>7.616999999999999</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7.13</v>
+        <v>6.89</v>
       </c>
       <c r="M178" t="n">
-        <v>7.34</v>
+        <v>7.11</v>
       </c>
       <c r="N178" t="n">
         <v>6.65</v>
@@ -13601,7 +13601,7 @@
         <v>9.33</v>
       </c>
       <c r="P178" t="n">
-        <v>7.4375</v>
+        <v>7.285</v>
       </c>
       <c r="Q178" t="n">
         <v>2</v>
@@ -13663,10 +13663,10 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="M179" t="n">
-        <v>8.77</v>
+        <v>8.52</v>
       </c>
       <c r="N179" t="n">
         <v>6.11</v>
@@ -13675,7 +13675,7 @@
         <v>6.44</v>
       </c>
       <c r="P179" t="n">
-        <v>7.861499999999999</v>
+        <v>7.69</v>
       </c>
       <c r="Q179" t="n">
         <v>3</v>
@@ -13737,10 +13737,10 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8.44</v>
+        <v>8.17</v>
       </c>
       <c r="M180" t="n">
-        <v>8.56</v>
+        <v>8.31</v>
       </c>
       <c r="N180" t="n">
         <v>8.6</v>
@@ -13749,7 +13749,7 @@
         <v>6.44</v>
       </c>
       <c r="P180" t="n">
-        <v>8.213999999999999</v>
+        <v>8.045500000000001</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8.130000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="M181" t="n">
-        <v>8.27</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N181" t="n">
         <v>8.6</v>
@@ -13823,7 +13823,7 @@
         <v>6.44</v>
       </c>
       <c r="P181" t="n">
-        <v>8.019499999999999</v>
+        <v>7.8575</v>
       </c>
       <c r="Q181" t="n">
         <v>2</v>
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7.91</v>
+        <v>7.65</v>
       </c>
       <c r="M182" t="n">
-        <v>8.06</v>
+        <v>7.82</v>
       </c>
       <c r="N182" t="n">
         <v>7</v>
@@ -13897,7 +13897,7 @@
         <v>6.31</v>
       </c>
       <c r="P182" t="n">
-        <v>7.5405</v>
+        <v>7.378500000000001</v>
       </c>
       <c r="Q182" t="n">
         <v>2</v>
@@ -13959,10 +13959,10 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7.46</v>
+        <v>7.21</v>
       </c>
       <c r="M183" t="n">
-        <v>7.64</v>
+        <v>7.41</v>
       </c>
       <c r="N183" t="n">
         <v>10</v>
@@ -13971,7 +13971,7 @@
         <v>6.31</v>
       </c>
       <c r="P183" t="n">
-        <v>7.858499999999999</v>
+        <v>7.702999999999999</v>
       </c>
       <c r="Q183" t="n">
         <v>1</v>
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7.12</v>
+        <v>6.88</v>
       </c>
       <c r="M184" t="n">
-        <v>7.33</v>
+        <v>7.1</v>
       </c>
       <c r="N184" t="n">
         <v>7.83</v>
@@ -14045,7 +14045,7 @@
         <v>6.31</v>
       </c>
       <c r="P184" t="n">
-        <v>7.213999999999999</v>
+        <v>7.061499999999999</v>
       </c>
       <c r="Q184" t="n">
         <v>3</v>
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8.539999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="M185" t="n">
-        <v>8.529999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="N185" t="n">
         <v>7.83</v>
@@ -14119,7 +14119,7 @@
         <v>7.51</v>
       </c>
       <c r="P185" t="n">
-        <v>8.239999999999998</v>
+        <v>8.068</v>
       </c>
       <c r="Q185" t="n">
         <v>2</v>
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>8.23</v>
+        <v>7.97</v>
       </c>
       <c r="M186" t="n">
-        <v>8.220000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="N186" t="n">
         <v>10</v>
@@ -14193,7 +14193,7 @@
         <v>7.51</v>
       </c>
       <c r="P186" t="n">
-        <v>8.4725</v>
+        <v>8.310499999999999</v>
       </c>
       <c r="Q186" t="n">
         <v>1</v>
@@ -14255,10 +14255,10 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>7.71</v>
+        <v>7.46</v>
       </c>
       <c r="M187" t="n">
-        <v>7.72</v>
+        <v>7.48</v>
       </c>
       <c r="N187" t="n">
         <v>6.11</v>
@@ -14267,7 +14267,7 @@
         <v>7.51</v>
       </c>
       <c r="P187" t="n">
-        <v>7.3635</v>
+        <v>7.2045</v>
       </c>
       <c r="Q187" t="n">
         <v>3</v>
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="M188" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N188" t="n">
         <v>7</v>
@@ -14341,7 +14341,7 @@
         <v>7.32</v>
       </c>
       <c r="P188" t="n">
-        <v>8.998000000000001</v>
+        <v>8.846</v>
       </c>
       <c r="Q188" t="n">
         <v>2</v>
@@ -14403,10 +14403,10 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>9.85</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M189" t="n">
-        <v>9.869999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="N189" t="n">
         <v>9.32</v>
@@ -14415,7 +14415,7 @@
         <v>7.32</v>
       </c>
       <c r="P189" t="n">
-        <v>9.371500000000001</v>
+        <v>9.180000000000001</v>
       </c>
       <c r="Q189" t="n">
         <v>1</v>
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>9.57</v>
+        <v>9.27</v>
       </c>
       <c r="M190" t="n">
-        <v>9.6</v>
+        <v>9.32</v>
       </c>
       <c r="N190" t="n">
         <v>7.83</v>
@@ -14489,7 +14489,7 @@
         <v>7.32</v>
       </c>
       <c r="P190" t="n">
-        <v>8.895</v>
+        <v>8.706999999999999</v>
       </c>
       <c r="Q190" t="n">
         <v>3</v>
@@ -14551,10 +14551,10 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>6.24</v>
+        <v>6.02</v>
       </c>
       <c r="M191" t="n">
-        <v>6.29</v>
+        <v>6.09</v>
       </c>
       <c r="N191" t="n">
         <v>7.83</v>
@@ -14563,7 +14563,7 @@
         <v>8.49</v>
       </c>
       <c r="P191" t="n">
-        <v>6.912999999999999</v>
+        <v>6.777</v>
       </c>
       <c r="Q191" t="n">
         <v>3</v>
@@ -14773,10 +14773,10 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>9.92</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M194" t="n">
-        <v>9.82</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N194" t="n">
         <v>6.11</v>
@@ -14785,7 +14785,7 @@
         <v>7.2</v>
       </c>
       <c r="P194" t="n">
-        <v>8.715</v>
+        <v>8.524000000000001</v>
       </c>
       <c r="Q194" t="n">
         <v>3</v>
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>9.449999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="M195" t="n">
-        <v>9.359999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="N195" t="n">
         <v>8.6</v>
@@ -14859,7 +14859,7 @@
         <v>7.2</v>
       </c>
       <c r="P195" t="n">
-        <v>8.910999999999998</v>
+        <v>8.7265</v>
       </c>
       <c r="Q195" t="n">
         <v>1</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>8.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M196" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N196" t="n">
         <v>9.32</v>
@@ -14933,7 +14933,7 @@
         <v>7.2</v>
       </c>
       <c r="P196" t="n">
-        <v>8.753</v>
+        <v>8.577999999999999</v>
       </c>
       <c r="Q196" t="n">
         <v>2</v>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M197" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="N197" t="n">
         <v>4.5</v>
@@ -15007,7 +15007,7 @@
         <v>6.8</v>
       </c>
       <c r="P197" t="n">
-        <v>3.124</v>
+        <v>3.056</v>
       </c>
       <c r="Q197" t="n">
         <v>3</v>
@@ -15069,10 +15069,10 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="M198" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="N198" t="n">
         <v>9.25</v>
@@ -15081,7 +15081,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P198" t="n">
-        <v>4.918</v>
+        <v>4.8305</v>
       </c>
       <c r="Q198" t="n">
         <v>2</v>
@@ -15143,10 +15143,10 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="M199" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="N199" t="n">
         <v>6.65</v>
@@ -15155,7 +15155,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P199" t="n">
-        <v>5.0375</v>
+        <v>4.94</v>
       </c>
       <c r="Q199" t="n">
         <v>1</v>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>6.95</v>
+        <v>6.72</v>
       </c>
       <c r="M200" t="n">
-        <v>6.98</v>
+        <v>6.76</v>
       </c>
       <c r="N200" t="n">
         <v>4.06</v>
@@ -15229,7 +15229,7 @@
         <v>6.03</v>
       </c>
       <c r="P200" t="n">
-        <v>6.2445</v>
+        <v>6.0985</v>
       </c>
       <c r="Q200" t="n">
         <v>2</v>
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>6.35</v>
+        <v>6.13</v>
       </c>
       <c r="M201" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="N201" t="n">
         <v>8.6</v>
@@ -15303,7 +15303,7 @@
         <v>6.03</v>
       </c>
       <c r="P201" t="n">
-        <v>6.769499999999999</v>
+        <v>6.629999999999999</v>
       </c>
       <c r="Q201" t="n">
         <v>1</v>
@@ -15365,10 +15365,10 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="M202" t="n">
-        <v>5.59</v>
+        <v>5.4</v>
       </c>
       <c r="N202" t="n">
         <v>6.11</v>
@@ -15377,7 +15377,7 @@
         <v>6.03</v>
       </c>
       <c r="P202" t="n">
-        <v>5.736</v>
+        <v>5.6095</v>
       </c>
       <c r="Q202" t="n">
         <v>3</v>
@@ -15439,10 +15439,10 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="M203" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="N203" t="n">
         <v>8.6</v>
@@ -15451,7 +15451,7 @@
         <v>7.59</v>
       </c>
       <c r="P203" t="n">
-        <v>3.0045</v>
+        <v>2.959</v>
       </c>
       <c r="Q203" t="n">
         <v>3</v>
@@ -15513,10 +15513,10 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="M204" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="N204" t="n">
         <v>8.6</v>
@@ -15525,7 +15525,7 @@
         <v>7.59</v>
       </c>
       <c r="P204" t="n">
-        <v>3.754</v>
+        <v>3.6925</v>
       </c>
       <c r="Q204" t="n">
         <v>2</v>
@@ -15587,10 +15587,10 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="M205" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="N205" t="n">
         <v>5.13</v>
@@ -15599,7 +15599,7 @@
         <v>7.91</v>
       </c>
       <c r="P205" t="n">
-        <v>3.858</v>
+        <v>3.777</v>
       </c>
       <c r="Q205" t="n">
         <v>1</v>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>9.75</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M209" t="n">
-        <v>9.699999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="N209" t="n">
         <v>7</v>
@@ -15895,7 +15895,7 @@
         <v>7.04</v>
       </c>
       <c r="P209" t="n">
-        <v>8.776</v>
+        <v>8.588000000000001</v>
       </c>
       <c r="Q209" t="n">
         <v>3</v>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M210" t="n">
-        <v>9.550000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="N210" t="n">
         <v>9.32</v>
@@ -15969,7 +15969,7 @@
         <v>7.04</v>
       </c>
       <c r="P210" t="n">
-        <v>9.142500000000002</v>
+        <v>8.954499999999999</v>
       </c>
       <c r="Q210" t="n">
         <v>1</v>
@@ -16031,10 +16031,10 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>9.449999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="M211" t="n">
-        <v>9.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N211" t="n">
         <v>8.6</v>
@@ -16043,7 +16043,7 @@
         <v>7.04</v>
       </c>
       <c r="P211" t="n">
-        <v>8.901</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="Q211" t="n">
         <v>2</v>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="M212" t="n">
-        <v>7.89</v>
+        <v>7.66</v>
       </c>
       <c r="N212" t="n">
         <v>1.38</v>
@@ -16117,7 +16117,7 @@
         <v>7.23</v>
       </c>
       <c r="P212" t="n">
-        <v>6.441</v>
+        <v>6.2825</v>
       </c>
       <c r="Q212" t="n">
         <v>3</v>
@@ -16179,10 +16179,10 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>7.43</v>
+        <v>7.19</v>
       </c>
       <c r="M213" t="n">
-        <v>7.62</v>
+        <v>7.39</v>
       </c>
       <c r="N213" t="n">
         <v>5.92</v>
@@ -16191,7 +16191,7 @@
         <v>7.23</v>
       </c>
       <c r="P213" t="n">
-        <v>7.164499999999999</v>
+        <v>7.012</v>
       </c>
       <c r="Q213" t="n">
         <v>2</v>
@@ -16253,10 +16253,10 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="M214" t="n">
-        <v>7.35</v>
+        <v>7.12</v>
       </c>
       <c r="N214" t="n">
         <v>9.109999999999999</v>
@@ -16265,7 +16265,7 @@
         <v>7.23</v>
       </c>
       <c r="P214" t="n">
-        <v>7.621</v>
+        <v>7.4685</v>
       </c>
       <c r="Q214" t="n">
         <v>1</v>
@@ -16478,7 +16478,7 @@
         <v>10</v>
       </c>
       <c r="M217" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="N217" t="n">
         <v>9.25</v>
@@ -16487,7 +16487,7 @@
         <v>7.76</v>
       </c>
       <c r="P217" t="n">
-        <v>9.513999999999999</v>
+        <v>9.510499999999999</v>
       </c>
       <c r="Q217" t="n">
         <v>1</v>
@@ -16919,10 +16919,10 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="M223" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N223" t="n">
         <v>10</v>
@@ -16931,7 +16931,7 @@
         <v>8.16</v>
       </c>
       <c r="P223" t="n">
-        <v>9.724</v>
+        <v>9.554</v>
       </c>
       <c r="Q223" t="n">
         <v>1</v>
@@ -17215,10 +17215,10 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>8.57</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M227" t="n">
-        <v>8.49</v>
+        <v>8.23</v>
       </c>
       <c r="N227" t="n">
         <v>7</v>
@@ -17227,7 +17227,7 @@
         <v>5.48</v>
       </c>
       <c r="P227" t="n">
-        <v>7.764500000000001</v>
+        <v>7.5925</v>
       </c>
       <c r="Q227" t="n">
         <v>3</v>
@@ -17659,10 +17659,10 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>7.18</v>
+        <v>6.94</v>
       </c>
       <c r="M233" t="n">
-        <v>7.2</v>
+        <v>6.98</v>
       </c>
       <c r="N233" t="n">
         <v>8.460000000000001</v>
@@ -17671,7 +17671,7 @@
         <v>6.37</v>
       </c>
       <c r="P233" t="n">
-        <v>7.321499999999999</v>
+        <v>7.1725</v>
       </c>
       <c r="Q233" t="n">
         <v>3</v>
@@ -17881,10 +17881,10 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>9.119999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="M236" t="n">
-        <v>9.08</v>
+        <v>8.82</v>
       </c>
       <c r="N236" t="n">
         <v>7</v>
@@ -17893,7 +17893,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P236" t="n">
-        <v>8.695500000000001</v>
+        <v>8.5175</v>
       </c>
       <c r="Q236" t="n">
         <v>3</v>
@@ -17955,10 +17955,10 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="M237" t="n">
-        <v>9.25</v>
+        <v>8.98</v>
       </c>
       <c r="N237" t="n">
         <v>10</v>
@@ -17967,7 +17967,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P237" t="n">
-        <v>9.406000000000001</v>
+        <v>9.224500000000001</v>
       </c>
       <c r="Q237" t="n">
         <v>1</v>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>8.199999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="M239" t="n">
-        <v>8.119999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="N239" t="n">
         <v>10</v>
@@ -18115,7 +18115,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="P239" t="n">
-        <v>8.631</v>
+        <v>8.4625</v>
       </c>
       <c r="Q239" t="n">
         <v>1</v>
@@ -18177,10 +18177,10 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="M240" t="n">
-        <v>8.44</v>
+        <v>8.18</v>
       </c>
       <c r="N240" t="n">
         <v>7</v>
@@ -18189,7 +18189,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="P240" t="n">
-        <v>8.239000000000001</v>
+        <v>8.067</v>
       </c>
       <c r="Q240" t="n">
         <v>2</v>
@@ -18325,10 +18325,10 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>8.960000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="M242" t="n">
-        <v>8.93</v>
+        <v>8.67</v>
       </c>
       <c r="N242" t="n">
         <v>8.6</v>
@@ -18337,7 +18337,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="P242" t="n">
-        <v>8.826499999999999</v>
+        <v>8.651499999999999</v>
       </c>
       <c r="Q242" t="n">
         <v>2</v>
@@ -18399,10 +18399,10 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>9.18</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M243" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N243" t="n">
         <v>9.32</v>
@@ -18411,7 +18411,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="P243" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9285</v>
       </c>
       <c r="Q243" t="n">
         <v>1</v>
@@ -18547,10 +18547,10 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>6.27</v>
+        <v>6.05</v>
       </c>
       <c r="M245" t="n">
-        <v>6.21</v>
+        <v>6.01</v>
       </c>
       <c r="N245" t="n">
         <v>9.18</v>
@@ -18559,10 +18559,10 @@
         <v>8.98</v>
       </c>
       <c r="P245" t="n">
-        <v>7.237499999999999</v>
+        <v>7.1015</v>
       </c>
       <c r="Q245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R245" t="n">
         <v>8.050000000000001</v>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>6.81</v>
+        <v>6.58</v>
       </c>
       <c r="M246" t="n">
-        <v>6.74</v>
+        <v>6.53</v>
       </c>
       <c r="N246" t="n">
         <v>5.13</v>
@@ -18633,7 +18633,7 @@
         <v>8.98</v>
       </c>
       <c r="P246" t="n">
-        <v>6.774999999999999</v>
+        <v>6.6325</v>
       </c>
       <c r="Q246" t="n">
         <v>3</v>
@@ -18710,7 +18710,7 @@
         <v>7.171</v>
       </c>
       <c r="Q247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -18769,10 +18769,10 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>6.35</v>
+        <v>6.13</v>
       </c>
       <c r="M248" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="N248" t="n">
         <v>6.65</v>
@@ -18781,7 +18781,7 @@
         <v>8.44</v>
       </c>
       <c r="P248" t="n">
-        <v>6.741</v>
+        <v>6.6015</v>
       </c>
       <c r="Q248" t="n">
         <v>3</v>
@@ -18843,10 +18843,10 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>6.64</v>
+        <v>6.42</v>
       </c>
       <c r="M249" t="n">
-        <v>6.68</v>
+        <v>6.47</v>
       </c>
       <c r="N249" t="n">
         <v>10</v>
@@ -18855,7 +18855,7 @@
         <v>8.44</v>
       </c>
       <c r="P249" t="n">
-        <v>7.595999999999999</v>
+        <v>7.4565</v>
       </c>
       <c r="Q249" t="n">
         <v>1</v>
@@ -18917,10 +18917,10 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>6.94</v>
+        <v>6.7</v>
       </c>
       <c r="M250" t="n">
-        <v>6.97</v>
+        <v>6.75</v>
       </c>
       <c r="N250" t="n">
         <v>6.65</v>
@@ -18929,7 +18929,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>7.2315</v>
+        <v>7.0825</v>
       </c>
       <c r="Q250" t="n">
         <v>2</v>
@@ -18991,10 +18991,10 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>8.09</v>
+        <v>7.83</v>
       </c>
       <c r="M251" t="n">
-        <v>8.01</v>
+        <v>7.77</v>
       </c>
       <c r="N251" t="n">
         <v>8.6</v>
@@ -19003,7 +19003,7 @@
         <v>7.72</v>
       </c>
       <c r="P251" t="n">
-        <v>8.108499999999999</v>
+        <v>7.946499999999999</v>
       </c>
       <c r="Q251" t="n">
         <v>1</v>
@@ -19065,10 +19065,10 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="M252" t="n">
-        <v>8.18</v>
+        <v>7.94</v>
       </c>
       <c r="N252" t="n">
         <v>6.11</v>
@@ -19077,7 +19077,7 @@
         <v>8.44</v>
       </c>
       <c r="P252" t="n">
-        <v>7.832</v>
+        <v>7.667000000000001</v>
       </c>
       <c r="Q252" t="n">
         <v>2</v>
@@ -19139,10 +19139,10 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>8.44</v>
+        <v>8.17</v>
       </c>
       <c r="M253" t="n">
-        <v>8.359999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N253" t="n">
         <v>2.86</v>
@@ -19151,7 +19151,7 @@
         <v>6.29</v>
       </c>
       <c r="P253" t="n">
-        <v>6.9735</v>
+        <v>6.805000000000001</v>
       </c>
       <c r="Q253" t="n">
         <v>3</v>
@@ -19213,10 +19213,10 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>3.84</v>
+        <v>3.67</v>
       </c>
       <c r="M254" t="n">
-        <v>3.96</v>
+        <v>3.81</v>
       </c>
       <c r="N254" t="n">
         <v>7.34</v>
@@ -19225,7 +19225,7 @@
         <v>8.08</v>
       </c>
       <c r="P254" t="n">
-        <v>5.218</v>
+        <v>5.1145</v>
       </c>
       <c r="Q254" t="n">
         <v>3</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="M255" t="n">
-        <v>4.68</v>
+        <v>4.52</v>
       </c>
       <c r="N255" t="n">
         <v>9.18</v>
@@ -19299,7 +19299,7 @@
         <v>8.08</v>
       </c>
       <c r="P255" t="n">
-        <v>6.06</v>
+        <v>5.95</v>
       </c>
       <c r="Q255" t="n">
         <v>1</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>5.33</v>
+        <v>5.13</v>
       </c>
       <c r="M256" t="n">
-        <v>5.41</v>
+        <v>5.22</v>
       </c>
       <c r="N256" t="n">
         <v>5.13</v>
@@ -19373,7 +19373,7 @@
         <v>8.41</v>
       </c>
       <c r="P256" t="n">
-        <v>5.779999999999999</v>
+        <v>5.653499999999999</v>
       </c>
       <c r="Q256" t="n">
         <v>2</v>
@@ -19435,10 +19435,10 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>8.470000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M257" t="n">
-        <v>8.390000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N257" t="n">
         <v>2.86</v>
@@ -19447,7 +19447,7 @@
         <v>6.45</v>
       </c>
       <c r="P257" t="n">
-        <v>7.017</v>
+        <v>6.8485</v>
       </c>
       <c r="Q257" t="n">
         <v>3</v>
@@ -19509,10 +19509,10 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>7.9</v>
+        <v>7.64</v>
       </c>
       <c r="M258" t="n">
-        <v>7.82</v>
+        <v>7.59</v>
       </c>
       <c r="N258" t="n">
         <v>7</v>
@@ -19521,7 +19521,7 @@
         <v>6.48</v>
       </c>
       <c r="P258" t="n">
-        <v>7.479000000000001</v>
+        <v>7.320499999999999</v>
       </c>
       <c r="Q258" t="n">
         <v>2</v>
@@ -19583,10 +19583,10 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>7.48</v>
+        <v>7.23</v>
       </c>
       <c r="M259" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="N259" t="n">
         <v>9.32</v>
@@ -19595,7 +19595,7 @@
         <v>6.48</v>
       </c>
       <c r="P259" t="n">
-        <v>7.67</v>
+        <v>7.518000000000001</v>
       </c>
       <c r="Q259" t="n">
         <v>1</v>
@@ -19879,10 +19879,10 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>8.43</v>
+        <v>8.16</v>
       </c>
       <c r="M263" t="n">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
@@ -19891,7 +19891,7 @@
         <v>2.91</v>
       </c>
       <c r="P263" t="n">
-        <v>5.887999999999999</v>
+        <v>5.719499999999999</v>
       </c>
       <c r="Q263" t="n">
         <v>3</v>
@@ -19953,10 +19953,10 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>8.119999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="M264" t="n">
-        <v>8.039999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="N264" t="n">
         <v>4.06</v>
@@ -19965,7 +19965,7 @@
         <v>6.24</v>
       </c>
       <c r="P264" t="n">
-        <v>6.997999999999999</v>
+        <v>6.836</v>
       </c>
       <c r="Q264" t="n">
         <v>2</v>
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>7.81</v>
+        <v>7.55</v>
       </c>
       <c r="M265" t="n">
-        <v>7.73</v>
+        <v>7.49</v>
       </c>
       <c r="N265" t="n">
         <v>7</v>
@@ -20039,7 +20039,7 @@
         <v>6.24</v>
       </c>
       <c r="P265" t="n">
-        <v>7.3845</v>
+        <v>7.2225</v>
       </c>
       <c r="Q265" t="n">
         <v>1</v>
@@ -20101,10 +20101,10 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>6.24</v>
+        <v>6.02</v>
       </c>
       <c r="M266" t="n">
-        <v>6.29</v>
+        <v>6.08</v>
       </c>
       <c r="N266" t="n">
         <v>7.83</v>
@@ -20113,7 +20113,7 @@
         <v>8.44</v>
       </c>
       <c r="P266" t="n">
-        <v>6.905499999999999</v>
+        <v>6.765999999999999</v>
       </c>
       <c r="Q266" t="n">
         <v>3</v>
@@ -20175,10 +20175,10 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>6.52</v>
+        <v>6.29</v>
       </c>
       <c r="M267" t="n">
-        <v>6.56</v>
+        <v>6.35</v>
       </c>
       <c r="N267" t="n">
         <v>10</v>
@@ -20187,7 +20187,7 @@
         <v>8.44</v>
       </c>
       <c r="P267" t="n">
-        <v>7.518</v>
+        <v>7.3755</v>
       </c>
       <c r="Q267" t="n">
         <v>1</v>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>6.8</v>
+        <v>6.57</v>
       </c>
       <c r="M268" t="n">
-        <v>6.84</v>
+        <v>6.62</v>
       </c>
       <c r="N268" t="n">
         <v>7.83</v>
@@ -20261,7 +20261,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="P268" t="n">
-        <v>7.316999999999999</v>
+        <v>7.171</v>
       </c>
       <c r="Q268" t="n">
         <v>2</v>
@@ -20323,10 +20323,10 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>8.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M269" t="n">
-        <v>8.74</v>
+        <v>8.48</v>
       </c>
       <c r="N269" t="n">
         <v>0</v>
@@ -20335,7 +20335,7 @@
         <v>2.85</v>
       </c>
       <c r="P269" t="n">
-        <v>6.1355</v>
+        <v>5.9605</v>
       </c>
       <c r="Q269" t="n">
         <v>3</v>
@@ -20397,10 +20397,10 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>8.5</v>
+        <v>8.23</v>
       </c>
       <c r="M270" t="n">
-        <v>8.42</v>
+        <v>8.17</v>
       </c>
       <c r="N270" t="n">
         <v>4.06</v>
@@ -20409,7 +20409,7 @@
         <v>6.14</v>
       </c>
       <c r="P270" t="n">
-        <v>7.23</v>
+        <v>7.061500000000001</v>
       </c>
       <c r="Q270" t="n">
         <v>2</v>
@@ -20471,10 +20471,10 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>8.17</v>
+        <v>7.91</v>
       </c>
       <c r="M271" t="n">
-        <v>8.09</v>
+        <v>7.85</v>
       </c>
       <c r="N271" t="n">
         <v>7</v>
@@ -20483,7 +20483,7 @@
         <v>6.14</v>
       </c>
       <c r="P271" t="n">
-        <v>7.6035</v>
+        <v>7.4415</v>
       </c>
       <c r="Q271" t="n">
         <v>1</v>
@@ -20545,10 +20545,10 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="M272" t="n">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="N272" t="n">
         <v>10</v>
@@ -20557,7 +20557,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="P272" t="n">
-        <v>5.465</v>
+        <v>5.3675</v>
       </c>
       <c r="Q272" t="n">
         <v>1</v>
@@ -20619,10 +20619,10 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="M273" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="N273" t="n">
         <v>7.59</v>
@@ -20631,7 +20631,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="P273" t="n">
-        <v>5.326999999999999</v>
+        <v>5.2265</v>
       </c>
       <c r="Q273" t="n">
         <v>2</v>
@@ -20693,10 +20693,10 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>4.48</v>
+        <v>4.31</v>
       </c>
       <c r="M274" t="n">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="N274" t="n">
         <v>4.5</v>
@@ -20705,7 +20705,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="P274" t="n">
-        <v>5.0565</v>
+        <v>4.946</v>
       </c>
       <c r="Q274" t="n">
         <v>3</v>
@@ -20767,10 +20767,10 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>8.859999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="M275" t="n">
-        <v>8.83</v>
+        <v>8.57</v>
       </c>
       <c r="N275" t="n">
         <v>5.13</v>
@@ -20779,7 +20779,7 @@
         <v>6.37</v>
       </c>
       <c r="P275" t="n">
-        <v>7.73</v>
+        <v>7.554999999999999</v>
       </c>
       <c r="Q275" t="n">
         <v>3</v>
@@ -20841,10 +20841,10 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>8.51</v>
+        <v>8.24</v>
       </c>
       <c r="M276" t="n">
-        <v>8.49</v>
+        <v>8.24</v>
       </c>
       <c r="N276" t="n">
         <v>7.83</v>
@@ -20853,7 +20853,7 @@
         <v>6.37</v>
       </c>
       <c r="P276" t="n">
-        <v>8.045999999999999</v>
+        <v>7.8775</v>
       </c>
       <c r="Q276" t="n">
         <v>2</v>
@@ -20915,10 +20915,10 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>8.16</v>
+        <v>7.9</v>
       </c>
       <c r="M277" t="n">
-        <v>8.15</v>
+        <v>7.91</v>
       </c>
       <c r="N277" t="n">
         <v>10</v>
@@ -20927,7 +20927,7 @@
         <v>6.37</v>
       </c>
       <c r="P277" t="n">
-        <v>8.256</v>
+        <v>8.094000000000001</v>
       </c>
       <c r="Q277" t="n">
         <v>1</v>
@@ -20989,10 +20989,10 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>6.27</v>
+        <v>6.05</v>
       </c>
       <c r="M278" t="n">
-        <v>6.32</v>
+        <v>6.11</v>
       </c>
       <c r="N278" t="n">
         <v>1.81</v>
@@ -21001,7 +21001,7 @@
         <v>5.16</v>
       </c>
       <c r="P278" t="n">
-        <v>5.229</v>
+        <v>5.0895</v>
       </c>
       <c r="Q278" t="n">
         <v>3</v>
@@ -21063,10 +21063,10 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="M279" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="N279" t="n">
         <v>5.63</v>
@@ -21075,7 +21075,7 @@
         <v>6.17</v>
       </c>
       <c r="P279" t="n">
-        <v>5.81</v>
+        <v>5.6805</v>
       </c>
       <c r="Q279" t="n">
         <v>2</v>
@@ -21137,10 +21137,10 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>5.22</v>
+        <v>5.03</v>
       </c>
       <c r="M280" t="n">
-        <v>5.3</v>
+        <v>5.12</v>
       </c>
       <c r="N280" t="n">
         <v>8.460000000000001</v>
@@ -21149,7 +21149,7 @@
         <v>6.17</v>
       </c>
       <c r="P280" t="n">
-        <v>6.038499999999999</v>
+        <v>5.9185</v>
       </c>
       <c r="Q280" t="n">
         <v>1</v>
@@ -21211,10 +21211,10 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>8.42</v>
+        <v>8.15</v>
       </c>
       <c r="M281" t="n">
-        <v>8.34</v>
+        <v>8.09</v>
       </c>
       <c r="N281" t="n">
         <v>0</v>
@@ -21223,7 +21223,7 @@
         <v>1.51</v>
       </c>
       <c r="P281" t="n">
-        <v>5.671499999999999</v>
+        <v>5.502999999999999</v>
       </c>
       <c r="Q281" t="n">
         <v>3</v>
@@ -21285,10 +21285,10 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>8.109999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="M282" t="n">
-        <v>8.029999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="N282" t="n">
         <v>1.53</v>
@@ -21297,7 +21297,7 @@
         <v>3.96</v>
       </c>
       <c r="P282" t="n">
-        <v>6.1435</v>
+        <v>5.9815</v>
       </c>
       <c r="Q282" t="n">
         <v>2</v>
@@ -21359,10 +21359,10 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="M283" t="n">
-        <v>7.73</v>
+        <v>7.49</v>
       </c>
       <c r="N283" t="n">
         <v>5.13</v>
@@ -21371,7 +21371,7 @@
         <v>6.03</v>
       </c>
       <c r="P283" t="n">
-        <v>6.975999999999999</v>
+        <v>6.816999999999999</v>
       </c>
       <c r="Q283" t="n">
         <v>1</v>
@@ -21433,10 +21433,10 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>9.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M284" t="n">
-        <v>9.029999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="N284" t="n">
         <v>5.13</v>
@@ -21445,7 +21445,7 @@
         <v>6.44</v>
       </c>
       <c r="P284" t="n">
-        <v>7.873499999999999</v>
+        <v>7.6955</v>
       </c>
       <c r="Q284" t="n">
         <v>3</v>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>8.73</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M285" t="n">
-        <v>8.699999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="N285" t="n">
         <v>7.83</v>
@@ -21519,7 +21519,7 @@
         <v>6.44</v>
       </c>
       <c r="P285" t="n">
-        <v>8.196</v>
+        <v>8.020999999999999</v>
       </c>
       <c r="Q285" t="n">
         <v>2</v>
@@ -21581,10 +21581,10 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>8.390000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M286" t="n">
-        <v>8.369999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N286" t="n">
         <v>10</v>
@@ -21593,7 +21593,7 @@
         <v>6.44</v>
       </c>
       <c r="P286" t="n">
-        <v>8.4125</v>
+        <v>8.243999999999998</v>
       </c>
       <c r="Q286" t="n">
         <v>1</v>
@@ -21655,10 +21655,10 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>8.789999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="M287" t="n">
-        <v>8.880000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N287" t="n">
         <v>0</v>
@@ -21667,7 +21667,7 @@
         <v>3.08</v>
       </c>
       <c r="P287" t="n">
-        <v>6.206999999999999</v>
+        <v>6.031999999999999</v>
       </c>
       <c r="Q287" t="n">
         <v>3</v>
@@ -21729,10 +21729,10 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>8.539999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="M288" t="n">
-        <v>8.65</v>
+        <v>8.4</v>
       </c>
       <c r="N288" t="n">
         <v>4.06</v>
@@ -21741,7 +21741,7 @@
         <v>6.51</v>
       </c>
       <c r="P288" t="n">
-        <v>7.377999999999999</v>
+        <v>7.209499999999999</v>
       </c>
       <c r="Q288" t="n">
         <v>2</v>
@@ -21803,10 +21803,10 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>8.289999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M289" t="n">
-        <v>8.42</v>
+        <v>8.17</v>
       </c>
       <c r="N289" t="n">
         <v>7</v>
@@ -21815,7 +21815,7 @@
         <v>6.51</v>
       </c>
       <c r="P289" t="n">
-        <v>7.810499999999999</v>
+        <v>7.645</v>
       </c>
       <c r="Q289" t="n">
         <v>1</v>
@@ -21877,10 +21877,10 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="M290" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="N290" t="n">
         <v>2.86</v>
@@ -21889,7 +21889,7 @@
         <v>4.92</v>
       </c>
       <c r="P290" t="n">
-        <v>1.5265</v>
+        <v>1.496</v>
       </c>
       <c r="Q290" t="n">
         <v>3</v>
@@ -22099,10 +22099,10 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>8.859999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="M293" t="n">
-        <v>8.77</v>
+        <v>8.51</v>
       </c>
       <c r="N293" t="n">
         <v>0</v>
@@ -22111,7 +22111,7 @@
         <v>2.91</v>
       </c>
       <c r="P293" t="n">
-        <v>6.163999999999999</v>
+        <v>5.986</v>
       </c>
       <c r="Q293" t="n">
         <v>3</v>
@@ -22173,10 +22173,10 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="M294" t="n">
-        <v>8.44</v>
+        <v>8.19</v>
       </c>
       <c r="N294" t="n">
         <v>4.06</v>
@@ -22185,7 +22185,7 @@
         <v>6.24</v>
       </c>
       <c r="P294" t="n">
-        <v>7.258</v>
+        <v>7.0895</v>
       </c>
       <c r="Q294" t="n">
         <v>2</v>
@@ -22247,10 +22247,10 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>8.19</v>
+        <v>7.93</v>
       </c>
       <c r="M295" t="n">
-        <v>8.109999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="N295" t="n">
         <v>7</v>
@@ -22259,7 +22259,7 @@
         <v>6.24</v>
       </c>
       <c r="P295" t="n">
-        <v>7.6315</v>
+        <v>7.4695</v>
       </c>
       <c r="Q295" t="n">
         <v>1</v>
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="M299" t="n">
-        <v>6.04</v>
+        <v>5.84</v>
       </c>
       <c r="N299" t="n">
         <v>7.83</v>
@@ -22555,7 +22555,7 @@
         <v>8.44</v>
       </c>
       <c r="P299" t="n">
-        <v>6.74</v>
+        <v>6.604</v>
       </c>
       <c r="Q299" t="n">
         <v>3</v>
@@ -22617,10 +22617,10 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>6.29</v>
+        <v>6.07</v>
       </c>
       <c r="M300" t="n">
-        <v>6.34</v>
+        <v>6.14</v>
       </c>
       <c r="N300" t="n">
         <v>10</v>
@@ -22629,7 +22629,7 @@
         <v>8.44</v>
       </c>
       <c r="P300" t="n">
-        <v>7.372</v>
+        <v>7.236</v>
       </c>
       <c r="Q300" t="n">
         <v>1</v>
@@ -22691,10 +22691,10 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="M301" t="n">
-        <v>6.64</v>
+        <v>6.43</v>
       </c>
       <c r="N301" t="n">
         <v>7.83</v>
@@ -22703,7 +22703,7 @@
         <v>8.44</v>
       </c>
       <c r="P301" t="n">
-        <v>7.135999999999999</v>
+        <v>6.996499999999999</v>
       </c>
       <c r="Q301" t="n">
         <v>2</v>
@@ -22765,10 +22765,10 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>7.46</v>
+        <v>7.21</v>
       </c>
       <c r="M302" t="n">
-        <v>7.38</v>
+        <v>7.16</v>
       </c>
       <c r="N302" t="n">
         <v>8.6</v>
@@ -22777,7 +22777,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P302" t="n">
-        <v>7.770999999999999</v>
+        <v>7.618999999999999</v>
       </c>
       <c r="Q302" t="n">
         <v>1</v>
@@ -22839,10 +22839,10 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>7.71</v>
+        <v>7.46</v>
       </c>
       <c r="M303" t="n">
-        <v>7.64</v>
+        <v>7.4</v>
       </c>
       <c r="N303" t="n">
         <v>6.11</v>
@@ -22851,7 +22851,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="P303" t="n">
-        <v>7.439</v>
+        <v>7.279999999999999</v>
       </c>
       <c r="Q303" t="n">
         <v>2</v>
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>7.97</v>
+        <v>7.71</v>
       </c>
       <c r="M304" t="n">
-        <v>7.89</v>
+        <v>7.65</v>
       </c>
       <c r="N304" t="n">
         <v>2.86</v>
@@ -22925,7 +22925,7 @@
         <v>6.37</v>
       </c>
       <c r="P304" t="n">
-        <v>6.68</v>
+        <v>6.517999999999999</v>
       </c>
       <c r="Q304" t="n">
         <v>3</v>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>6.57</v>
+        <v>6.35</v>
       </c>
       <c r="M305" t="n">
-        <v>6.51</v>
+        <v>6.3</v>
       </c>
       <c r="N305" t="n">
         <v>0</v>
@@ -22999,7 +22999,7 @@
         <v>2.54</v>
       </c>
       <c r="P305" t="n">
-        <v>4.6305</v>
+        <v>4.491</v>
       </c>
       <c r="Q305" t="n">
         <v>3</v>
@@ -23061,10 +23061,10 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="M306" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="N306" t="n">
         <v>5.13</v>
@@ -23073,7 +23073,7 @@
         <v>5.61</v>
       </c>
       <c r="P306" t="n">
-        <v>5.75</v>
+        <v>5.616999999999999</v>
       </c>
       <c r="Q306" t="n">
         <v>2</v>
@@ -23135,10 +23135,10 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>5.43</v>
+        <v>5.23</v>
       </c>
       <c r="M307" t="n">
-        <v>5.38</v>
+        <v>5.2</v>
       </c>
       <c r="N307" t="n">
         <v>8.6</v>
@@ -23147,7 +23147,7 @@
         <v>5.61</v>
       </c>
       <c r="P307" t="n">
-        <v>6.073499999999999</v>
+        <v>5.9505</v>
       </c>
       <c r="Q307" t="n">
         <v>1</v>
@@ -23209,10 +23209,10 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="M308" t="n">
-        <v>6.17</v>
+        <v>5.96</v>
       </c>
       <c r="N308" t="n">
         <v>7</v>
@@ -23221,7 +23221,7 @@
         <v>7.79</v>
       </c>
       <c r="P308" t="n">
-        <v>6.486</v>
+        <v>6.3495</v>
       </c>
       <c r="Q308" t="n">
         <v>3</v>
@@ -23283,10 +23283,10 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>6.25</v>
+        <v>6.03</v>
       </c>
       <c r="M309" t="n">
-        <v>6.52</v>
+        <v>6.31</v>
       </c>
       <c r="N309" t="n">
         <v>9.32</v>
@@ -23295,7 +23295,7 @@
         <v>7.79</v>
       </c>
       <c r="P309" t="n">
-        <v>7.1895</v>
+        <v>7.05</v>
       </c>
       <c r="Q309" t="n">
         <v>2</v>
@@ -23357,10 +23357,10 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>6.63</v>
+        <v>6.4</v>
       </c>
       <c r="M310" t="n">
-        <v>6.88</v>
+        <v>6.66</v>
       </c>
       <c r="N310" t="n">
         <v>8.6</v>
@@ -23369,7 +23369,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="P310" t="n">
-        <v>7.335</v>
+        <v>7.188999999999999</v>
       </c>
       <c r="Q310" t="n">
         <v>1</v>
@@ -23431,10 +23431,10 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M311" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="N311" t="n">
         <v>5.13</v>
@@ -23443,7 +23443,7 @@
         <v>7.76</v>
       </c>
       <c r="P311" t="n">
-        <v>8.69</v>
+        <v>8.5185</v>
       </c>
       <c r="Q311" t="n">
         <v>3</v>
@@ -23505,10 +23505,10 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>9.76</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M312" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="N312" t="n">
         <v>7.83</v>
@@ -23517,7 +23517,7 @@
         <v>7.76</v>
       </c>
       <c r="P312" t="n">
-        <v>9.081</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="Q312" t="n">
         <v>2</v>
@@ -23579,10 +23579,10 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>9.49</v>
+        <v>9.19</v>
       </c>
       <c r="M313" t="n">
-        <v>9.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="N313" t="n">
         <v>10</v>
@@ -23591,7 +23591,7 @@
         <v>6.61</v>
       </c>
       <c r="P313" t="n">
-        <v>9.173999999999999</v>
+        <v>8.985999999999999</v>
       </c>
       <c r="Q313" t="n">
         <v>1</v>
@@ -23653,10 +23653,10 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>8.59</v>
+        <v>8.31</v>
       </c>
       <c r="M314" t="n">
-        <v>8.69</v>
+        <v>8.44</v>
       </c>
       <c r="N314" t="n">
         <v>8.6</v>
@@ -23665,7 +23665,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="P314" t="n">
-        <v>8.667499999999999</v>
+        <v>8.495999999999999</v>
       </c>
       <c r="Q314" t="n">
         <v>3</v>
@@ -23727,10 +23727,10 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>8.69</v>
+        <v>8.41</v>
       </c>
       <c r="M315" t="n">
-        <v>8.789999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N315" t="n">
         <v>10</v>
@@ -23739,7 +23739,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="P315" t="n">
-        <v>9.012499999999999</v>
+        <v>8.8375</v>
       </c>
       <c r="Q315" t="n">
         <v>1</v>
@@ -23801,10 +23801,10 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>8.85</v>
+        <v>8.57</v>
       </c>
       <c r="M316" t="n">
-        <v>8.93</v>
+        <v>8.67</v>
       </c>
       <c r="N316" t="n">
         <v>7.83</v>
@@ -23813,7 +23813,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="P316" t="n">
-        <v>8.728</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="Q316" t="n">
         <v>2</v>

--- a/Ground Truth/ground_truth_hvac.xlsx
+++ b/Ground Truth/ground_truth_hvac.xlsx
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.75</v>
+        <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>7.77</v>
+        <v>0.78</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="P2" t="n">
-        <v>7.558999999999999</v>
+        <v>0.7579999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.96</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>8.3955</v>
+        <v>0.8414999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9285</v>
+        <v>0.7945</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.949999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="N5" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O5" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P5" t="n">
-        <v>9.1165</v>
+        <v>0.91</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="M6" t="n">
-        <v>9.74</v>
+        <v>0.97</v>
       </c>
       <c r="N6" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O6" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P6" t="n">
-        <v>9.153500000000001</v>
+        <v>0.914</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.609999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M7" t="n">
-        <v>9.58</v>
+        <v>0.96</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P7" t="n">
-        <v>8.5825</v>
+        <v>0.8584999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.36</v>
+        <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>5.44</v>
+        <v>0.54</v>
       </c>
       <c r="N8" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O8" t="n">
-        <v>7.71</v>
+        <v>0.77</v>
       </c>
       <c r="P8" t="n">
-        <v>6.532500000000001</v>
+        <v>0.6525000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.75</v>
+        <v>0.58</v>
       </c>
       <c r="M9" t="n">
-        <v>5.83</v>
+        <v>0.58</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>7.71</v>
+        <v>0.77</v>
       </c>
       <c r="P9" t="n">
-        <v>6.321999999999999</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>6.22</v>
+        <v>0.62</v>
       </c>
       <c r="N10" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O10" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P10" t="n">
-        <v>5.89</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.53</v>
+        <v>0.75</v>
       </c>
       <c r="M11" t="n">
-        <v>7.56</v>
+        <v>0.76</v>
       </c>
       <c r="N11" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O11" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P11" t="n">
-        <v>7.021</v>
+        <v>0.703</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
@@ -1305,19 +1305,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.15</v>
+        <v>0.72</v>
       </c>
       <c r="M12" t="n">
-        <v>7.19</v>
+        <v>0.72</v>
       </c>
       <c r="N12" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O12" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P12" t="n">
-        <v>7.2755</v>
+        <v>0.73</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1379,19 +1379,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.77</v>
+        <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>6.82</v>
+        <v>0.68</v>
       </c>
       <c r="N13" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O13" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P13" t="n">
-        <v>7.175999999999999</v>
+        <v>0.718</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>7.38</v>
+        <v>0.74</v>
       </c>
       <c r="M14" t="n">
-        <v>7.33</v>
+        <v>0.73</v>
       </c>
       <c r="N14" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O14" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P14" t="n">
-        <v>7.624499999999999</v>
+        <v>0.762</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -1527,19 +1527,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7.58</v>
+        <v>0.76</v>
       </c>
       <c r="M15" t="n">
-        <v>7.52</v>
+        <v>0.75</v>
       </c>
       <c r="N15" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O15" t="n">
-        <v>7.82</v>
+        <v>0.78</v>
       </c>
       <c r="P15" t="n">
-        <v>7.943</v>
+        <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.78</v>
+        <v>0.78</v>
       </c>
       <c r="M16" t="n">
-        <v>7.72</v>
+        <v>0.77</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>7.82</v>
+        <v>0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>7.609</v>
+        <v>0.7605</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -1675,19 +1675,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>6.96</v>
+        <v>0.7</v>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O17" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="P17" t="n">
-        <v>7.3255</v>
+        <v>0.7335</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1749,19 +1749,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.21</v>
+        <v>0.72</v>
       </c>
       <c r="M18" t="n">
-        <v>7.24</v>
+        <v>0.72</v>
       </c>
       <c r="N18" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O18" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="P18" t="n">
-        <v>7.012499999999999</v>
+        <v>0.6995</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1823,19 +1823,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.49</v>
+        <v>0.75</v>
       </c>
       <c r="M19" t="n">
-        <v>7.51</v>
+        <v>0.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O19" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>6.289</v>
+        <v>0.6294999999999998</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>8.15</v>
+        <v>0.82</v>
       </c>
       <c r="N20" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O20" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.164999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -1971,19 +1971,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="M21" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N21" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.491</v>
+        <v>0.7469999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
@@ -2045,19 +2045,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.48</v>
+        <v>0.75</v>
       </c>
       <c r="M22" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>7.7105</v>
+        <v>0.7715</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -2119,19 +2119,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>6.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="P23" t="n">
-        <v>7.7055</v>
+        <v>0.7685</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2193,19 +2193,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7.15</v>
+        <v>0.71</v>
       </c>
       <c r="M24" t="n">
-        <v>7.18</v>
+        <v>0.72</v>
       </c>
       <c r="N24" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="P24" t="n">
-        <v>7.423999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -2267,19 +2267,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7.38</v>
+        <v>0.74</v>
       </c>
       <c r="M25" t="n">
-        <v>7.41</v>
+        <v>0.74</v>
       </c>
       <c r="N25" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O25" t="n">
-        <v>8.33</v>
+        <v>0.83</v>
       </c>
       <c r="P25" t="n">
-        <v>7.082999999999999</v>
+        <v>0.7074999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9.529999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="M26" t="n">
-        <v>9.49</v>
+        <v>0.95</v>
       </c>
       <c r="N26" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O26" t="n">
-        <v>6.2</v>
+        <v>0.62</v>
       </c>
       <c r="P26" t="n">
-        <v>8.676499999999999</v>
+        <v>0.8664999999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
@@ -2415,19 +2415,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>9.289999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="M27" t="n">
-        <v>9.27</v>
+        <v>0.93</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>6.2</v>
+        <v>0.62</v>
       </c>
       <c r="P27" t="n">
-        <v>8.961499999999999</v>
+        <v>0.8975</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -2489,19 +2489,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9.06</v>
+        <v>0.91</v>
       </c>
       <c r="M28" t="n">
-        <v>9.039999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N28" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O28" t="n">
-        <v>6.2</v>
+        <v>0.62</v>
       </c>
       <c r="P28" t="n">
-        <v>8.378</v>
+        <v>0.8370000000000001</v>
       </c>
       <c r="Q28" t="n">
         <v>3</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O29" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P29" t="n">
-        <v>9.207000000000001</v>
+        <v>0.9209999999999999</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
@@ -2637,19 +2637,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O30" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P30" t="n">
-        <v>9.351000000000001</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O31" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P31" t="n">
-        <v>8.887</v>
+        <v>0.8889999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>3</v>
@@ -2785,19 +2785,19 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="M32" t="n">
-        <v>8.390000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="P32" t="n">
-        <v>8.833499999999999</v>
+        <v>0.8855</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2859,19 +2859,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8.609999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="M33" t="n">
-        <v>8.550000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="N33" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O33" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="P33" t="n">
-        <v>8.503499999999999</v>
+        <v>0.8480000000000001</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
@@ -2933,19 +2933,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.77</v>
+        <v>0.88</v>
       </c>
       <c r="M34" t="n">
-        <v>8.710000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="N34" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O34" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P34" t="n">
-        <v>8.121499999999999</v>
+        <v>0.8115</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -3007,19 +3007,19 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.81</v>
+        <v>0.98</v>
       </c>
       <c r="M35" t="n">
-        <v>9.74</v>
+        <v>0.97</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O35" t="n">
-        <v>7.13</v>
+        <v>0.71</v>
       </c>
       <c r="P35" t="n">
-        <v>8.8215</v>
+        <v>0.88</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
@@ -3081,19 +3081,19 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.640000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="M36" t="n">
-        <v>9.57</v>
+        <v>0.96</v>
       </c>
       <c r="N36" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O36" t="n">
-        <v>7.13</v>
+        <v>0.71</v>
       </c>
       <c r="P36" t="n">
-        <v>9.175000000000001</v>
+        <v>0.9165</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3155,19 +3155,19 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.48</v>
+        <v>0.95</v>
       </c>
       <c r="M37" t="n">
-        <v>9.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O37" t="n">
-        <v>7.13</v>
+        <v>0.71</v>
       </c>
       <c r="P37" t="n">
-        <v>8.923500000000001</v>
+        <v>0.8925</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
@@ -3229,19 +3229,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="M38" t="n">
-        <v>8.380000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>9.52</v>
+        <v>0.95</v>
       </c>
       <c r="P38" t="n">
-        <v>8.893000000000001</v>
+        <v>0.8885</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -3303,19 +3303,19 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8.58</v>
+        <v>0.86</v>
       </c>
       <c r="M39" t="n">
-        <v>8.52</v>
+        <v>0.85</v>
       </c>
       <c r="N39" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="O39" t="n">
-        <v>9.52</v>
+        <v>0.95</v>
       </c>
       <c r="P39" t="n">
-        <v>8.451999999999998</v>
+        <v>0.844</v>
       </c>
       <c r="Q39" t="n">
         <v>2</v>
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>8.73</v>
+        <v>0.87</v>
       </c>
       <c r="M40" t="n">
-        <v>8.66</v>
+        <v>0.87</v>
       </c>
       <c r="N40" t="n">
-        <v>3.83</v>
+        <v>0.38</v>
       </c>
       <c r="O40" t="n">
-        <v>9.52</v>
+        <v>0.95</v>
       </c>
       <c r="P40" t="n">
-        <v>7.844</v>
+        <v>0.7839999999999999</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
@@ -3451,19 +3451,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="M41" t="n">
-        <v>8.210000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="N41" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O41" t="n">
-        <v>9.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>8.312499999999998</v>
+        <v>0.83</v>
       </c>
       <c r="Q41" t="n">
         <v>3</v>
@@ -3525,19 +3525,19 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8.35</v>
+        <v>0.84</v>
       </c>
       <c r="M42" t="n">
-        <v>8.35</v>
+        <v>0.84</v>
       </c>
       <c r="N42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>9.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P42" t="n">
-        <v>8.8405</v>
+        <v>0.887</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -3599,19 +3599,19 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8.5</v>
+        <v>0.85</v>
       </c>
       <c r="M43" t="n">
-        <v>8.49</v>
+        <v>0.85</v>
       </c>
       <c r="N43" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O43" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="P43" t="n">
-        <v>8.554499999999999</v>
+        <v>0.8555</v>
       </c>
       <c r="Q43" t="n">
         <v>2</v>
@@ -3673,19 +3673,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="M44" t="n">
-        <v>7.18</v>
+        <v>0.72</v>
       </c>
       <c r="N44" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O44" t="n">
-        <v>9.199999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="P44" t="n">
-        <v>7.782</v>
+        <v>0.778</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -3747,19 +3747,19 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>7.52</v>
+        <v>0.75</v>
       </c>
       <c r="M45" t="n">
-        <v>7.46</v>
+        <v>0.75</v>
       </c>
       <c r="N45" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O45" t="n">
-        <v>9.199999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="P45" t="n">
-        <v>7.468999999999999</v>
+        <v>0.7474999999999999</v>
       </c>
       <c r="Q45" t="n">
         <v>2</v>
@@ -3821,19 +3821,19 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="M46" t="n">
-        <v>7.74</v>
+        <v>0.77</v>
       </c>
       <c r="N46" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O46" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P46" t="n">
-        <v>6.7055</v>
+        <v>0.6694999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>7.11</v>
+        <v>0.71</v>
       </c>
       <c r="M47" t="n">
-        <v>7.06</v>
+        <v>0.71</v>
       </c>
       <c r="N47" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O47" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P47" t="n">
-        <v>6.9105</v>
+        <v>0.6914999999999999</v>
       </c>
       <c r="Q47" t="n">
         <v>3</v>
@@ -3969,19 +3969,19 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.75</v>
+        <v>0.67</v>
       </c>
       <c r="M48" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="N48" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O48" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P48" t="n">
-        <v>7.174499999999999</v>
+        <v>0.7155</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -4043,19 +4043,19 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6.39</v>
+        <v>0.64</v>
       </c>
       <c r="M49" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="N49" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O49" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P49" t="n">
-        <v>7.084499999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -4117,19 +4117,19 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="M50" t="n">
-        <v>7.7</v>
+        <v>0.77</v>
       </c>
       <c r="N50" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O50" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P50" t="n">
-        <v>8.2685</v>
+        <v>0.8275</v>
       </c>
       <c r="Q50" t="n">
         <v>2</v>
@@ -4191,19 +4191,19 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="M51" t="n">
-        <v>7.95</v>
+        <v>0.8</v>
       </c>
       <c r="N51" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O51" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P51" t="n">
-        <v>8.286999999999999</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4265,19 +4265,19 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>8.26</v>
+        <v>0.83</v>
       </c>
       <c r="M52" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N52" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O52" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P52" t="n">
-        <v>7.951499999999999</v>
+        <v>0.7959999999999999</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
@@ -4339,19 +4339,19 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>7.74</v>
+        <v>0.77</v>
       </c>
       <c r="M53" t="n">
-        <v>7.68</v>
+        <v>0.77</v>
       </c>
       <c r="N53" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O53" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9645</v>
+        <v>0.7955</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>7.94</v>
+        <v>0.79</v>
       </c>
       <c r="M54" t="n">
-        <v>7.88</v>
+        <v>0.79</v>
       </c>
       <c r="N54" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O54" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="P54" t="n">
-        <v>7.460500000000001</v>
+        <v>0.7444999999999999</v>
       </c>
       <c r="Q54" t="n">
         <v>2</v>
@@ -4487,19 +4487,19 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>8.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="O55" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="P55" t="n">
-        <v>6.409</v>
+        <v>0.639</v>
       </c>
       <c r="Q55" t="n">
         <v>3</v>
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>5.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>5.73</v>
+        <v>0.57</v>
       </c>
       <c r="N56" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O56" t="n">
-        <v>8.48</v>
+        <v>0.85</v>
       </c>
       <c r="P56" t="n">
-        <v>5.9985</v>
+        <v>0.597</v>
       </c>
       <c r="Q56" t="n">
         <v>3</v>
@@ -4635,19 +4635,19 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.98</v>
+        <v>0.6</v>
       </c>
       <c r="M57" t="n">
-        <v>6.05</v>
+        <v>0.6</v>
       </c>
       <c r="N57" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O57" t="n">
-        <v>8.48</v>
+        <v>0.85</v>
       </c>
       <c r="P57" t="n">
-        <v>7.0195</v>
+        <v>0.7015</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
@@ -4709,19 +4709,19 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="M58" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="N58" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="O58" t="n">
-        <v>8.48</v>
+        <v>0.85</v>
       </c>
       <c r="P58" t="n">
-        <v>6.8625</v>
+        <v>0.6864999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>2</v>
@@ -4783,19 +4783,19 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.65</v>
+        <v>0.47</v>
       </c>
       <c r="M59" t="n">
-        <v>4.62</v>
+        <v>0.46</v>
       </c>
       <c r="N59" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O59" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P59" t="n">
-        <v>6.114</v>
+        <v>0.612</v>
       </c>
       <c r="Q59" t="n">
         <v>2</v>
@@ -4857,19 +4857,19 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="M60" t="n">
-        <v>4.98</v>
+        <v>0.5</v>
       </c>
       <c r="N60" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O60" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P60" t="n">
-        <v>6.172000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -4931,19 +4931,19 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5.37</v>
+        <v>0.54</v>
       </c>
       <c r="M61" t="n">
-        <v>5.33</v>
+        <v>0.53</v>
       </c>
       <c r="N61" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O61" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P61" t="n">
-        <v>5.7685</v>
+        <v>0.5755</v>
       </c>
       <c r="Q61" t="n">
         <v>3</v>
@@ -5005,19 +5005,19 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7.07</v>
+        <v>0.71</v>
       </c>
       <c r="M62" t="n">
-        <v>7.02</v>
+        <v>0.7</v>
       </c>
       <c r="N62" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="O62" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P62" t="n">
-        <v>6.823</v>
+        <v>0.6829999999999999</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
@@ -5079,19 +5079,19 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.68</v>
+        <v>0.67</v>
       </c>
       <c r="M63" t="n">
-        <v>6.64</v>
+        <v>0.66</v>
       </c>
       <c r="N63" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O63" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P63" t="n">
-        <v>7.151</v>
+        <v>0.715</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
@@ -5153,19 +5153,19 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>6.3</v>
+        <v>0.63</v>
       </c>
       <c r="M64" t="n">
-        <v>6.25</v>
+        <v>0.63</v>
       </c>
       <c r="N64" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O64" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P64" t="n">
-        <v>6.7245</v>
+        <v>0.6745</v>
       </c>
       <c r="Q64" t="n">
         <v>3</v>
@@ -5227,19 +5227,19 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>6.6</v>
+        <v>0.66</v>
       </c>
       <c r="M65" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="N65" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O65" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P65" t="n">
-        <v>6.495500000000001</v>
+        <v>0.6505</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
@@ -5301,19 +5301,19 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6.18</v>
+        <v>0.62</v>
       </c>
       <c r="M66" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="N66" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O66" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P66" t="n">
-        <v>6.723999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
@@ -5375,19 +5375,19 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.75</v>
+        <v>0.57</v>
       </c>
       <c r="M67" t="n">
-        <v>5.82</v>
+        <v>0.58</v>
       </c>
       <c r="N67" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O67" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P67" t="n">
-        <v>6.592</v>
+        <v>0.656</v>
       </c>
       <c r="Q67" t="n">
         <v>2</v>
@@ -5449,19 +5449,19 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.97</v>
+        <v>0.5</v>
       </c>
       <c r="M68" t="n">
-        <v>5.07</v>
+        <v>0.51</v>
       </c>
       <c r="N68" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O68" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="P68" t="n">
-        <v>6.3255</v>
+        <v>0.6355000000000001</v>
       </c>
       <c r="Q68" t="n">
         <v>2</v>
@@ -5523,19 +5523,19 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.38</v>
+        <v>0.54</v>
       </c>
       <c r="M69" t="n">
-        <v>5.46</v>
+        <v>0.55</v>
       </c>
       <c r="N69" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O69" t="n">
-        <v>8.49</v>
+        <v>0.85</v>
       </c>
       <c r="P69" t="n">
-        <v>6.4585</v>
+        <v>0.6480000000000001</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
@@ -5597,19 +5597,19 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.78</v>
+        <v>0.58</v>
       </c>
       <c r="M70" t="n">
-        <v>5.86</v>
+        <v>0.59</v>
       </c>
       <c r="N70" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O70" t="n">
-        <v>8.49</v>
+        <v>0.85</v>
       </c>
       <c r="P70" t="n">
-        <v>6.0845</v>
+        <v>0.6099999999999999</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
@@ -5671,19 +5671,19 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7.47</v>
+        <v>0.75</v>
       </c>
       <c r="M71" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="N71" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="O71" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="P71" t="n">
-        <v>7.000999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Q71" t="n">
         <v>2</v>
@@ -5745,19 +5745,19 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>7.08</v>
+        <v>0.71</v>
       </c>
       <c r="M72" t="n">
-        <v>7.12</v>
+        <v>0.71</v>
       </c>
       <c r="N72" t="n">
-        <v>9.109999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="O72" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="P72" t="n">
-        <v>7.388999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
@@ -5819,19 +5819,19 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="M73" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="N73" t="n">
-        <v>8.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O73" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="P73" t="n">
-        <v>6.946999999999999</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="Q73" t="n">
         <v>3</v>
@@ -5893,19 +5893,19 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>5.42</v>
+        <v>0.54</v>
       </c>
       <c r="M74" t="n">
-        <v>5.51</v>
+        <v>0.55</v>
       </c>
       <c r="N74" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O74" t="n">
-        <v>7.92</v>
+        <v>0.79</v>
       </c>
       <c r="P74" t="n">
-        <v>6.462499999999999</v>
+        <v>0.645</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -5967,19 +5967,19 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.88</v>
+        <v>0.59</v>
       </c>
       <c r="M75" t="n">
-        <v>5.95</v>
+        <v>0.59</v>
       </c>
       <c r="N75" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O75" t="n">
-        <v>8.25</v>
+        <v>0.82</v>
       </c>
       <c r="P75" t="n">
-        <v>6.306</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -6041,19 +6041,19 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>6.34</v>
+        <v>0.63</v>
       </c>
       <c r="M76" t="n">
-        <v>6.39</v>
+        <v>0.64</v>
       </c>
       <c r="N76" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O76" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P76" t="n">
-        <v>5.6315</v>
+        <v>0.5625</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
@@ -6115,19 +6115,19 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>5.47</v>
+        <v>0.55</v>
       </c>
       <c r="M77" t="n">
-        <v>5.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O77" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P77" t="n">
-        <v>5.73</v>
+        <v>0.5745</v>
       </c>
       <c r="Q77" t="n">
         <v>2</v>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.94</v>
+        <v>0.49</v>
       </c>
       <c r="M78" t="n">
-        <v>5.04</v>
+        <v>0.5</v>
       </c>
       <c r="N78" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O78" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P78" t="n">
-        <v>5.887</v>
+        <v>0.5855</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
@@ -6263,19 +6263,19 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.41</v>
+        <v>0.44</v>
       </c>
       <c r="M79" t="n">
-        <v>4.52</v>
+        <v>0.45</v>
       </c>
       <c r="N79" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O79" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P79" t="n">
-        <v>5.69</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="Q79" t="n">
         <v>3</v>
@@ -6337,19 +6337,19 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.94</v>
+        <v>0.29</v>
       </c>
       <c r="M80" t="n">
-        <v>3.09</v>
+        <v>0.31</v>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>7.88</v>
+        <v>0.79</v>
       </c>
       <c r="P80" t="n">
-        <v>5.1455</v>
+        <v>0.514</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -6411,19 +6411,19 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.48</v>
+        <v>0.35</v>
       </c>
       <c r="M81" t="n">
-        <v>3.62</v>
+        <v>0.36</v>
       </c>
       <c r="N81" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O81" t="n">
-        <v>7.88</v>
+        <v>0.79</v>
       </c>
       <c r="P81" t="n">
-        <v>5.058999999999999</v>
+        <v>0.5055000000000001</v>
       </c>
       <c r="Q81" t="n">
         <v>2</v>
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.03</v>
+        <v>0.4</v>
       </c>
       <c r="M82" t="n">
-        <v>4.15</v>
+        <v>0.42</v>
       </c>
       <c r="N82" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O82" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P82" t="n">
-        <v>4.9175</v>
+        <v>0.492</v>
       </c>
       <c r="Q82" t="n">
         <v>3</v>
@@ -6559,19 +6559,19 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.47</v>
+        <v>0.45</v>
       </c>
       <c r="M83" t="n">
-        <v>4.58</v>
+        <v>0.46</v>
       </c>
       <c r="N83" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O83" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="P83" t="n">
-        <v>5.259</v>
+        <v>0.5275000000000001</v>
       </c>
       <c r="Q83" t="n">
         <v>2</v>
@@ -6633,19 +6633,19 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="N84" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O84" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="P84" t="n">
-        <v>5.34</v>
+        <v>0.5345000000000001</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -6707,19 +6707,19 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.27</v>
+        <v>0.33</v>
       </c>
       <c r="M85" t="n">
-        <v>3.42</v>
+        <v>0.34</v>
       </c>
       <c r="N85" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O85" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="P85" t="n">
-        <v>4.813</v>
+        <v>0.4815</v>
       </c>
       <c r="Q85" t="n">
         <v>3</v>
@@ -6781,19 +6781,19 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.33</v>
+        <v>0.43</v>
       </c>
       <c r="M86" t="n">
-        <v>4.45</v>
+        <v>0.44</v>
       </c>
       <c r="N86" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O86" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P86" t="n">
-        <v>5.685</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="Q86" t="n">
         <v>3</v>
@@ -6855,19 +6855,19 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.7</v>
+        <v>0.47</v>
       </c>
       <c r="M87" t="n">
-        <v>4.8</v>
+        <v>0.48</v>
       </c>
       <c r="N87" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O87" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P87" t="n">
-        <v>6.0945</v>
+        <v>0.61</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -6929,19 +6929,19 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.06</v>
+        <v>0.51</v>
       </c>
       <c r="M88" t="n">
-        <v>5.15</v>
+        <v>0.52</v>
       </c>
       <c r="N88" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="O88" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P88" t="n">
-        <v>5.7965</v>
+        <v>0.5825</v>
       </c>
       <c r="Q88" t="n">
         <v>2</v>
@@ -7003,19 +7003,19 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="M89" t="n">
-        <v>6.2</v>
+        <v>0.62</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O89" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P89" t="n">
-        <v>6.306</v>
+        <v>0.63</v>
       </c>
       <c r="Q89" t="n">
         <v>2</v>
@@ -7077,19 +7077,19 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>5.72</v>
+        <v>0.57</v>
       </c>
       <c r="M90" t="n">
-        <v>5.8</v>
+        <v>0.58</v>
       </c>
       <c r="N90" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O90" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P90" t="n">
-        <v>6.504</v>
+        <v>0.65</v>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -7151,19 +7151,19 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5.3</v>
+        <v>0.53</v>
       </c>
       <c r="M91" t="n">
-        <v>5.39</v>
+        <v>0.54</v>
       </c>
       <c r="N91" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O91" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="P91" t="n">
-        <v>6.0905</v>
+        <v>0.61</v>
       </c>
       <c r="Q91" t="n">
         <v>3</v>
@@ -7225,19 +7225,19 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>5.29</v>
+        <v>0.53</v>
       </c>
       <c r="M92" t="n">
-        <v>5.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O92" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P92" t="n">
-        <v>5.7955</v>
+        <v>0.579</v>
       </c>
       <c r="Q92" t="n">
         <v>2</v>
@@ -7299,19 +7299,19 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4.75</v>
+        <v>0.47</v>
       </c>
       <c r="M93" t="n">
-        <v>5.12</v>
+        <v>0.51</v>
       </c>
       <c r="N93" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O93" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P93" t="n">
-        <v>5.922499999999999</v>
+        <v>0.5895</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
@@ -7373,19 +7373,19 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.21</v>
+        <v>0.42</v>
       </c>
       <c r="M94" t="n">
-        <v>4.62</v>
+        <v>0.46</v>
       </c>
       <c r="N94" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O94" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P94" t="n">
-        <v>5.4415</v>
+        <v>0.543</v>
       </c>
       <c r="Q94" t="n">
         <v>3</v>
@@ -7453,13 +7453,13 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O95" t="n">
-        <v>6.84</v>
+        <v>0.68</v>
       </c>
       <c r="P95" t="n">
-        <v>2.718</v>
+        <v>0.272</v>
       </c>
       <c r="Q95" t="n">
         <v>1</v>
@@ -7527,13 +7527,13 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O96" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P96" t="n">
-        <v>2.455</v>
+        <v>0.2465</v>
       </c>
       <c r="Q96" t="n">
         <v>2</v>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O97" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P97" t="n">
-        <v>2.025</v>
+        <v>0.2025</v>
       </c>
       <c r="Q97" t="n">
         <v>3</v>
@@ -7669,19 +7669,19 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>4.37</v>
+        <v>0.44</v>
       </c>
       <c r="M98" t="n">
-        <v>4.49</v>
+        <v>0.45</v>
       </c>
       <c r="N98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P98" t="n">
-        <v>6.1005</v>
+        <v>0.611</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
@@ -7743,19 +7743,19 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.62</v>
+        <v>0.46</v>
       </c>
       <c r="M99" t="n">
-        <v>4.73</v>
+        <v>0.47</v>
       </c>
       <c r="N99" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O99" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P99" t="n">
-        <v>5.9795</v>
+        <v>0.5960000000000001</v>
       </c>
       <c r="Q99" t="n">
         <v>2</v>
@@ -7817,19 +7817,19 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>4.87</v>
+        <v>0.49</v>
       </c>
       <c r="M100" t="n">
-        <v>4.97</v>
+        <v>0.5</v>
       </c>
       <c r="N100" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O100" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P100" t="n">
-        <v>5.8185</v>
+        <v>0.5834999999999999</v>
       </c>
       <c r="Q100" t="n">
         <v>3</v>
@@ -7897,13 +7897,13 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="O101" t="n">
-        <v>7.71</v>
+        <v>0.77</v>
       </c>
       <c r="P101" t="n">
-        <v>2.6245</v>
+        <v>0.2615</v>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
@@ -7971,13 +7971,13 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O102" t="n">
-        <v>7.71</v>
+        <v>0.77</v>
       </c>
       <c r="P102" t="n">
-        <v>2.1825</v>
+        <v>0.2175</v>
       </c>
       <c r="Q102" t="n">
         <v>2</v>
@@ -8045,13 +8045,13 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.35</v>
+        <v>0.23</v>
       </c>
       <c r="O103" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="P103" t="n">
-        <v>1.481</v>
+        <v>0.1465</v>
       </c>
       <c r="Q103" t="n">
         <v>3</v>
@@ -8113,19 +8113,19 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>5.74</v>
+        <v>0.57</v>
       </c>
       <c r="M104" t="n">
-        <v>5.7</v>
+        <v>0.57</v>
       </c>
       <c r="N104" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O104" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P104" t="n">
-        <v>6.810999999999999</v>
+        <v>0.6795</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -8187,19 +8187,19 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="M105" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N105" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O105" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P105" t="n">
-        <v>6.656</v>
+        <v>0.6655</v>
       </c>
       <c r="Q105" t="n">
         <v>2</v>
@@ -8261,19 +8261,19 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>6.18</v>
+        <v>0.62</v>
       </c>
       <c r="M106" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="N106" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O106" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P106" t="n">
-        <v>6.454999999999999</v>
+        <v>0.6445</v>
       </c>
       <c r="Q106" t="n">
         <v>3</v>
@@ -8335,19 +8335,19 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>6.8</v>
+        <v>0.68</v>
       </c>
       <c r="M107" t="n">
-        <v>6.84</v>
+        <v>0.68</v>
       </c>
       <c r="N107" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O107" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="P107" t="n">
-        <v>6.508</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="Q107" t="n">
         <v>3</v>
@@ -8409,19 +8409,19 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>6.36</v>
+        <v>0.64</v>
       </c>
       <c r="M108" t="n">
-        <v>6.42</v>
+        <v>0.64</v>
       </c>
       <c r="N108" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O108" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="P108" t="n">
-        <v>6.726999999999999</v>
+        <v>0.6735</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -8483,19 +8483,19 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="M109" t="n">
-        <v>5.99</v>
+        <v>0.6</v>
       </c>
       <c r="N109" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O109" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="P109" t="n">
-        <v>6.5885</v>
+        <v>0.6585000000000001</v>
       </c>
       <c r="Q109" t="n">
         <v>2</v>
@@ -8557,19 +8557,19 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.26</v>
+        <v>0.53</v>
       </c>
       <c r="M110" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="N110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="P110" t="n">
-        <v>6.6985</v>
+        <v>0.6689999999999999</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -8631,19 +8631,19 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.39</v>
+        <v>0.54</v>
       </c>
       <c r="M111" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="N111" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O111" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="P111" t="n">
-        <v>6.647</v>
+        <v>0.665</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
@@ -8705,19 +8705,19 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>5.52</v>
+        <v>0.55</v>
       </c>
       <c r="M112" t="n">
-        <v>5.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N112" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O112" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="P112" t="n">
-        <v>6.584</v>
+        <v>0.6575</v>
       </c>
       <c r="Q112" t="n">
         <v>3</v>
@@ -8779,19 +8779,19 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>6.45</v>
+        <v>0.64</v>
       </c>
       <c r="M113" t="n">
-        <v>6.4</v>
+        <v>0.64</v>
       </c>
       <c r="N113" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O113" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P113" t="n">
-        <v>6.4385</v>
+        <v>0.6425000000000001</v>
       </c>
       <c r="Q113" t="n">
         <v>2</v>
@@ -8853,19 +8853,19 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>5.9</v>
+        <v>0.59</v>
       </c>
       <c r="M114" t="n">
-        <v>5.86</v>
+        <v>0.59</v>
       </c>
       <c r="N114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>8.75</v>
+        <v>0.87</v>
       </c>
       <c r="P114" t="n">
-        <v>7.1335</v>
+        <v>0.714</v>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -8927,19 +8927,19 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.36</v>
+        <v>0.54</v>
       </c>
       <c r="M115" t="n">
-        <v>5.32</v>
+        <v>0.53</v>
       </c>
       <c r="N115" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O115" t="n">
-        <v>7.36</v>
+        <v>0.74</v>
       </c>
       <c r="P115" t="n">
-        <v>5.474</v>
+        <v>0.5485000000000001</v>
       </c>
       <c r="Q115" t="n">
         <v>3</v>
@@ -9001,19 +9001,19 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>6.59</v>
+        <v>0.66</v>
       </c>
       <c r="M116" t="n">
-        <v>6.64</v>
+        <v>0.66</v>
       </c>
       <c r="N116" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O116" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P116" t="n">
-        <v>6.489000000000001</v>
+        <v>0.6469999999999999</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -9075,19 +9075,19 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>5.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M117" t="n">
-        <v>5.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N117" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O117" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P117" t="n">
-        <v>6.327999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="Q117" t="n">
         <v>2</v>
@@ -9149,19 +9149,19 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.54</v>
+        <v>0.45</v>
       </c>
       <c r="M118" t="n">
-        <v>4.65</v>
+        <v>0.46</v>
       </c>
       <c r="N118" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="O118" t="n">
-        <v>5.04</v>
+        <v>0.5</v>
       </c>
       <c r="P118" t="n">
-        <v>4.0515</v>
+        <v>0.4010000000000001</v>
       </c>
       <c r="Q118" t="n">
         <v>3</v>
@@ -9226,16 +9226,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
       <c r="N119" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O119" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P119" t="n">
-        <v>2.878</v>
+        <v>0.287</v>
       </c>
       <c r="Q119" t="n">
         <v>1</v>
@@ -9297,19 +9297,19 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
       </c>
       <c r="M120" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N120" t="n">
         <v>0.7</v>
       </c>
-      <c r="N120" t="n">
-        <v>7</v>
-      </c>
       <c r="O120" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P120" t="n">
-        <v>2.8255</v>
+        <v>0.2815</v>
       </c>
       <c r="Q120" t="n">
         <v>2</v>
@@ -9371,19 +9371,19 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="M121" t="n">
-        <v>1.19</v>
+        <v>0.12</v>
       </c>
       <c r="N121" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O121" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P121" t="n">
-        <v>2.758</v>
+        <v>0.276</v>
       </c>
       <c r="Q121" t="n">
         <v>3</v>
@@ -9445,19 +9445,19 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="M122" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="N122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="P122" t="n">
-        <v>8.904999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
@@ -9519,19 +9519,19 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M123" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N123" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O123" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="P123" t="n">
-        <v>8.354000000000001</v>
+        <v>0.8335</v>
       </c>
       <c r="Q123" t="n">
         <v>2</v>
@@ -9593,19 +9593,19 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>9.76</v>
+        <v>0.98</v>
       </c>
       <c r="M124" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>3.22</v>
+        <v>0.32</v>
       </c>
       <c r="P124" t="n">
-        <v>6.833999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="Q124" t="n">
         <v>3</v>
@@ -9667,19 +9667,19 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.92</v>
+        <v>0.39</v>
       </c>
       <c r="M125" t="n">
-        <v>3.89</v>
+        <v>0.39</v>
       </c>
       <c r="N125" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="O125" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P125" t="n">
-        <v>5.223999999999999</v>
+        <v>0.5225</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
@@ -9741,19 +9741,19 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.29</v>
+        <v>0.43</v>
       </c>
       <c r="M126" t="n">
-        <v>4.26</v>
+        <v>0.43</v>
       </c>
       <c r="N126" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O126" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P126" t="n">
-        <v>5.0725</v>
+        <v>0.5085</v>
       </c>
       <c r="Q126" t="n">
         <v>2</v>
@@ -9815,19 +9815,19 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>4.66</v>
+        <v>0.47</v>
       </c>
       <c r="M127" t="n">
-        <v>4.63</v>
+        <v>0.46</v>
       </c>
       <c r="N127" t="n">
-        <v>3.23</v>
+        <v>0.32</v>
       </c>
       <c r="O127" t="n">
-        <v>6.82</v>
+        <v>0.68</v>
       </c>
       <c r="P127" t="n">
-        <v>4.687499999999999</v>
+        <v>0.468</v>
       </c>
       <c r="Q127" t="n">
         <v>3</v>
@@ -9889,19 +9889,19 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>8.99</v>
+        <v>0.9</v>
       </c>
       <c r="M128" t="n">
-        <v>9.07</v>
+        <v>0.91</v>
       </c>
       <c r="N128" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O128" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>8.134500000000001</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="Q128" t="n">
         <v>3</v>
@@ -9963,19 +9963,19 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="M129" t="n">
-        <v>8.869999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N129" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O129" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P129" t="n">
-        <v>8.499499999999999</v>
+        <v>0.8510000000000001</v>
       </c>
       <c r="Q129" t="n">
         <v>2</v>
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>8.640000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="M130" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="N130" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P130" t="n">
-        <v>8.692</v>
+        <v>0.866</v>
       </c>
       <c r="Q130" t="n">
         <v>1</v>
@@ -10111,19 +10111,19 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>5.2</v>
+        <v>0.52</v>
       </c>
       <c r="M131" t="n">
-        <v>5.17</v>
+        <v>0.52</v>
       </c>
       <c r="N131" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O131" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P131" t="n">
-        <v>6.258</v>
+        <v>0.627</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
@@ -10185,19 +10185,19 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="M132" t="n">
-        <v>5.44</v>
+        <v>0.54</v>
       </c>
       <c r="N132" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O132" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P132" t="n">
-        <v>6.166</v>
+        <v>0.6154999999999999</v>
       </c>
       <c r="Q132" t="n">
         <v>2</v>
@@ -10259,19 +10259,19 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>5.76</v>
+        <v>0.58</v>
       </c>
       <c r="M133" t="n">
-        <v>5.72</v>
+        <v>0.57</v>
       </c>
       <c r="N133" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O133" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P133" t="n">
-        <v>5.973999999999999</v>
+        <v>0.597</v>
       </c>
       <c r="Q133" t="n">
         <v>3</v>
@@ -10333,19 +10333,19 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0.82</v>
+        <v>0.08</v>
       </c>
       <c r="M134" t="n">
-        <v>0.82</v>
+        <v>0.08</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>2.85</v>
+        <v>0.29</v>
       </c>
       <c r="P134" t="n">
-        <v>0.9604999999999999</v>
+        <v>0.0955</v>
       </c>
       <c r="Q134" t="n">
         <v>3</v>
@@ -10413,13 +10413,13 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.35</v>
+        <v>0.23</v>
       </c>
       <c r="O135" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P135" t="n">
-        <v>1.391</v>
+        <v>0.1375</v>
       </c>
       <c r="Q135" t="n">
         <v>2</v>
@@ -10487,13 +10487,13 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="O136" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P136" t="n">
-        <v>2.389</v>
+        <v>0.2375</v>
       </c>
       <c r="Q136" t="n">
         <v>1</v>
@@ -10555,19 +10555,19 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>6.35</v>
+        <v>0.64</v>
       </c>
       <c r="M137" t="n">
-        <v>6.41</v>
+        <v>0.64</v>
       </c>
       <c r="N137" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O137" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="P137" t="n">
-        <v>7.0315</v>
+        <v>0.7040000000000001</v>
       </c>
       <c r="Q137" t="n">
         <v>3</v>
@@ -10629,19 +10629,19 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>6.77</v>
+        <v>0.68</v>
       </c>
       <c r="M138" t="n">
-        <v>6.81</v>
+        <v>0.68</v>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="P138" t="n">
-        <v>7.7315</v>
+        <v>0.774</v>
       </c>
       <c r="Q138" t="n">
         <v>2</v>
@@ -10703,19 +10703,19 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O139" t="n">
-        <v>7.05</v>
+        <v>0.7</v>
       </c>
       <c r="P139" t="n">
-        <v>9.1235</v>
+        <v>0.9109999999999999</v>
       </c>
       <c r="Q139" t="n">
         <v>1</v>
@@ -10777,19 +10777,19 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4.54</v>
+        <v>0.45</v>
       </c>
       <c r="M140" t="n">
-        <v>4.65</v>
+        <v>0.46</v>
       </c>
       <c r="N140" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O140" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P140" t="n">
-        <v>6.013</v>
+        <v>0.5985</v>
       </c>
       <c r="Q140" t="n">
         <v>3</v>
@@ -10851,19 +10851,19 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>5.2</v>
+        <v>0.52</v>
       </c>
       <c r="M141" t="n">
-        <v>5.3</v>
+        <v>0.53</v>
       </c>
       <c r="N141" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O141" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P141" t="n">
-        <v>6.4385</v>
+        <v>0.6440000000000001</v>
       </c>
       <c r="Q141" t="n">
         <v>1</v>
@@ -10925,19 +10925,19 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>5.54</v>
+        <v>0.55</v>
       </c>
       <c r="M142" t="n">
-        <v>5.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N142" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="O142" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P142" t="n">
-        <v>6.2505</v>
+        <v>0.6234999999999999</v>
       </c>
       <c r="Q142" t="n">
         <v>2</v>
@@ -10999,19 +10999,19 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="M143" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="N143" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O143" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P143" t="n">
-        <v>8.194999999999999</v>
+        <v>0.8170000000000001</v>
       </c>
       <c r="Q143" t="n">
         <v>3</v>
@@ -11073,19 +11073,19 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
       <c r="M144" t="n">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
       <c r="N144" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O144" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P144" t="n">
-        <v>8.6425</v>
+        <v>0.8665</v>
       </c>
       <c r="Q144" t="n">
         <v>2</v>
@@ -11147,19 +11147,19 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O145" t="n">
-        <v>6.96</v>
+        <v>0.7</v>
       </c>
       <c r="P145" t="n">
-        <v>8.944000000000001</v>
+        <v>0.8949999999999999</v>
       </c>
       <c r="Q145" t="n">
         <v>1</v>
@@ -11221,19 +11221,19 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O146" t="n">
-        <v>8.279999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="P146" t="n">
-        <v>9.071999999999999</v>
+        <v>0.9084999999999999</v>
       </c>
       <c r="Q146" t="n">
         <v>3</v>
@@ -11295,19 +11295,19 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O147" t="n">
-        <v>7.58</v>
+        <v>0.76</v>
       </c>
       <c r="P147" t="n">
-        <v>9.487</v>
+        <v>0.95</v>
       </c>
       <c r="Q147" t="n">
         <v>1</v>
@@ -11369,19 +11369,19 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O148" t="n">
-        <v>7.58</v>
+        <v>0.76</v>
       </c>
       <c r="P148" t="n">
-        <v>9.329000000000001</v>
+        <v>0.9339999999999999</v>
       </c>
       <c r="Q148" t="n">
         <v>2</v>
@@ -11443,19 +11443,19 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>9.76</v>
+        <v>0.98</v>
       </c>
       <c r="M149" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="N149" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O149" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P149" t="n">
-        <v>8.6365</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="Q149" t="n">
         <v>2</v>
@@ -11517,19 +11517,19 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>9.34</v>
+        <v>0.93</v>
       </c>
       <c r="M150" t="n">
-        <v>9.31</v>
+        <v>0.93</v>
       </c>
       <c r="N150" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O150" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P150" t="n">
-        <v>8.865</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="Q150" t="n">
         <v>1</v>
@@ -11591,19 +11591,19 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="M151" t="n">
-        <v>8.77</v>
+        <v>0.88</v>
       </c>
       <c r="N151" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O151" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P151" t="n">
-        <v>8.507999999999999</v>
+        <v>0.8520000000000001</v>
       </c>
       <c r="Q151" t="n">
         <v>3</v>
@@ -11665,19 +11665,19 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O152" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P152" t="n">
-        <v>8.955</v>
+        <v>0.8964999999999999</v>
       </c>
       <c r="Q152" t="n">
         <v>2</v>
@@ -11739,19 +11739,19 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>9.789999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="M153" t="n">
-        <v>9.74</v>
+        <v>0.97</v>
       </c>
       <c r="N153" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P153" t="n">
-        <v>9.471</v>
+        <v>0.946</v>
       </c>
       <c r="Q153" t="n">
         <v>1</v>
@@ -11813,19 +11813,19 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>9.33</v>
+        <v>0.93</v>
       </c>
       <c r="M154" t="n">
-        <v>9.300000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="N154" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O154" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P154" t="n">
-        <v>8.509</v>
+        <v>0.851</v>
       </c>
       <c r="Q154" t="n">
         <v>3</v>
@@ -11887,19 +11887,19 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.96</v>
+        <v>0.3</v>
       </c>
       <c r="M155" t="n">
-        <v>3.12</v>
+        <v>0.31</v>
       </c>
       <c r="N155" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O155" t="n">
-        <v>7.5</v>
+        <v>0.75</v>
       </c>
       <c r="P155" t="n">
-        <v>4.327</v>
+        <v>0.433</v>
       </c>
       <c r="Q155" t="n">
         <v>3</v>
@@ -11961,19 +11961,19 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.73</v>
+        <v>0.37</v>
       </c>
       <c r="M156" t="n">
-        <v>3.86</v>
+        <v>0.39</v>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P156" t="n">
-        <v>5.699999999999999</v>
+        <v>0.5705</v>
       </c>
       <c r="Q156" t="n">
         <v>1</v>
@@ -12035,19 +12035,19 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="M157" t="n">
-        <v>4.75</v>
+        <v>0.48</v>
       </c>
       <c r="N157" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O157" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P157" t="n">
-        <v>5.310499999999999</v>
+        <v>0.531</v>
       </c>
       <c r="Q157" t="n">
         <v>2</v>
@@ -12115,13 +12115,13 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O158" t="n">
-        <v>6.73</v>
+        <v>0.67</v>
       </c>
       <c r="P158" t="n">
-        <v>1.9095</v>
+        <v>0.1905</v>
       </c>
       <c r="Q158" t="n">
         <v>3</v>
@@ -12183,19 +12183,19 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.39</v>
+        <v>0.14</v>
       </c>
       <c r="M159" t="n">
-        <v>1.59</v>
+        <v>0.16</v>
       </c>
       <c r="N159" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="P159" t="n">
-        <v>4.1795</v>
+        <v>0.418</v>
       </c>
       <c r="Q159" t="n">
         <v>2</v>
@@ -12257,19 +12257,19 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.25</v>
+        <v>0.22</v>
       </c>
       <c r="M160" t="n">
-        <v>2.42</v>
+        <v>0.24</v>
       </c>
       <c r="N160" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="O160" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="P160" t="n">
-        <v>4.246</v>
+        <v>0.422</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -12331,19 +12331,19 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="M161" t="n">
-        <v>6.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N161" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O161" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="P161" t="n">
-        <v>7.375</v>
+        <v>0.7349999999999999</v>
       </c>
       <c r="Q161" t="n">
         <v>2</v>
@@ -12405,19 +12405,19 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>7.28</v>
+        <v>0.73</v>
       </c>
       <c r="M162" t="n">
-        <v>7.22</v>
+        <v>0.72</v>
       </c>
       <c r="N162" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O162" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="P162" t="n">
-        <v>7.8515</v>
+        <v>0.7845</v>
       </c>
       <c r="Q162" t="n">
         <v>1</v>
@@ -12479,19 +12479,19 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>7.62</v>
+        <v>0.76</v>
       </c>
       <c r="M163" t="n">
-        <v>7.57</v>
+        <v>0.76</v>
       </c>
       <c r="N163" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O163" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="P163" t="n">
-        <v>7.238</v>
+        <v>0.7235</v>
       </c>
       <c r="Q163" t="n">
         <v>3</v>
@@ -12553,19 +12553,19 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="M164" t="n">
-        <v>6.21</v>
+        <v>0.62</v>
       </c>
       <c r="N164" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O164" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P164" t="n">
-        <v>5.991</v>
+        <v>0.5995</v>
       </c>
       <c r="Q164" t="n">
         <v>2</v>
@@ -12627,19 +12627,19 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>5.54</v>
+        <v>0.55</v>
       </c>
       <c r="M165" t="n">
-        <v>5.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N165" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O165" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P165" t="n">
-        <v>6.295499999999999</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="Q165" t="n">
         <v>1</v>
@@ -12701,19 +12701,19 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>4.61</v>
+        <v>0.46</v>
       </c>
       <c r="M166" t="n">
-        <v>4.72</v>
+        <v>0.47</v>
       </c>
       <c r="N166" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P166" t="n">
-        <v>5.381500000000001</v>
+        <v>0.537</v>
       </c>
       <c r="Q166" t="n">
         <v>3</v>
@@ -12775,19 +12775,19 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>5.95</v>
+        <v>0.59</v>
       </c>
       <c r="M167" t="n">
-        <v>6.01</v>
+        <v>0.6</v>
       </c>
       <c r="N167" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O167" t="n">
-        <v>5.89</v>
+        <v>0.59</v>
       </c>
       <c r="P167" t="n">
-        <v>5.994</v>
+        <v>0.5975</v>
       </c>
       <c r="Q167" t="n">
         <v>2</v>
@@ -12849,19 +12849,19 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>5.11</v>
+        <v>0.51</v>
       </c>
       <c r="M168" t="n">
-        <v>5.2</v>
+        <v>0.52</v>
       </c>
       <c r="N168" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>5.89</v>
+        <v>0.59</v>
       </c>
       <c r="P168" t="n">
-        <v>6.236499999999999</v>
+        <v>0.6234999999999999</v>
       </c>
       <c r="Q168" t="n">
         <v>1</v>
@@ -12923,19 +12923,19 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>3.91</v>
+        <v>0.39</v>
       </c>
       <c r="M169" t="n">
-        <v>4.23</v>
+        <v>0.42</v>
       </c>
       <c r="N169" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O169" t="n">
-        <v>5.89</v>
+        <v>0.59</v>
       </c>
       <c r="P169" t="n">
-        <v>4.563</v>
+        <v>0.4545</v>
       </c>
       <c r="Q169" t="n">
         <v>3</v>
@@ -12997,19 +12997,19 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>5.7</v>
+        <v>0.57</v>
       </c>
       <c r="M170" t="n">
-        <v>5.67</v>
+        <v>0.57</v>
       </c>
       <c r="N170" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O170" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P170" t="n">
-        <v>6.644499999999999</v>
+        <v>0.6655</v>
       </c>
       <c r="Q170" t="n">
         <v>2</v>
@@ -13071,19 +13071,19 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="M171" t="n">
-        <v>6.51</v>
+        <v>0.65</v>
       </c>
       <c r="N171" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="O171" t="n">
-        <v>5.14</v>
+        <v>0.51</v>
       </c>
       <c r="P171" t="n">
-        <v>5.323499999999999</v>
+        <v>0.532</v>
       </c>
       <c r="Q171" t="n">
         <v>3</v>
@@ -13145,19 +13145,19 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="P172" t="n">
-        <v>6.7265</v>
+        <v>0.6724999999999999</v>
       </c>
       <c r="Q172" t="n">
         <v>1</v>
@@ -13219,19 +13219,19 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="M173" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="N173" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O173" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="P173" t="n">
-        <v>7.334</v>
+        <v>0.7350000000000001</v>
       </c>
       <c r="Q173" t="n">
         <v>1</v>
@@ -13293,19 +13293,19 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>7.35</v>
+        <v>0.73</v>
       </c>
       <c r="M174" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="N174" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="O174" t="n">
-        <v>5.37</v>
+        <v>0.54</v>
       </c>
       <c r="P174" t="n">
-        <v>5.867999999999999</v>
+        <v>0.5855</v>
       </c>
       <c r="Q174" t="n">
         <v>3</v>
@@ -13367,19 +13367,19 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N175" t="n">
         <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="P175" t="n">
-        <v>6.7265</v>
+        <v>0.6724999999999999</v>
       </c>
       <c r="Q175" t="n">
         <v>2</v>
@@ -13441,19 +13441,19 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>6.18</v>
+        <v>0.62</v>
       </c>
       <c r="M176" t="n">
-        <v>6.46</v>
+        <v>0.65</v>
       </c>
       <c r="N176" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="O176" t="n">
-        <v>8.970000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="P176" t="n">
-        <v>6.978499999999999</v>
+        <v>0.7005</v>
       </c>
       <c r="Q176" t="n">
         <v>3</v>
@@ -13515,19 +13515,19 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>6.59</v>
+        <v>0.66</v>
       </c>
       <c r="M177" t="n">
-        <v>6.83</v>
+        <v>0.68</v>
       </c>
       <c r="N177" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O177" t="n">
-        <v>9.33</v>
+        <v>0.93</v>
       </c>
       <c r="P177" t="n">
-        <v>7.616999999999999</v>
+        <v>0.7615000000000001</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
@@ -13589,19 +13589,19 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>6.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M178" t="n">
-        <v>7.11</v>
+        <v>0.71</v>
       </c>
       <c r="N178" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O178" t="n">
-        <v>9.33</v>
+        <v>0.93</v>
       </c>
       <c r="P178" t="n">
-        <v>7.285</v>
+        <v>0.7289999999999999</v>
       </c>
       <c r="Q178" t="n">
         <v>2</v>
@@ -13663,19 +13663,19 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8.4</v>
+        <v>0.84</v>
       </c>
       <c r="M179" t="n">
-        <v>8.52</v>
+        <v>0.85</v>
       </c>
       <c r="N179" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O179" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P179" t="n">
-        <v>7.69</v>
+        <v>0.7675</v>
       </c>
       <c r="Q179" t="n">
         <v>3</v>
@@ -13737,19 +13737,19 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="M180" t="n">
-        <v>8.31</v>
+        <v>0.83</v>
       </c>
       <c r="N180" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O180" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P180" t="n">
-        <v>8.045500000000001</v>
+        <v>0.8045</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
@@ -13811,19 +13811,19 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="M181" t="n">
-        <v>8.029999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="N181" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O181" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P181" t="n">
-        <v>7.8575</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="Q181" t="n">
         <v>2</v>
@@ -13885,19 +13885,19 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7.65</v>
+        <v>0.77</v>
       </c>
       <c r="M182" t="n">
-        <v>7.82</v>
+        <v>0.78</v>
       </c>
       <c r="N182" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O182" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P182" t="n">
-        <v>7.378500000000001</v>
+        <v>0.7385</v>
       </c>
       <c r="Q182" t="n">
         <v>2</v>
@@ -13959,19 +13959,19 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7.21</v>
+        <v>0.72</v>
       </c>
       <c r="M183" t="n">
-        <v>7.41</v>
+        <v>0.74</v>
       </c>
       <c r="N183" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P183" t="n">
-        <v>7.702999999999999</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="Q183" t="n">
         <v>1</v>
@@ -14033,19 +14033,19 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M184" t="n">
-        <v>7.1</v>
+        <v>0.71</v>
       </c>
       <c r="N184" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O184" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P184" t="n">
-        <v>7.061499999999999</v>
+        <v>0.706</v>
       </c>
       <c r="Q184" t="n">
         <v>3</v>
@@ -14107,19 +14107,19 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>8.27</v>
+        <v>0.83</v>
       </c>
       <c r="M185" t="n">
-        <v>8.27</v>
+        <v>0.83</v>
       </c>
       <c r="N185" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O185" t="n">
-        <v>7.51</v>
+        <v>0.75</v>
       </c>
       <c r="P185" t="n">
-        <v>8.068</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="Q185" t="n">
         <v>2</v>
@@ -14181,19 +14181,19 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>7.97</v>
+        <v>0.8</v>
       </c>
       <c r="M186" t="n">
-        <v>7.98</v>
+        <v>0.8</v>
       </c>
       <c r="N186" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>7.51</v>
+        <v>0.75</v>
       </c>
       <c r="P186" t="n">
-        <v>8.310499999999999</v>
+        <v>0.8325</v>
       </c>
       <c r="Q186" t="n">
         <v>1</v>
@@ -14255,19 +14255,19 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>7.46</v>
+        <v>0.75</v>
       </c>
       <c r="M187" t="n">
-        <v>7.48</v>
+        <v>0.75</v>
       </c>
       <c r="N187" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O187" t="n">
-        <v>7.51</v>
+        <v>0.75</v>
       </c>
       <c r="P187" t="n">
-        <v>7.2045</v>
+        <v>0.722</v>
       </c>
       <c r="Q187" t="n">
         <v>3</v>
@@ -14329,19 +14329,19 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>9.75</v>
+        <v>0.98</v>
       </c>
       <c r="M188" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N188" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O188" t="n">
-        <v>7.32</v>
+        <v>0.73</v>
       </c>
       <c r="P188" t="n">
-        <v>8.846</v>
+        <v>0.8865000000000001</v>
       </c>
       <c r="Q188" t="n">
         <v>2</v>
@@ -14403,19 +14403,19 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>9.550000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M189" t="n">
-        <v>9.58</v>
+        <v>0.96</v>
       </c>
       <c r="N189" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O189" t="n">
-        <v>7.32</v>
+        <v>0.73</v>
       </c>
       <c r="P189" t="n">
-        <v>9.180000000000001</v>
+        <v>0.9165000000000001</v>
       </c>
       <c r="Q189" t="n">
         <v>1</v>
@@ -14477,19 +14477,19 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>9.27</v>
+        <v>0.93</v>
       </c>
       <c r="M190" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="N190" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O190" t="n">
-        <v>7.32</v>
+        <v>0.73</v>
       </c>
       <c r="P190" t="n">
-        <v>8.706999999999999</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="Q190" t="n">
         <v>3</v>
@@ -14551,19 +14551,19 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>6.02</v>
+        <v>0.6</v>
       </c>
       <c r="M191" t="n">
-        <v>6.09</v>
+        <v>0.61</v>
       </c>
       <c r="N191" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O191" t="n">
-        <v>8.49</v>
+        <v>0.85</v>
       </c>
       <c r="P191" t="n">
-        <v>6.777</v>
+        <v>0.677</v>
       </c>
       <c r="Q191" t="n">
         <v>3</v>
@@ -14625,19 +14625,19 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O192" t="n">
-        <v>7.95</v>
+        <v>0.8</v>
       </c>
       <c r="P192" t="n">
-        <v>9.5565</v>
+        <v>0.956</v>
       </c>
       <c r="Q192" t="n">
         <v>1</v>
@@ -14699,19 +14699,19 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N193" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O193" t="n">
-        <v>6.18</v>
+        <v>0.62</v>
       </c>
       <c r="P193" t="n">
-        <v>8.827</v>
+        <v>0.8829999999999999</v>
       </c>
       <c r="Q193" t="n">
         <v>2</v>
@@ -14773,19 +14773,19 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>9.609999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M194" t="n">
-        <v>9.539999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="N194" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O194" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="P194" t="n">
-        <v>8.524000000000001</v>
+        <v>0.8504999999999999</v>
       </c>
       <c r="Q194" t="n">
         <v>3</v>
@@ -14847,19 +14847,19 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>9.15</v>
+        <v>0.92</v>
       </c>
       <c r="M195" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="N195" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O195" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="P195" t="n">
-        <v>8.7265</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="Q195" t="n">
         <v>1</v>
@@ -14921,19 +14921,19 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>8.699999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="M196" t="n">
-        <v>8.640000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="N196" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O196" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="P196" t="n">
-        <v>8.577999999999999</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="Q196" t="n">
         <v>2</v>
@@ -14995,19 +14995,19 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.64</v>
+        <v>0.16</v>
       </c>
       <c r="M197" t="n">
-        <v>1.84</v>
+        <v>0.18</v>
       </c>
       <c r="N197" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O197" t="n">
-        <v>6.8</v>
+        <v>0.68</v>
       </c>
       <c r="P197" t="n">
-        <v>3.056</v>
+        <v>0.303</v>
       </c>
       <c r="Q197" t="n">
         <v>3</v>
@@ -15069,19 +15069,19 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.62</v>
+        <v>0.26</v>
       </c>
       <c r="M198" t="n">
-        <v>2.79</v>
+        <v>0.28</v>
       </c>
       <c r="N198" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O198" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P198" t="n">
-        <v>4.8305</v>
+        <v>0.4835</v>
       </c>
       <c r="Q198" t="n">
         <v>2</v>
@@ -15143,19 +15143,19 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>3.61</v>
+        <v>0.36</v>
       </c>
       <c r="M199" t="n">
-        <v>3.74</v>
+        <v>0.37</v>
       </c>
       <c r="N199" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O199" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P199" t="n">
-        <v>4.94</v>
+        <v>0.493</v>
       </c>
       <c r="Q199" t="n">
         <v>1</v>
@@ -15217,19 +15217,19 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>6.72</v>
+        <v>0.67</v>
       </c>
       <c r="M200" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="N200" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O200" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="P200" t="n">
-        <v>6.0985</v>
+        <v>0.611</v>
       </c>
       <c r="Q200" t="n">
         <v>2</v>
@@ -15291,19 +15291,19 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>6.13</v>
+        <v>0.61</v>
       </c>
       <c r="M201" t="n">
-        <v>6.19</v>
+        <v>0.62</v>
       </c>
       <c r="N201" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O201" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="P201" t="n">
-        <v>6.629999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="Q201" t="n">
         <v>1</v>
@@ -15365,19 +15365,19 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>5.31</v>
+        <v>0.53</v>
       </c>
       <c r="M202" t="n">
-        <v>5.4</v>
+        <v>0.54</v>
       </c>
       <c r="N202" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O202" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="P202" t="n">
-        <v>5.6095</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="Q202" t="n">
         <v>3</v>
@@ -15439,19 +15439,19 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="N203" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O203" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="P203" t="n">
-        <v>2.959</v>
+        <v>0.2965</v>
       </c>
       <c r="Q203" t="n">
         <v>3</v>
@@ -15513,19 +15513,19 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.17</v>
+        <v>0.12</v>
       </c>
       <c r="M204" t="n">
-        <v>1.38</v>
+        <v>0.14</v>
       </c>
       <c r="N204" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O204" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="P204" t="n">
-        <v>3.6925</v>
+        <v>0.371</v>
       </c>
       <c r="Q204" t="n">
         <v>2</v>
@@ -15587,19 +15587,19 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.31</v>
+        <v>0.23</v>
       </c>
       <c r="M205" t="n">
-        <v>2.49</v>
+        <v>0.25</v>
       </c>
       <c r="N205" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O205" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="P205" t="n">
-        <v>3.777</v>
+        <v>0.377</v>
       </c>
       <c r="Q205" t="n">
         <v>1</v>
@@ -15661,19 +15661,19 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O206" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P206" t="n">
-        <v>9.583500000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="Q206" t="n">
         <v>2</v>
@@ -15735,19 +15735,19 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P207" t="n">
-        <v>9.8635</v>
+        <v>0.9864999999999999</v>
       </c>
       <c r="Q207" t="n">
         <v>1</v>
@@ -15809,19 +15809,19 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O208" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P208" t="n">
-        <v>9.583500000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="Q208" t="n">
         <v>3</v>
@@ -15883,19 +15883,19 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>9.449999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="M209" t="n">
-        <v>9.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N209" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O209" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P209" t="n">
-        <v>8.588000000000001</v>
+        <v>0.8589999999999999</v>
       </c>
       <c r="Q209" t="n">
         <v>3</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>9.300000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="M210" t="n">
-        <v>9.27</v>
+        <v>0.93</v>
       </c>
       <c r="N210" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O210" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P210" t="n">
-        <v>8.954499999999999</v>
+        <v>0.8955000000000001</v>
       </c>
       <c r="Q210" t="n">
         <v>1</v>
@@ -16031,19 +16031,19 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>9.15</v>
+        <v>0.91</v>
       </c>
       <c r="M211" t="n">
-        <v>9.119999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="N211" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O211" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P211" t="n">
-        <v>8.712999999999999</v>
+        <v>0.8685</v>
       </c>
       <c r="Q211" t="n">
         <v>2</v>
@@ -16105,19 +16105,19 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>7.47</v>
+        <v>0.75</v>
       </c>
       <c r="M212" t="n">
-        <v>7.66</v>
+        <v>0.77</v>
       </c>
       <c r="N212" t="n">
-        <v>1.38</v>
+        <v>0.14</v>
       </c>
       <c r="O212" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P212" t="n">
-        <v>6.2825</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="Q212" t="n">
         <v>3</v>
@@ -16179,19 +16179,19 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>7.19</v>
+        <v>0.72</v>
       </c>
       <c r="M213" t="n">
-        <v>7.39</v>
+        <v>0.74</v>
       </c>
       <c r="N213" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="O213" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P213" t="n">
-        <v>7.012</v>
+        <v>0.701</v>
       </c>
       <c r="Q213" t="n">
         <v>2</v>
@@ -16253,19 +16253,19 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>6.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M214" t="n">
-        <v>7.12</v>
+        <v>0.71</v>
       </c>
       <c r="N214" t="n">
-        <v>9.109999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="O214" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="P214" t="n">
-        <v>7.4685</v>
+        <v>0.7454999999999999</v>
       </c>
       <c r="Q214" t="n">
         <v>1</v>
@@ -16327,19 +16327,19 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N215" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O215" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="P215" t="n">
-        <v>8.790000000000001</v>
+        <v>0.8789999999999999</v>
       </c>
       <c r="Q215" t="n">
         <v>3</v>
@@ -16401,19 +16401,19 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N216" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O216" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="P216" t="n">
-        <v>9.356</v>
+        <v>0.9369999999999999</v>
       </c>
       <c r="Q216" t="n">
         <v>2</v>
@@ -16475,19 +16475,19 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>9.99</v>
+        <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O217" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="P217" t="n">
-        <v>9.510499999999999</v>
+        <v>0.953</v>
       </c>
       <c r="Q217" t="n">
         <v>1</v>
@@ -16549,19 +16549,19 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O218" t="n">
-        <v>7.78</v>
+        <v>0.78</v>
       </c>
       <c r="P218" t="n">
-        <v>8.239000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="Q218" t="n">
         <v>3</v>
@@ -16623,19 +16623,19 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N219" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O219" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="P219" t="n">
-        <v>9.262</v>
+        <v>0.9264999999999999</v>
       </c>
       <c r="Q219" t="n">
         <v>2</v>
@@ -16697,19 +16697,19 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N220" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O220" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="P220" t="n">
-        <v>9.726000000000001</v>
+        <v>0.9724999999999999</v>
       </c>
       <c r="Q220" t="n">
         <v>1</v>
@@ -16771,19 +16771,19 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N221" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O221" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="P221" t="n">
-        <v>8.946</v>
+        <v>0.8949999999999999</v>
       </c>
       <c r="Q221" t="n">
         <v>3</v>
@@ -16845,19 +16845,19 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N222" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O222" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="P222" t="n">
-        <v>9.444000000000001</v>
+        <v>0.945</v>
       </c>
       <c r="Q222" t="n">
         <v>2</v>
@@ -16919,19 +16919,19 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>9.76</v>
+        <v>0.98</v>
       </c>
       <c r="M223" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="N223" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="P223" t="n">
-        <v>9.554</v>
+        <v>0.9564999999999999</v>
       </c>
       <c r="Q223" t="n">
         <v>1</v>
@@ -16993,19 +16993,19 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N224" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O224" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="P224" t="n">
-        <v>9.583500000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="Q224" t="n">
         <v>1</v>
@@ -17067,19 +17067,19 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N225" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O225" t="n">
-        <v>8.75</v>
+        <v>0.87</v>
       </c>
       <c r="P225" t="n">
-        <v>9.532500000000001</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="Q225" t="n">
         <v>2</v>
@@ -17141,19 +17141,19 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N226" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O226" t="n">
-        <v>8.75</v>
+        <v>0.87</v>
       </c>
       <c r="P226" t="n">
-        <v>8.8385</v>
+        <v>0.8824999999999998</v>
       </c>
       <c r="Q226" t="n">
         <v>3</v>
@@ -17215,19 +17215,19 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="M227" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="N227" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O227" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="P227" t="n">
-        <v>7.5925</v>
+        <v>0.7585</v>
       </c>
       <c r="Q227" t="n">
         <v>3</v>
@@ -17289,19 +17289,19 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N228" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O228" t="n">
-        <v>9.67</v>
+        <v>0.97</v>
       </c>
       <c r="P228" t="n">
-        <v>9.670500000000001</v>
+        <v>0.9674999999999999</v>
       </c>
       <c r="Q228" t="n">
         <v>1</v>
@@ -17363,19 +17363,19 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N229" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O229" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P229" t="n">
-        <v>8.292999999999999</v>
+        <v>0.8294999999999999</v>
       </c>
       <c r="Q229" t="n">
         <v>2</v>
@@ -17437,19 +17437,19 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N230" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O230" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="P230" t="n">
-        <v>8.837</v>
+        <v>0.8824999999999998</v>
       </c>
       <c r="Q230" t="n">
         <v>3</v>
@@ -17511,19 +17511,19 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N231" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O231" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="P231" t="n">
-        <v>9.531000000000001</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="Q231" t="n">
         <v>1</v>
@@ -17585,19 +17585,19 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N232" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O232" t="n">
-        <v>8.4</v>
+        <v>0.84</v>
       </c>
       <c r="P232" t="n">
-        <v>9.48</v>
+        <v>0.948</v>
       </c>
       <c r="Q232" t="n">
         <v>2</v>
@@ -17659,19 +17659,19 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M233" t="n">
-        <v>6.98</v>
+        <v>0.7</v>
       </c>
       <c r="N233" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O233" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="P233" t="n">
-        <v>7.1725</v>
+        <v>0.718</v>
       </c>
       <c r="Q233" t="n">
         <v>3</v>
@@ -17733,19 +17733,19 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M234" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N234" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O234" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="P234" t="n">
-        <v>9.471500000000001</v>
+        <v>0.9475</v>
       </c>
       <c r="Q234" t="n">
         <v>1</v>
@@ -17807,19 +17807,19 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N235" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O235" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="P235" t="n">
-        <v>8.679500000000001</v>
+        <v>0.8674999999999999</v>
       </c>
       <c r="Q235" t="n">
         <v>2</v>
@@ -17881,19 +17881,19 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>8.83</v>
+        <v>0.88</v>
       </c>
       <c r="M236" t="n">
-        <v>8.82</v>
+        <v>0.88</v>
       </c>
       <c r="N236" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O236" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P236" t="n">
-        <v>8.5175</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="Q236" t="n">
         <v>3</v>
@@ -17955,19 +17955,19 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="M237" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="N237" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P237" t="n">
-        <v>9.224500000000001</v>
+        <v>0.9229999999999999</v>
       </c>
       <c r="Q237" t="n">
         <v>1</v>
@@ -18029,19 +18029,19 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N238" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O238" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="P238" t="n">
-        <v>9.1805</v>
+        <v>0.9169999999999999</v>
       </c>
       <c r="Q238" t="n">
         <v>2</v>
@@ -18103,19 +18103,19 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>7.93</v>
+        <v>0.79</v>
       </c>
       <c r="M239" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="N239" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P239" t="n">
-        <v>8.4625</v>
+        <v>0.847</v>
       </c>
       <c r="Q239" t="n">
         <v>1</v>
@@ -18177,19 +18177,19 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>8.25</v>
+        <v>0.82</v>
       </c>
       <c r="M240" t="n">
-        <v>8.18</v>
+        <v>0.82</v>
       </c>
       <c r="N240" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O240" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P240" t="n">
-        <v>8.067</v>
+        <v>0.8065</v>
       </c>
       <c r="Q240" t="n">
         <v>2</v>
@@ -18251,19 +18251,19 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N241" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O241" t="n">
-        <v>4.35</v>
+        <v>0.44</v>
       </c>
       <c r="P241" t="n">
-        <v>7.9645</v>
+        <v>0.7979999999999998</v>
       </c>
       <c r="Q241" t="n">
         <v>3</v>
@@ -18325,19 +18325,19 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>8.68</v>
+        <v>0.87</v>
       </c>
       <c r="M242" t="n">
-        <v>8.67</v>
+        <v>0.87</v>
       </c>
       <c r="N242" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O242" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="P242" t="n">
-        <v>8.651499999999999</v>
+        <v>0.8665</v>
       </c>
       <c r="Q242" t="n">
         <v>2</v>
@@ -18399,19 +18399,19 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>8.890000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="M243" t="n">
-        <v>8.869999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N243" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O243" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="P243" t="n">
-        <v>8.9285</v>
+        <v>0.8935000000000001</v>
       </c>
       <c r="Q243" t="n">
         <v>1</v>
@@ -18473,19 +18473,19 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N244" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O244" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P244" t="n">
-        <v>8.5665</v>
+        <v>0.8559999999999999</v>
       </c>
       <c r="Q244" t="n">
         <v>3</v>
@@ -18547,19 +18547,19 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>6.05</v>
+        <v>0.61</v>
       </c>
       <c r="M245" t="n">
-        <v>6.01</v>
+        <v>0.6</v>
       </c>
       <c r="N245" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O245" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="P245" t="n">
-        <v>7.1015</v>
+        <v>0.7120000000000001</v>
       </c>
       <c r="Q245" t="n">
         <v>2</v>
@@ -18621,19 +18621,19 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="M246" t="n">
-        <v>6.53</v>
+        <v>0.65</v>
       </c>
       <c r="N246" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O246" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="P246" t="n">
-        <v>6.6325</v>
+        <v>0.6625</v>
       </c>
       <c r="Q246" t="n">
         <v>3</v>
@@ -18695,19 +18695,19 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N247" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="O247" t="n">
-        <v>3.62</v>
+        <v>0.36</v>
       </c>
       <c r="P247" t="n">
-        <v>7.171</v>
+        <v>0.716</v>
       </c>
       <c r="Q247" t="n">
         <v>1</v>
@@ -18769,19 +18769,19 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>6.13</v>
+        <v>0.61</v>
       </c>
       <c r="M248" t="n">
-        <v>6.19</v>
+        <v>0.62</v>
       </c>
       <c r="N248" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O248" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P248" t="n">
-        <v>6.6015</v>
+        <v>0.66</v>
       </c>
       <c r="Q248" t="n">
         <v>3</v>
@@ -18843,19 +18843,19 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>6.42</v>
+        <v>0.64</v>
       </c>
       <c r="M249" t="n">
-        <v>6.47</v>
+        <v>0.65</v>
       </c>
       <c r="N249" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P249" t="n">
-        <v>7.4565</v>
+        <v>0.7454999999999999</v>
       </c>
       <c r="Q249" t="n">
         <v>1</v>
@@ -18917,19 +18917,19 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="M250" t="n">
-        <v>6.75</v>
+        <v>0.68</v>
       </c>
       <c r="N250" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="O250" t="n">
-        <v>9.199999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="P250" t="n">
-        <v>7.0825</v>
+        <v>0.711</v>
       </c>
       <c r="Q250" t="n">
         <v>2</v>
@@ -18991,19 +18991,19 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="M251" t="n">
-        <v>7.77</v>
+        <v>0.78</v>
       </c>
       <c r="N251" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O251" t="n">
-        <v>7.72</v>
+        <v>0.77</v>
       </c>
       <c r="P251" t="n">
-        <v>7.946499999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="Q251" t="n">
         <v>1</v>
@@ -19065,19 +19065,19 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="M252" t="n">
-        <v>7.94</v>
+        <v>0.79</v>
       </c>
       <c r="N252" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O252" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P252" t="n">
-        <v>7.667000000000001</v>
+        <v>0.7645</v>
       </c>
       <c r="Q252" t="n">
         <v>2</v>
@@ -19139,19 +19139,19 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="M253" t="n">
-        <v>8.109999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N253" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O253" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="P253" t="n">
-        <v>6.805000000000001</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="Q253" t="n">
         <v>3</v>
@@ -19213,19 +19213,19 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>3.67</v>
+        <v>0.37</v>
       </c>
       <c r="M254" t="n">
-        <v>3.81</v>
+        <v>0.38</v>
       </c>
       <c r="N254" t="n">
-        <v>7.34</v>
+        <v>0.73</v>
       </c>
       <c r="O254" t="n">
-        <v>8.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P254" t="n">
-        <v>5.1145</v>
+        <v>0.5115000000000001</v>
       </c>
       <c r="Q254" t="n">
         <v>3</v>
@@ -19287,19 +19287,19 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>4.4</v>
+        <v>0.44</v>
       </c>
       <c r="M255" t="n">
-        <v>4.52</v>
+        <v>0.45</v>
       </c>
       <c r="N255" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="O255" t="n">
-        <v>8.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P255" t="n">
-        <v>5.95</v>
+        <v>0.595</v>
       </c>
       <c r="Q255" t="n">
         <v>1</v>
@@ -19361,19 +19361,19 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="M256" t="n">
-        <v>5.22</v>
+        <v>0.52</v>
       </c>
       <c r="N256" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O256" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="P256" t="n">
-        <v>5.653499999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Q256" t="n">
         <v>2</v>
@@ -19435,19 +19435,19 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="M257" t="n">
-        <v>8.140000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N257" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O257" t="n">
-        <v>6.45</v>
+        <v>0.65</v>
       </c>
       <c r="P257" t="n">
-        <v>6.8485</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="Q257" t="n">
         <v>3</v>
@@ -19509,19 +19509,19 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>7.64</v>
+        <v>0.76</v>
       </c>
       <c r="M258" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="N258" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O258" t="n">
-        <v>6.48</v>
+        <v>0.65</v>
       </c>
       <c r="P258" t="n">
-        <v>7.320499999999999</v>
+        <v>0.7314999999999999</v>
       </c>
       <c r="Q258" t="n">
         <v>2</v>
@@ -19583,19 +19583,19 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="M259" t="n">
-        <v>7.18</v>
+        <v>0.72</v>
       </c>
       <c r="N259" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O259" t="n">
-        <v>6.48</v>
+        <v>0.65</v>
       </c>
       <c r="P259" t="n">
-        <v>7.518000000000001</v>
+        <v>0.7515000000000001</v>
       </c>
       <c r="Q259" t="n">
         <v>1</v>
@@ -19657,19 +19657,19 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M260" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N260" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O260" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P260" t="n">
-        <v>8.956</v>
+        <v>0.8949999999999999</v>
       </c>
       <c r="Q260" t="n">
         <v>3</v>
@@ -19731,19 +19731,19 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M261" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N261" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O261" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P261" t="n">
-        <v>9.420000000000002</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q261" t="n">
         <v>1</v>
@@ -19805,19 +19805,19 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N262" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O262" t="n">
-        <v>7.04</v>
+        <v>0.7</v>
       </c>
       <c r="P262" t="n">
-        <v>9.276</v>
+        <v>0.9269999999999999</v>
       </c>
       <c r="Q262" t="n">
         <v>2</v>
@@ -19879,19 +19879,19 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="M263" t="n">
-        <v>8.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>2.91</v>
+        <v>0.29</v>
       </c>
       <c r="P263" t="n">
-        <v>5.719499999999999</v>
+        <v>0.573</v>
       </c>
       <c r="Q263" t="n">
         <v>3</v>
@@ -19953,19 +19953,19 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>7.86</v>
+        <v>0.79</v>
       </c>
       <c r="M264" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="N264" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O264" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="P264" t="n">
-        <v>6.836</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="Q264" t="n">
         <v>2</v>
@@ -20027,19 +20027,19 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>7.55</v>
+        <v>0.75</v>
       </c>
       <c r="M265" t="n">
-        <v>7.49</v>
+        <v>0.75</v>
       </c>
       <c r="N265" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O265" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="P265" t="n">
-        <v>7.2225</v>
+        <v>0.7204999999999999</v>
       </c>
       <c r="Q265" t="n">
         <v>1</v>
@@ -20101,19 +20101,19 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>6.02</v>
+        <v>0.6</v>
       </c>
       <c r="M266" t="n">
-        <v>6.08</v>
+        <v>0.61</v>
       </c>
       <c r="N266" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O266" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P266" t="n">
-        <v>6.765999999999999</v>
+        <v>0.6755</v>
       </c>
       <c r="Q266" t="n">
         <v>3</v>
@@ -20175,19 +20175,19 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="M267" t="n">
-        <v>6.35</v>
+        <v>0.64</v>
       </c>
       <c r="N267" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P267" t="n">
-        <v>7.3755</v>
+        <v>0.739</v>
       </c>
       <c r="Q267" t="n">
         <v>1</v>
@@ -20249,19 +20249,19 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>6.57</v>
+        <v>0.66</v>
       </c>
       <c r="M268" t="n">
-        <v>6.62</v>
+        <v>0.66</v>
       </c>
       <c r="N268" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O268" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="P268" t="n">
-        <v>7.171</v>
+        <v>0.717</v>
       </c>
       <c r="Q268" t="n">
         <v>2</v>
@@ -20323,19 +20323,19 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>8.550000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="M269" t="n">
-        <v>8.48</v>
+        <v>0.85</v>
       </c>
       <c r="N269" t="n">
         <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>2.85</v>
+        <v>0.29</v>
       </c>
       <c r="P269" t="n">
-        <v>5.9605</v>
+        <v>0.596</v>
       </c>
       <c r="Q269" t="n">
         <v>3</v>
@@ -20397,19 +20397,19 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="M270" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="N270" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O270" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P270" t="n">
-        <v>7.061500000000001</v>
+        <v>0.7064999999999999</v>
       </c>
       <c r="Q270" t="n">
         <v>2</v>
@@ -20471,19 +20471,19 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="M271" t="n">
-        <v>7.85</v>
+        <v>0.79</v>
       </c>
       <c r="N271" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O271" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="P271" t="n">
-        <v>7.4415</v>
+        <v>0.745</v>
       </c>
       <c r="Q271" t="n">
         <v>1</v>
@@ -20545,19 +20545,19 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>3.25</v>
+        <v>0.32</v>
       </c>
       <c r="M272" t="n">
-        <v>3.39</v>
+        <v>0.34</v>
       </c>
       <c r="N272" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="P272" t="n">
-        <v>5.3675</v>
+        <v>0.535</v>
       </c>
       <c r="Q272" t="n">
         <v>1</v>
@@ -20619,19 +20619,19 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>3.78</v>
+        <v>0.38</v>
       </c>
       <c r="M273" t="n">
-        <v>3.91</v>
+        <v>0.39</v>
       </c>
       <c r="N273" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="O273" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="P273" t="n">
-        <v>5.2265</v>
+        <v>0.5225</v>
       </c>
       <c r="Q273" t="n">
         <v>2</v>
@@ -20693,19 +20693,19 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>4.31</v>
+        <v>0.43</v>
       </c>
       <c r="M274" t="n">
-        <v>4.42</v>
+        <v>0.44</v>
       </c>
       <c r="N274" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="O274" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="P274" t="n">
-        <v>4.946</v>
+        <v>0.493</v>
       </c>
       <c r="Q274" t="n">
         <v>3</v>
@@ -20767,19 +20767,19 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>8.58</v>
+        <v>0.86</v>
       </c>
       <c r="M275" t="n">
-        <v>8.57</v>
+        <v>0.86</v>
       </c>
       <c r="N275" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O275" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="P275" t="n">
-        <v>7.554999999999999</v>
+        <v>0.7569999999999999</v>
       </c>
       <c r="Q275" t="n">
         <v>3</v>
@@ -20841,19 +20841,19 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>8.24</v>
+        <v>0.82</v>
       </c>
       <c r="M276" t="n">
-        <v>8.24</v>
+        <v>0.82</v>
       </c>
       <c r="N276" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O276" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="P276" t="n">
-        <v>7.8775</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="Q276" t="n">
         <v>2</v>
@@ -20915,19 +20915,19 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>7.9</v>
+        <v>0.79</v>
       </c>
       <c r="M277" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="N277" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O277" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="P277" t="n">
-        <v>8.094000000000001</v>
+        <v>0.8095</v>
       </c>
       <c r="Q277" t="n">
         <v>1</v>
@@ -20989,19 +20989,19 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>6.05</v>
+        <v>0.6</v>
       </c>
       <c r="M278" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="N278" t="n">
-        <v>1.81</v>
+        <v>0.18</v>
       </c>
       <c r="O278" t="n">
-        <v>5.16</v>
+        <v>0.52</v>
       </c>
       <c r="P278" t="n">
-        <v>5.0895</v>
+        <v>0.5075</v>
       </c>
       <c r="Q278" t="n">
         <v>3</v>
@@ -21063,19 +21063,19 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>5.54</v>
+        <v>0.55</v>
       </c>
       <c r="M279" t="n">
-        <v>5.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N279" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O279" t="n">
-        <v>6.17</v>
+        <v>0.62</v>
       </c>
       <c r="P279" t="n">
-        <v>5.6805</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q279" t="n">
         <v>2</v>
@@ -21137,19 +21137,19 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>5.03</v>
+        <v>0.5</v>
       </c>
       <c r="M280" t="n">
-        <v>5.12</v>
+        <v>0.51</v>
       </c>
       <c r="N280" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O280" t="n">
-        <v>6.17</v>
+        <v>0.62</v>
       </c>
       <c r="P280" t="n">
-        <v>5.9185</v>
+        <v>0.5915</v>
       </c>
       <c r="Q280" t="n">
         <v>1</v>
@@ -21211,19 +21211,19 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>8.15</v>
+        <v>0.82</v>
       </c>
       <c r="M281" t="n">
-        <v>8.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N281" t="n">
         <v>0</v>
       </c>
       <c r="O281" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="P281" t="n">
-        <v>5.502999999999999</v>
+        <v>0.5519999999999999</v>
       </c>
       <c r="Q281" t="n">
         <v>3</v>
@@ -21285,19 +21285,19 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>7.85</v>
+        <v>0.78</v>
       </c>
       <c r="M282" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="N282" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="O282" t="n">
-        <v>3.96</v>
+        <v>0.4</v>
       </c>
       <c r="P282" t="n">
-        <v>5.9815</v>
+        <v>0.597</v>
       </c>
       <c r="Q282" t="n">
         <v>2</v>
@@ -21359,19 +21359,19 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>7.55</v>
+        <v>0.75</v>
       </c>
       <c r="M283" t="n">
-        <v>7.49</v>
+        <v>0.75</v>
       </c>
       <c r="N283" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O283" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="P283" t="n">
-        <v>6.816999999999999</v>
+        <v>0.6794999999999999</v>
       </c>
       <c r="Q283" t="n">
         <v>1</v>
@@ -21433,19 +21433,19 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="M284" t="n">
-        <v>8.77</v>
+        <v>0.88</v>
       </c>
       <c r="N284" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O284" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P284" t="n">
-        <v>7.6955</v>
+        <v>0.77</v>
       </c>
       <c r="Q284" t="n">
         <v>3</v>
@@ -21507,19 +21507,19 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>8.449999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="M285" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="N285" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O285" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P285" t="n">
-        <v>8.020999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="Q285" t="n">
         <v>2</v>
@@ -21581,19 +21581,19 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M286" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N286" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="P286" t="n">
-        <v>8.243999999999998</v>
+        <v>0.8224999999999999</v>
       </c>
       <c r="Q286" t="n">
         <v>1</v>
@@ -21655,19 +21655,19 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="M287" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="N287" t="n">
         <v>0</v>
       </c>
       <c r="O287" t="n">
-        <v>3.08</v>
+        <v>0.31</v>
       </c>
       <c r="P287" t="n">
-        <v>6.031999999999999</v>
+        <v>0.6025</v>
       </c>
       <c r="Q287" t="n">
         <v>3</v>
@@ -21729,19 +21729,19 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>8.27</v>
+        <v>0.83</v>
       </c>
       <c r="M288" t="n">
-        <v>8.4</v>
+        <v>0.84</v>
       </c>
       <c r="N288" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O288" t="n">
-        <v>6.51</v>
+        <v>0.65</v>
       </c>
       <c r="P288" t="n">
-        <v>7.209499999999999</v>
+        <v>0.7224999999999999</v>
       </c>
       <c r="Q288" t="n">
         <v>2</v>
@@ -21803,19 +21803,19 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>8.029999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="M289" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="N289" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O289" t="n">
-        <v>6.51</v>
+        <v>0.65</v>
       </c>
       <c r="P289" t="n">
-        <v>7.645</v>
+        <v>0.7645</v>
       </c>
       <c r="Q289" t="n">
         <v>1</v>
@@ -21877,19 +21877,19 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="M290" t="n">
-        <v>0.48</v>
+        <v>0.05</v>
       </c>
       <c r="N290" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O290" t="n">
-        <v>4.92</v>
+        <v>0.49</v>
       </c>
       <c r="P290" t="n">
-        <v>1.496</v>
+        <v>0.152</v>
       </c>
       <c r="Q290" t="n">
         <v>3</v>
@@ -21957,13 +21957,13 @@
         <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O291" t="n">
-        <v>5.89</v>
+        <v>0.59</v>
       </c>
       <c r="P291" t="n">
-        <v>2.1055</v>
+        <v>0.2105</v>
       </c>
       <c r="Q291" t="n">
         <v>2</v>
@@ -22031,13 +22031,13 @@
         <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O292" t="n">
-        <v>5.89</v>
+        <v>0.59</v>
       </c>
       <c r="P292" t="n">
-        <v>2.6035</v>
+        <v>0.2605</v>
       </c>
       <c r="Q292" t="n">
         <v>1</v>
@@ -22099,19 +22099,19 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>8.57</v>
+        <v>0.86</v>
       </c>
       <c r="M293" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="N293" t="n">
         <v>0</v>
       </c>
       <c r="O293" t="n">
-        <v>2.91</v>
+        <v>0.29</v>
       </c>
       <c r="P293" t="n">
-        <v>5.986</v>
+        <v>0.599</v>
       </c>
       <c r="Q293" t="n">
         <v>3</v>
@@ -22173,19 +22173,19 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
       <c r="M294" t="n">
-        <v>8.19</v>
+        <v>0.82</v>
       </c>
       <c r="N294" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="O294" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="P294" t="n">
-        <v>7.0895</v>
+        <v>0.7109999999999999</v>
       </c>
       <c r="Q294" t="n">
         <v>2</v>
@@ -22247,19 +22247,19 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>7.93</v>
+        <v>0.79</v>
       </c>
       <c r="M295" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="N295" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O295" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="P295" t="n">
-        <v>7.4695</v>
+        <v>0.7464999999999999</v>
       </c>
       <c r="Q295" t="n">
         <v>1</v>
@@ -22327,13 +22327,13 @@
         <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="O296" t="n">
-        <v>5.28</v>
+        <v>0.53</v>
       </c>
       <c r="P296" t="n">
-        <v>0.92</v>
+        <v>0.0915</v>
       </c>
       <c r="Q296" t="n">
         <v>3</v>
@@ -22401,13 +22401,13 @@
         <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O297" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P297" t="n">
-        <v>1.9725</v>
+        <v>0.1965</v>
       </c>
       <c r="Q297" t="n">
         <v>2</v>
@@ -22475,13 +22475,13 @@
         <v>0</v>
       </c>
       <c r="N298" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="O298" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="P298" t="n">
-        <v>2.6065</v>
+        <v>0.2605</v>
       </c>
       <c r="Q298" t="n">
         <v>1</v>
@@ -22543,19 +22543,19 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>5.76</v>
+        <v>0.58</v>
       </c>
       <c r="M299" t="n">
-        <v>5.84</v>
+        <v>0.58</v>
       </c>
       <c r="N299" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O299" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P299" t="n">
-        <v>6.604</v>
+        <v>0.659</v>
       </c>
       <c r="Q299" t="n">
         <v>3</v>
@@ -22617,19 +22617,19 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>6.07</v>
+        <v>0.61</v>
       </c>
       <c r="M300" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="N300" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O300" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P300" t="n">
-        <v>7.236</v>
+        <v>0.7225</v>
       </c>
       <c r="Q300" t="n">
         <v>1</v>
@@ -22691,19 +22691,19 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>6.38</v>
+        <v>0.64</v>
       </c>
       <c r="M301" t="n">
-        <v>6.43</v>
+        <v>0.64</v>
       </c>
       <c r="N301" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O301" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="P301" t="n">
-        <v>6.996499999999999</v>
+        <v>0.6980000000000001</v>
       </c>
       <c r="Q301" t="n">
         <v>2</v>
@@ -22765,19 +22765,19 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>7.21</v>
+        <v>0.72</v>
       </c>
       <c r="M302" t="n">
-        <v>7.16</v>
+        <v>0.72</v>
       </c>
       <c r="N302" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O302" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P302" t="n">
-        <v>7.618999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="Q302" t="n">
         <v>1</v>
@@ -22839,19 +22839,19 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>7.46</v>
+        <v>0.75</v>
       </c>
       <c r="M303" t="n">
-        <v>7.4</v>
+        <v>0.74</v>
       </c>
       <c r="N303" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="O303" t="n">
-        <v>8.199999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P303" t="n">
-        <v>7.279999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="Q303" t="n">
         <v>2</v>
@@ -22913,19 +22913,19 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>7.71</v>
+        <v>0.77</v>
       </c>
       <c r="M304" t="n">
-        <v>7.65</v>
+        <v>0.77</v>
       </c>
       <c r="N304" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O304" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="P304" t="n">
-        <v>6.517999999999999</v>
+        <v>0.6545</v>
       </c>
       <c r="Q304" t="n">
         <v>3</v>
@@ -22987,19 +22987,19 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>6.35</v>
+        <v>0.63</v>
       </c>
       <c r="M305" t="n">
-        <v>6.3</v>
+        <v>0.63</v>
       </c>
       <c r="N305" t="n">
         <v>0</v>
       </c>
       <c r="O305" t="n">
-        <v>2.54</v>
+        <v>0.25</v>
       </c>
       <c r="P305" t="n">
-        <v>4.491</v>
+        <v>0.447</v>
       </c>
       <c r="Q305" t="n">
         <v>3</v>
@@ -23061,19 +23061,19 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>5.79</v>
+        <v>0.58</v>
       </c>
       <c r="M306" t="n">
-        <v>5.75</v>
+        <v>0.58</v>
       </c>
       <c r="N306" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O306" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P306" t="n">
-        <v>5.616999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Q306" t="n">
         <v>2</v>
@@ -23135,19 +23135,19 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>5.23</v>
+        <v>0.52</v>
       </c>
       <c r="M307" t="n">
-        <v>5.2</v>
+        <v>0.52</v>
       </c>
       <c r="N307" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O307" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P307" t="n">
-        <v>5.9505</v>
+        <v>0.594</v>
       </c>
       <c r="Q307" t="n">
         <v>1</v>
@@ -23209,19 +23209,19 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>5.65</v>
+        <v>0.57</v>
       </c>
       <c r="M308" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="N308" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="O308" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P308" t="n">
-        <v>6.3495</v>
+        <v>0.638</v>
       </c>
       <c r="Q308" t="n">
         <v>3</v>
@@ -23283,19 +23283,19 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="M309" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="N309" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="O309" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="P309" t="n">
-        <v>7.05</v>
+        <v>0.7035</v>
       </c>
       <c r="Q309" t="n">
         <v>2</v>
@@ -23357,19 +23357,19 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>6.4</v>
+        <v>0.64</v>
       </c>
       <c r="M310" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="N310" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O310" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P310" t="n">
-        <v>7.188999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="Q310" t="n">
         <v>1</v>
@@ -23431,19 +23431,19 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="M311" t="n">
-        <v>9.75</v>
+        <v>0.97</v>
       </c>
       <c r="N311" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="O311" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="P311" t="n">
-        <v>8.5185</v>
+        <v>0.8494999999999999</v>
       </c>
       <c r="Q311" t="n">
         <v>3</v>
@@ -23505,19 +23505,19 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M312" t="n">
-        <v>9.5</v>
+        <v>0.95</v>
       </c>
       <c r="N312" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O312" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="P312" t="n">
-        <v>8.893000000000001</v>
+        <v>0.8905</v>
       </c>
       <c r="Q312" t="n">
         <v>2</v>
@@ -23579,19 +23579,19 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>9.19</v>
+        <v>0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="N313" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O313" t="n">
-        <v>6.61</v>
+        <v>0.66</v>
       </c>
       <c r="P313" t="n">
-        <v>8.985999999999999</v>
+        <v>0.9005000000000001</v>
       </c>
       <c r="Q313" t="n">
         <v>1</v>
@@ -23653,19 +23653,19 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>8.31</v>
+        <v>0.83</v>
       </c>
       <c r="M314" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="N314" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="O314" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P314" t="n">
-        <v>8.495999999999999</v>
+        <v>0.8485</v>
       </c>
       <c r="Q314" t="n">
         <v>3</v>
@@ -23727,19 +23727,19 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="M315" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="N315" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O315" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P315" t="n">
-        <v>8.8375</v>
+        <v>0.883</v>
       </c>
       <c r="Q315" t="n">
         <v>1</v>
@@ -23801,19 +23801,19 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>8.57</v>
+        <v>0.86</v>
       </c>
       <c r="M316" t="n">
-        <v>8.67</v>
+        <v>0.87</v>
       </c>
       <c r="N316" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="O316" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="P316" t="n">
-        <v>8.553000000000001</v>
+        <v>0.8565</v>
       </c>
       <c r="Q316" t="n">
         <v>2</v>
